--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lopez\Desktop\V3.0 Javier_LeonhArt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lopez\Desktop\V3.2 Javier_LeonhArt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93DA299-C21B-42D3-991D-89BF8A0B77F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E856D380-3798-4A76-94B1-0FE2677BCA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{8FABD0BB-35D2-4746-8BF5-22ED6BD8493F}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="499">
   <si>
     <t>Date</t>
   </si>
@@ -1552,7 +1552,10 @@
     <t>Gems Main</t>
   </si>
   <si>
-    <t>5x Gossamid Archers</t>
+    <t>Gossamid Archers</t>
+  </si>
+  <si>
+    <t>12 x Kurnoth Hunters</t>
   </si>
 </sst>
 </file>
@@ -2049,10 +2052,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$172</c:f>
+              <c:f>Sheet1!$A$2:$A$176</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="171"/>
+                <c:ptCount val="175"/>
                 <c:pt idx="0">
                   <c:v>43405</c:v>
                 </c:pt>
@@ -2562,16 +2565,28 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>45505</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>45536</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>45627</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$172</c:f>
+              <c:f>Sheet1!$C$2:$C$176</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="171"/>
+                <c:ptCount val="175"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -3078,6 +3093,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3862,8 +3880,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{61558924-6BAF-41CB-A458-0F8F58CE51F4}" name="Table2" displayName="Table2" ref="A1:F172" totalsRowShown="0">
-  <autoFilter ref="A1:F172" xr:uid="{61558924-6BAF-41CB-A458-0F8F58CE51F4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{61558924-6BAF-41CB-A458-0F8F58CE51F4}" name="Table2" displayName="Table2" ref="A1:F176" totalsRowShown="0">
+  <autoFilter ref="A1:F176" xr:uid="{61558924-6BAF-41CB-A458-0F8F58CE51F4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{A1C8C315-1AF4-46A9-829B-F6F66670A080}" name="Date" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{5DD88343-1F7A-4E8C-82DC-76B842BC6326}" name="Project"/>
@@ -3891,7 +3909,7 @@
   <autoFilter ref="H1:H2" xr:uid="{E331850F-6965-449B-A1DC-94B726771513}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{55DB5F22-E9C6-43F4-91B3-C8775CAB6E79}" name="Total Painted">
-      <calculatedColumnFormula>SUM(C2:C1024)</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(C2:C1028)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3934,7 +3952,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0F21A842-DBF6-43AE-B39A-A0811F55AAD9}" name="Table5" displayName="Table5" ref="A1:P236" totalsRowShown="0">
   <autoFilter ref="A1:P236" xr:uid="{0F21A842-DBF6-43AE-B39A-A0811F55AAD9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P236">
-    <sortCondition descending="1" ref="D1:D236"/>
+    <sortCondition ref="B1:B236"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{303018FD-1CFE-44C3-A9A5-27F54CDD884C}" name="Paint"/>
@@ -4277,7 +4295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F725C0D8-4E5E-44F7-BED9-972635B5DB06}">
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J176"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -4336,8 +4354,8 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <f>SUM(C2:C1024)</f>
-        <v>524</v>
+        <f>SUM(C2:C1028)</f>
+        <v>529</v>
       </c>
       <c r="J2" t="s">
         <v>8</v>
@@ -4412,7 +4430,7 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -4515,7 +4533,7 @@
       </c>
       <c r="H9" t="str" cm="1">
         <f t="array" ref="H9">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 2), ROW(Paints!D:D), ""), 2)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 3), Paints!D:D, 0)))</f>
-        <v>Dragon Blood</v>
+        <v>Afro Shadow</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -4542,7 +4560,7 @@
       </c>
       <c r="H10" t="str" cm="1">
         <f t="array" ref="H10">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 3), ROW(Paints!D:D), ""), 3)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 4), Paints!D:D, 0)))</f>
-        <v>Grimy Grey</v>
+        <v>Dragon Blood</v>
       </c>
       <c r="J10" t="s">
         <v>30</v>
@@ -7534,7 +7552,42 @@
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A172" s="1"/>
+      <c r="A172" s="1">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A173" s="1">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A174" s="1">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A175" s="1">
+        <v>45627</v>
+      </c>
+      <c r="B175" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175">
+        <v>5</v>
+      </c>
+      <c r="D175" t="s">
+        <v>497</v>
+      </c>
+      <c r="E175" t="s">
+        <v>170</v>
+      </c>
+      <c r="F175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A176" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J11 B2:B1048576">
@@ -7663,58 +7716,46 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>254</v>
+        <v>390</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D65" si="0">SUM(E2,G2,I2,K2,M2,O2)</f>
-        <v>0</v>
+        <f>SUM(E2,G2,I2,K2,M2,O2)</f>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="B3" t="s">
         <v>294</v>
@@ -7723,103 +7764,85 @@
         <v>296</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(E3,G3,I3,K3,M3,O3)</f>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>448</v>
+        <v>452</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>452</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>487</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>448</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="s">
-        <v>448</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
         <v>294</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>453</v>
+        <f>SUM(E4,G4,I4,K4,M4,O4)</f>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>421</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>307</v>
+        <v>388</v>
       </c>
       <c r="B5" t="s">
         <v>294</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>448</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>468</v>
+        <f>SUM(E5,G5,I5,K5,M5,O5)</f>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>486</v>
+        <v>484</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B6" t="s">
         <v>294</v>
@@ -7828,74 +7851,62 @@
         <v>296</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>452</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>452</v>
+        <f>SUM(E6,G6,I6,K6,M6,O6)</f>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>263</v>
+        <v>418</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>182</v>
+        <v>389</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
-        <v>455</v>
+        <v>296</v>
       </c>
       <c r="D7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>494</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>494</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>331</v>
+        <f>SUM(E7,G7,I7,K7,M7,O7)</f>
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>484</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>294</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
       <c r="D8">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(E8,G8,I8,K8,M8,O8)</f>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -7903,38 +7914,26 @@
       <c r="F8" t="s">
         <v>446</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>445</v>
-      </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B9" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C9" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D9">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>446</v>
+        <f>SUM(E9,G9,I9,K9,M9,O9)</f>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -7946,78 +7945,54 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>298</v>
+        <v>410</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D10">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>493</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>493</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>493</v>
+        <f>SUM(E10,G10,I10,K10,M10,O10)</f>
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B11" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C11" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D11">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>459</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>459</v>
+        <f>SUM(E11,G11,I11,K11,M11,O11)</f>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>313</v>
+        <v>426</v>
       </c>
       <c r="B12" t="s">
         <v>294</v>
@@ -8026,25 +8001,19 @@
         <v>296</v>
       </c>
       <c r="D12">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>416</v>
+        <f>SUM(E12,G12,I12,K12,M12,O12)</f>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>486</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>316</v>
+        <v>409</v>
       </c>
       <c r="B13" t="s">
         <v>294</v>
@@ -8053,25 +8022,49 @@
         <v>296</v>
       </c>
       <c r="D13">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(E13,G13,I13,K13,M13,O13)</f>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>461</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>451</v>
+        <v>461</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>461</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>461</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>461</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>388</v>
+        <v>435</v>
       </c>
       <c r="B14" t="s">
         <v>294</v>
@@ -8080,25 +8073,49 @@
         <v>296</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(E14,G14,I14,K14,M14,O14)</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>461</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>461</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>461</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>449</v>
+        <v>461</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B15" t="s">
         <v>294</v>
@@ -8107,25 +8124,49 @@
         <v>296</v>
       </c>
       <c r="D15">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(E15,G15,I15,K15,M15,O15)</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>461</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>461</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>461</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>418</v>
+        <v>461</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>461</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="B16" t="s">
         <v>294</v>
@@ -8134,25 +8175,25 @@
         <v>296</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
+        <f>SUM(E16,G16,I16,K16,M16,O16)</f>
         <v>2</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
-        <v>484</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16" t="s">
-        <v>449</v>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>451</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="B17" t="s">
         <v>294</v>
@@ -8161,25 +8202,19 @@
         <v>296</v>
       </c>
       <c r="D17">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>446</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17" t="s">
-        <v>417</v>
+        <f>SUM(E17,G17,I17,K17,M17,O17)</f>
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>433</v>
+        <v>293</v>
       </c>
       <c r="B18" t="s">
         <v>294</v>
@@ -8188,313 +8223,214 @@
         <v>296</v>
       </c>
       <c r="D18">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(E18,G18,I18,K18,M18,O18)</f>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>445</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>431</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>386</v>
+        <v>321</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>454</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
+        <f>SUM(E19,G19,I19,K19,M19,O19)</f>
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B20" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D20">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>484</v>
+        <f>SUM(E20,G20,I20,K20,M20,O20)</f>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>1</v>
+      </c>
+      <c r="N20" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="B21" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D21">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>446</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21" t="s">
-        <v>485</v>
+        <f>SUM(E21,G21,I21,K21,M21,O21)</f>
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>412</v>
+        <v>319</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C22" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D22">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>452</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22" t="s">
-        <v>420</v>
+        <f>SUM(E22,G22,I22,K22,M22,O22)</f>
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>186</v>
+        <v>380</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="C23" t="s">
-        <v>455</v>
+        <v>296</v>
       </c>
       <c r="D23">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>494</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23" t="s">
-        <v>494</v>
+        <f>SUM(E23,G23,I23,K23,M23,O23)</f>
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>473</v>
+        <v>305</v>
       </c>
       <c r="B24" t="s">
-        <v>220</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>471</v>
+        <v>296</v>
       </c>
       <c r="D24">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="s">
-        <v>416</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24" t="s">
-        <v>481</v>
+        <f>SUM(E24,G24,I24,K24,M24,O24)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>474</v>
+        <v>306</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>294</v>
       </c>
       <c r="C25" t="s">
-        <v>471</v>
+        <v>296</v>
       </c>
       <c r="D25">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>496</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25" t="s">
-        <v>481</v>
+        <f>SUM(E25,G25,I25,K25,M25,O25)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>378</v>
+        <v>295</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D26">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26" t="s">
-        <v>457</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
+        <f>SUM(E26,G26,I26,K26,M26,O26)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>397</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C27" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="D27">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27" t="s">
-        <v>431</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-      <c r="P27" t="s">
-        <v>464</v>
+        <f>SUM(E27,G27,I27,K27,M27,O27)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>441</v>
+        <v>325</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="D28">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>442</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
-      <c r="P28" t="s">
-        <v>465</v>
+        <f>SUM(E28,G28,I28,K28,M28,O28)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C29" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="D29">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>451</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>451</v>
+        <f>SUM(E29,G29,I29,K29,M29,O29)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>315</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
         <v>294</v>
@@ -8503,19 +8439,13 @@
         <v>296</v>
       </c>
       <c r="D30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>451</v>
+        <f>SUM(E30,G30,I30,K30,M30,O30)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="B31" t="s">
         <v>294</v>
@@ -8524,292 +8454,349 @@
         <v>296</v>
       </c>
       <c r="D31">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>493</v>
+        <f>SUM(E31,G31,I31,K31,M31,O31)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B32" t="s">
         <v>294</v>
       </c>
       <c r="C32" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="D32">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(E32,G32,I32,K32,M32,O32)</f>
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>453</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>451</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
         <v>294</v>
       </c>
       <c r="C33" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="D33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="P33" t="s">
-        <v>457</v>
+        <f>SUM(E33,G33,I33,K33,M33,O33)</f>
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>448</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>468</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>398</v>
+        <v>477</v>
       </c>
       <c r="B34" t="s">
-        <v>294</v>
+        <v>406</v>
       </c>
       <c r="C34" t="s">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="D34">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
-        <v>431</v>
+        <f>SUM(E34,G34,I34,K34,M34,O34)</f>
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>424</v>
+        <v>480</v>
       </c>
       <c r="B35" t="s">
-        <v>294</v>
+        <v>406</v>
       </c>
       <c r="C35" t="s">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="D35">
-        <f t="shared" si="0"/>
+        <f>SUM(E35,G35,I35,K35,M35,O35)</f>
         <v>1</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>425</v>
+        <v>488</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>393</v>
+        <v>479</v>
       </c>
       <c r="B36" t="s">
-        <v>294</v>
+        <v>406</v>
       </c>
       <c r="C36" t="s">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="D36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
-        <v>450</v>
+        <f>SUM(E36,G36,I36,K36,M36,O36)</f>
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="B37" t="s">
-        <v>294</v>
+        <v>406</v>
       </c>
       <c r="C37" t="s">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="D37">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(E37,G37,I37,K37,M37,O37)</f>
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>461</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>461</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>461</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37" t="s">
+        <v>461</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>461</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>380</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C38" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="D38">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
-      <c r="N38" t="s">
-        <v>449</v>
+        <f>SUM(E38,G38,I38,K38,M38,O38)</f>
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>446</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B39" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C39" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="D39">
-        <f t="shared" si="0"/>
+        <f>SUM(E39,G39,I39,K39,M39,O39)</f>
         <v>1</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>477</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s">
-        <v>406</v>
+        <v>274</v>
       </c>
       <c r="C40" t="s">
-        <v>478</v>
+        <v>331</v>
       </c>
       <c r="D40">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
-        <v>482</v>
+        <f>SUM(E40,G40,I40,K40,M40,O40)</f>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>480</v>
+        <v>396</v>
       </c>
       <c r="B41" t="s">
-        <v>406</v>
+        <v>274</v>
       </c>
       <c r="C41" t="s">
-        <v>478</v>
+        <v>331</v>
       </c>
       <c r="D41">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-      <c r="L41" t="s">
-        <v>488</v>
+        <f>SUM(E41,G41,I41,K41,M41,O41)</f>
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="N41" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>479</v>
+        <v>394</v>
       </c>
       <c r="B42" t="s">
-        <v>406</v>
+        <v>274</v>
       </c>
       <c r="C42" t="s">
-        <v>478</v>
+        <v>331</v>
       </c>
       <c r="D42">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42" t="s">
-        <v>482</v>
+        <f>SUM(E42,G42,I42,K42,M42,O42)</f>
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>273</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s">
         <v>274</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="D43">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>416</v>
+        <f>SUM(E43,G43,I43,K43,M43,O43)</f>
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s">
         <v>274</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="D44">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44" t="s">
-        <v>416</v>
+        <f>SUM(E44,G44,I44,K44,M44,O44)</f>
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s">
         <v>274</v>
@@ -8818,22 +8805,19 @@
         <v>331</v>
       </c>
       <c r="D45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
+        <f>SUM(E45,G45,I45,K45,M45,O45)</f>
+        <v>1</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s">
         <v>274</v>
@@ -8842,79 +8826,58 @@
         <v>331</v>
       </c>
       <c r="D46">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46" t="s">
-        <v>431</v>
+        <f>SUM(E46,G46,I46,K46,M46,O46)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s">
         <v>274</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="D47">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K47">
-        <v>1</v>
-      </c>
-      <c r="L47" t="s">
-        <v>443</v>
+        <f>SUM(E47,G47,I47,K47,M47,O47)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s">
         <v>274</v>
       </c>
       <c r="C48" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="L48" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E48,G48,I48,K48,M48,O48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s">
         <v>274</v>
       </c>
       <c r="C49" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="D49">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E49,G49,I49,K49,M49,O49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s">
         <v>274</v>
@@ -8923,19 +8886,13 @@
         <v>331</v>
       </c>
       <c r="D50">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-      <c r="N50" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E50,G50,I50,K50,M50,O50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s">
         <v>274</v>
@@ -8944,19 +8901,13 @@
         <v>331</v>
       </c>
       <c r="D51">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-      <c r="N51" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E51,G51,I51,K51,M51,O51)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>438</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s">
         <v>274</v>
@@ -8965,61 +8916,43 @@
         <v>331</v>
       </c>
       <c r="D52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E52,G52,I52,K52,M52,O52)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>395</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s">
         <v>274</v>
       </c>
       <c r="C53" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D53">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="N53" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E53,G53,I53,K53,M53,O53)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s">
         <v>274</v>
       </c>
       <c r="C54" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D54">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O54">
-        <v>1</v>
-      </c>
-      <c r="P54" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E54,G54,I54,K54,M54,O54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s">
         <v>274</v>
@@ -9028,19 +8961,13 @@
         <v>331</v>
       </c>
       <c r="D55">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O55">
-        <v>1</v>
-      </c>
-      <c r="P55" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.45">
+        <f>SUM(E55,G55,I55,K55,M55,O55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s">
         <v>274</v>
@@ -9049,2852 +8976,2900 @@
         <v>331</v>
       </c>
       <c r="D56">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="P56" t="s">
+        <f>SUM(E56,G56,I56,K56,M56,O56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B57" t="s">
+        <v>274</v>
+      </c>
+      <c r="C57" t="s">
+        <v>331</v>
+      </c>
+      <c r="D57">
+        <f>SUM(E57,G57,I57,K57,M57,O57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B58" t="s">
+        <v>274</v>
+      </c>
+      <c r="C58" t="s">
+        <v>331</v>
+      </c>
+      <c r="D58">
+        <f>SUM(E58,G58,I58,K58,M58,O58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B59" t="s">
+        <v>274</v>
+      </c>
+      <c r="C59" t="s">
+        <v>331</v>
+      </c>
+      <c r="D59">
+        <f>SUM(E59,G59,I59,K59,M59,O59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B60" t="s">
+        <v>274</v>
+      </c>
+      <c r="C60" t="s">
+        <v>331</v>
+      </c>
+      <c r="D60">
+        <f>SUM(E60,G60,I60,K60,M60,O60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A61" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B61" t="s">
+        <v>274</v>
+      </c>
+      <c r="C61" t="s">
+        <v>331</v>
+      </c>
+      <c r="D61">
+        <f>SUM(E61,G61,I61,K61,M61,O61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B62" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62">
+        <f>SUM(E62,G62,I62,K62,M62,O62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A63" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B63" t="s">
+        <v>274</v>
+      </c>
+      <c r="C63" t="s">
+        <v>331</v>
+      </c>
+      <c r="D63">
+        <f>SUM(E63,G63,I63,K63,M63,O63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B64" t="s">
+        <v>274</v>
+      </c>
+      <c r="C64" t="s">
+        <v>275</v>
+      </c>
+      <c r="D64">
+        <f>SUM(E64,G64,I64,K64,M64,O64)</f>
+        <v>2</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>484</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A65" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B65" t="s">
+        <v>274</v>
+      </c>
+      <c r="C65" t="s">
+        <v>275</v>
+      </c>
+      <c r="D65">
+        <f>SUM(E65,G65,I65,K65,M65,O65)</f>
+        <v>2</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A57" s="2" t="s">
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A66" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B66" t="s">
+        <v>274</v>
+      </c>
+      <c r="C66" t="s">
+        <v>275</v>
+      </c>
+      <c r="D66">
+        <f>SUM(E66,G66,I66,K66,M66,O66)</f>
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A67" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B67" t="s">
+        <v>274</v>
+      </c>
+      <c r="C67" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67">
+        <f>SUM(E67,G67,I67,K67,M67,O67)</f>
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>454</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A68" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B68" t="s">
+        <v>274</v>
+      </c>
+      <c r="C68" t="s">
+        <v>275</v>
+      </c>
+      <c r="D68">
+        <f>SUM(E68,G68,I68,K68,M68,O68)</f>
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A69" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" t="s">
+        <v>274</v>
+      </c>
+      <c r="C69" t="s">
+        <v>275</v>
+      </c>
+      <c r="D69">
+        <f>SUM(E69,G69,I69,K69,M69,O69)</f>
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A70" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B70" t="s">
+        <v>274</v>
+      </c>
+      <c r="C70" t="s">
+        <v>275</v>
+      </c>
+      <c r="D70">
+        <f>SUM(E70,G70,I70,K70,M70,O70)</f>
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A71" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" t="s">
+        <v>275</v>
+      </c>
+      <c r="D71">
+        <f>SUM(E71,G71,I71,K71,M71,O71)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A72" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B72" t="s">
+        <v>274</v>
+      </c>
+      <c r="C72" t="s">
+        <v>275</v>
+      </c>
+      <c r="D72">
+        <f>SUM(E72,G72,I72,K72,M72,O72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A73" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B73" t="s">
+        <v>274</v>
+      </c>
+      <c r="C73" t="s">
+        <v>275</v>
+      </c>
+      <c r="D73">
+        <f>SUM(E73,G73,I73,K73,M73,O73)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A74" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B74" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" t="s">
+        <v>275</v>
+      </c>
+      <c r="D74">
+        <f>SUM(E74,G74,I74,K74,M74,O74)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B75" t="s">
+        <v>274</v>
+      </c>
+      <c r="C75" t="s">
+        <v>275</v>
+      </c>
+      <c r="D75">
+        <f>SUM(E75,G75,I75,K75,M75,O75)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A76" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" t="s">
+        <v>274</v>
+      </c>
+      <c r="C76" t="s">
+        <v>275</v>
+      </c>
+      <c r="D76">
+        <f>SUM(E76,G76,I76,K76,M76,O76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A77" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B77" t="s">
+        <v>274</v>
+      </c>
+      <c r="C77" t="s">
+        <v>275</v>
+      </c>
+      <c r="D77">
+        <f>SUM(E77,G77,I77,K77,M77,O77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A78" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B78" t="s">
+        <v>274</v>
+      </c>
+      <c r="C78" t="s">
+        <v>275</v>
+      </c>
+      <c r="D78">
+        <f>SUM(E78,G78,I78,K78,M78,O78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A79" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B79" t="s">
+        <v>274</v>
+      </c>
+      <c r="C79" t="s">
+        <v>335</v>
+      </c>
+      <c r="D79">
+        <f>SUM(E79,G79,I79,K79,M79,O79)</f>
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A80" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B80" t="s">
+        <v>274</v>
+      </c>
+      <c r="C80" t="s">
+        <v>335</v>
+      </c>
+      <c r="D80">
+        <f>SUM(E80,G80,I80,K80,M80,O80)</f>
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A81" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B81" t="s">
+        <v>274</v>
+      </c>
+      <c r="C81" t="s">
+        <v>335</v>
+      </c>
+      <c r="D81">
+        <f>SUM(E81,G81,I81,K81,M81,O81)</f>
+        <v>1</v>
+      </c>
+      <c r="O81">
+        <v>1</v>
+      </c>
+      <c r="P81" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A82" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B82" t="s">
+        <v>274</v>
+      </c>
+      <c r="C82" t="s">
+        <v>335</v>
+      </c>
+      <c r="D82">
+        <f>SUM(E82,G82,I82,K82,M82,O82)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A83" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B83" t="s">
+        <v>274</v>
+      </c>
+      <c r="C83" t="s">
+        <v>335</v>
+      </c>
+      <c r="D83">
+        <f>SUM(E83,G83,I83,K83,M83,O83)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A84" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B84" t="s">
+        <v>274</v>
+      </c>
+      <c r="C84" t="s">
+        <v>335</v>
+      </c>
+      <c r="D84">
+        <f>SUM(E84,G84,I84,K84,M84,O84)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A85" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B85" t="s">
+        <v>274</v>
+      </c>
+      <c r="C85" t="s">
+        <v>335</v>
+      </c>
+      <c r="D85">
+        <f>SUM(E85,G85,I85,K85,M85,O85)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A86" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B86" t="s">
+        <v>274</v>
+      </c>
+      <c r="C86" t="s">
+        <v>335</v>
+      </c>
+      <c r="D86">
+        <f>SUM(E86,G86,I86,K86,M86,O86)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A87" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B87" t="s">
+        <v>274</v>
+      </c>
+      <c r="C87" t="s">
+        <v>335</v>
+      </c>
+      <c r="D87">
+        <f>SUM(E87,G87,I87,K87,M87,O87)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A88" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B88" t="s">
+        <v>274</v>
+      </c>
+      <c r="C88" t="s">
+        <v>335</v>
+      </c>
+      <c r="D88">
+        <f>SUM(E88,G88,I88,K88,M88,O88)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A89" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B89" t="s">
+        <v>274</v>
+      </c>
+      <c r="C89" t="s">
+        <v>335</v>
+      </c>
+      <c r="D89">
+        <f>SUM(E89,G89,I89,K89,M89,O89)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A90" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B90" t="s">
+        <v>274</v>
+      </c>
+      <c r="C90" t="s">
+        <v>335</v>
+      </c>
+      <c r="D90">
+        <f>SUM(E90,G90,I90,K90,M90,O90)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A91" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B91" t="s">
+        <v>274</v>
+      </c>
+      <c r="C91" t="s">
+        <v>335</v>
+      </c>
+      <c r="D91">
+        <f>SUM(E91,G91,I91,K91,M91,O91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A92" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B92" t="s">
+        <v>274</v>
+      </c>
+      <c r="C92" t="s">
+        <v>335</v>
+      </c>
+      <c r="D92">
+        <f>SUM(E92,G92,I92,K92,M92,O92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A93" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B93" t="s">
+        <v>274</v>
+      </c>
+      <c r="C93" t="s">
+        <v>335</v>
+      </c>
+      <c r="D93">
+        <f>SUM(E93,G93,I93,K93,M93,O93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A94" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B94" t="s">
+        <v>274</v>
+      </c>
+      <c r="C94" t="s">
+        <v>335</v>
+      </c>
+      <c r="D94">
+        <f>SUM(E94,G94,I94,K94,M94,O94)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A95" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B95" t="s">
+        <v>274</v>
+      </c>
+      <c r="C95" t="s">
+        <v>335</v>
+      </c>
+      <c r="D95">
+        <f>SUM(E95,G95,I95,K95,M95,O95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A96" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B96" t="s">
+        <v>274</v>
+      </c>
+      <c r="C96" t="s">
+        <v>335</v>
+      </c>
+      <c r="D96">
+        <f>SUM(E96,G96,I96,K96,M96,O96)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A97" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B97" t="s">
+        <v>274</v>
+      </c>
+      <c r="C97" t="s">
+        <v>335</v>
+      </c>
+      <c r="D97">
+        <f>SUM(E97,G97,I97,K97,M97,O97)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A98" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B98" t="s">
+        <v>274</v>
+      </c>
+      <c r="C98" t="s">
+        <v>335</v>
+      </c>
+      <c r="D98">
+        <f>SUM(E98,G98,I98,K98,M98,O98)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A99" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B99" t="s">
+        <v>274</v>
+      </c>
+      <c r="C99" t="s">
+        <v>335</v>
+      </c>
+      <c r="D99">
+        <f>SUM(E99,G99,I99,K99,M99,O99)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A100" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B100" t="s">
+        <v>274</v>
+      </c>
+      <c r="C100" t="s">
+        <v>335</v>
+      </c>
+      <c r="D100">
+        <f>SUM(E100,G100,I100,K100,M100,O100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A101" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B101" t="s">
+        <v>274</v>
+      </c>
+      <c r="C101" t="s">
+        <v>335</v>
+      </c>
+      <c r="D101">
+        <f>SUM(E101,G101,I101,K101,M101,O101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A102" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B102" t="s">
+        <v>274</v>
+      </c>
+      <c r="C102" t="s">
+        <v>335</v>
+      </c>
+      <c r="D102">
+        <f>SUM(E102,G102,I102,K102,M102,O102)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A103" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B103" t="s">
+        <v>274</v>
+      </c>
+      <c r="C103" t="s">
+        <v>335</v>
+      </c>
+      <c r="D103">
+        <f>SUM(E103,G103,I103,K103,M103,O103)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A104" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" t="s">
+        <v>179</v>
+      </c>
+      <c r="C104" t="s">
+        <v>238</v>
+      </c>
+      <c r="D104">
+        <f>SUM(E104,G104,I104,K104,M104,O104)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A105" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
+        <v>179</v>
+      </c>
+      <c r="C105" t="s">
+        <v>238</v>
+      </c>
+      <c r="D105">
+        <f>SUM(E105,G105,I105,K105,M105,O105)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A106" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" t="s">
+        <v>179</v>
+      </c>
+      <c r="C106" t="s">
+        <v>238</v>
+      </c>
+      <c r="D106">
+        <f>SUM(E106,G106,I106,K106,M106,O106)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A107" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" t="s">
+        <v>179</v>
+      </c>
+      <c r="C107" t="s">
+        <v>238</v>
+      </c>
+      <c r="D107">
+        <f>SUM(E107,G107,I107,K107,M107,O107)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A108" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B108" t="s">
+        <v>179</v>
+      </c>
+      <c r="C108" t="s">
+        <v>238</v>
+      </c>
+      <c r="D108">
+        <f>SUM(E108,G108,I108,K108,M108,O108)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A109" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B109" t="s">
+        <v>179</v>
+      </c>
+      <c r="C109" t="s">
+        <v>238</v>
+      </c>
+      <c r="D109">
+        <f>SUM(E109,G109,I109,K109,M109,O109)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A110" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
+        <v>179</v>
+      </c>
+      <c r="C110" t="s">
+        <v>329</v>
+      </c>
+      <c r="D110">
+        <f>SUM(E110,G110,I110,K110,M110,O110)</f>
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A111" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
+        <v>179</v>
+      </c>
+      <c r="C111" t="s">
+        <v>329</v>
+      </c>
+      <c r="D111">
+        <f>SUM(E111,G111,I111,K111,M111,O111)</f>
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A112" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B112" t="s">
+        <v>179</v>
+      </c>
+      <c r="C112" t="s">
+        <v>329</v>
+      </c>
+      <c r="D112">
+        <f>SUM(E112,G112,I112,K112,M112,O112)</f>
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A113" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B113" t="s">
         <v>179</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C113" t="s">
         <v>329</v>
       </c>
-      <c r="D57">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
-      <c r="J57" t="s">
+      <c r="D113">
+        <f>SUM(E113,G113,I113,K113,M113,O113)</f>
+        <v>1</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A58" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B58" t="s">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A114" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B114" t="s">
         <v>179</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C114" t="s">
         <v>329</v>
       </c>
-      <c r="D58">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="L58" t="s">
+      <c r="D114">
+        <f>SUM(E114,G114,I114,K114,M114,O114)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A115" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B115" t="s">
+        <v>179</v>
+      </c>
+      <c r="C115" t="s">
+        <v>329</v>
+      </c>
+      <c r="D115">
+        <f>SUM(E115,G115,I115,K115,M115,O115)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A116" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B116" t="s">
+        <v>179</v>
+      </c>
+      <c r="C116" t="s">
+        <v>329</v>
+      </c>
+      <c r="D116">
+        <f>SUM(E116,G116,I116,K116,M116,O116)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A117" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B117" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" t="s">
+        <v>329</v>
+      </c>
+      <c r="D117">
+        <f>SUM(E117,G117,I117,K117,M117,O117)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A118" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B118" t="s">
+        <v>179</v>
+      </c>
+      <c r="C118" t="s">
+        <v>329</v>
+      </c>
+      <c r="D118">
+        <f>SUM(E118,G118,I118,K118,M118,O118)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A119" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B119" t="s">
+        <v>179</v>
+      </c>
+      <c r="C119" t="s">
+        <v>329</v>
+      </c>
+      <c r="D119">
+        <f>SUM(E119,G119,I119,K119,M119,O119)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A120" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B120" t="s">
+        <v>179</v>
+      </c>
+      <c r="C120" t="s">
+        <v>329</v>
+      </c>
+      <c r="D120">
+        <f>SUM(E120,G120,I120,K120,M120,O120)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A121" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B121" t="s">
+        <v>179</v>
+      </c>
+      <c r="C121" t="s">
+        <v>329</v>
+      </c>
+      <c r="D121">
+        <f>SUM(E121,G121,I121,K121,M121,O121)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A122" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B122" t="s">
+        <v>179</v>
+      </c>
+      <c r="C122" t="s">
+        <v>329</v>
+      </c>
+      <c r="D122">
+        <f>SUM(E122,G122,I122,K122,M122,O122)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A123" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B123" t="s">
+        <v>179</v>
+      </c>
+      <c r="C123" t="s">
+        <v>329</v>
+      </c>
+      <c r="D123">
+        <f>SUM(E123,G123,I123,K123,M123,O123)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A124" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B124" t="s">
+        <v>179</v>
+      </c>
+      <c r="C124" t="s">
+        <v>237</v>
+      </c>
+      <c r="D124">
+        <f>SUM(E124,G124,I124,K124,M124,O124)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A125" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B125" t="s">
+        <v>179</v>
+      </c>
+      <c r="C125" t="s">
+        <v>237</v>
+      </c>
+      <c r="D125">
+        <f>SUM(E125,G125,I125,K125,M125,O125)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A126" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B126" t="s">
+        <v>179</v>
+      </c>
+      <c r="C126" t="s">
+        <v>237</v>
+      </c>
+      <c r="D126">
+        <f>SUM(E126,G126,I126,K126,M126,O126)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A127" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B127" t="s">
+        <v>179</v>
+      </c>
+      <c r="C127" t="s">
+        <v>237</v>
+      </c>
+      <c r="D127">
+        <f>SUM(E127,G127,I127,K127,M127,O127)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A128" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B128" t="s">
+        <v>179</v>
+      </c>
+      <c r="C128" t="s">
+        <v>237</v>
+      </c>
+      <c r="D128">
+        <f>SUM(E128,G128,I128,K128,M128,O128)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A129" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B129" t="s">
+        <v>179</v>
+      </c>
+      <c r="C129" t="s">
+        <v>237</v>
+      </c>
+      <c r="D129">
+        <f>SUM(E129,G129,I129,K129,M129,O129)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A130" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B130" t="s">
+        <v>179</v>
+      </c>
+      <c r="C130" t="s">
+        <v>455</v>
+      </c>
+      <c r="D130">
+        <f>SUM(E130,G130,I130,K130,M130,O130)</f>
+        <v>3</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130" t="s">
+        <v>494</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130" t="s">
+        <v>494</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A59" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A131" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B131" t="s">
         <v>179</v>
       </c>
-      <c r="C59" t="s">
-        <v>329</v>
-      </c>
-      <c r="D59">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
-      </c>
-      <c r="L59" t="s">
+      <c r="C131" t="s">
+        <v>455</v>
+      </c>
+      <c r="D131">
+        <f>SUM(E131,G131,I131,K131,M131,O131)</f>
+        <v>2</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131" t="s">
+        <v>494</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A132" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B132" t="s">
+        <v>179</v>
+      </c>
+      <c r="C132" t="s">
+        <v>455</v>
+      </c>
+      <c r="D132">
+        <f>SUM(E132,G132,I132,K132,M132,O132)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A133" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B133" t="s">
+        <v>179</v>
+      </c>
+      <c r="C133" t="s">
+        <v>455</v>
+      </c>
+      <c r="D133">
+        <f>SUM(E133,G133,I133,K133,M133,O133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A134" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B134" t="s">
+        <v>179</v>
+      </c>
+      <c r="C134" t="s">
+        <v>455</v>
+      </c>
+      <c r="D134">
+        <f>SUM(E134,G134,I134,K134,M134,O134)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A135" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B135" t="s">
+        <v>179</v>
+      </c>
+      <c r="C135" t="s">
+        <v>455</v>
+      </c>
+      <c r="D135">
+        <f>SUM(E135,G135,I135,K135,M135,O135)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A136" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B136" t="s">
+        <v>179</v>
+      </c>
+      <c r="C136" t="s">
+        <v>455</v>
+      </c>
+      <c r="D136">
+        <f>SUM(E136,G136,I136,K136,M136,O136)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A137" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B137" t="s">
+        <v>179</v>
+      </c>
+      <c r="C137" t="s">
+        <v>455</v>
+      </c>
+      <c r="D137">
+        <f>SUM(E137,G137,I137,K137,M137,O137)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A138" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B138" t="s">
+        <v>179</v>
+      </c>
+      <c r="C138" t="s">
+        <v>455</v>
+      </c>
+      <c r="D138">
+        <f>SUM(E138,G138,I138,K138,M138,O138)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A139" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B139" t="s">
+        <v>179</v>
+      </c>
+      <c r="C139" t="s">
+        <v>455</v>
+      </c>
+      <c r="D139">
+        <f>SUM(E139,G139,I139,K139,M139,O139)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A140" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B140" t="s">
+        <v>179</v>
+      </c>
+      <c r="C140" t="s">
+        <v>455</v>
+      </c>
+      <c r="D140">
+        <f>SUM(E140,G140,I140,K140,M140,O140)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A141" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B141" t="s">
+        <v>179</v>
+      </c>
+      <c r="C141" t="s">
+        <v>455</v>
+      </c>
+      <c r="D141">
+        <f>SUM(E141,G141,I141,K141,M141,O141)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A142" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B142" t="s">
+        <v>179</v>
+      </c>
+      <c r="C142" t="s">
+        <v>455</v>
+      </c>
+      <c r="D142">
+        <f>SUM(E142,G142,I142,K142,M142,O142)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A143" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B143" t="s">
+        <v>233</v>
+      </c>
+      <c r="C143" t="s">
+        <v>243</v>
+      </c>
+      <c r="D143">
+        <f>SUM(E143,G143,I143,K143,M143,O143)</f>
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A144" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B144" t="s">
+        <v>233</v>
+      </c>
+      <c r="C144" t="s">
+        <v>243</v>
+      </c>
+      <c r="D144">
+        <f>SUM(E144,G144,I144,K144,M144,O144)</f>
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+      <c r="H144" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A145" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B145" t="s">
+        <v>233</v>
+      </c>
+      <c r="C145" t="s">
+        <v>243</v>
+      </c>
+      <c r="D145">
+        <f>SUM(E145,G145,I145,K145,M145,O145)</f>
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A146" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B146" t="s">
+        <v>233</v>
+      </c>
+      <c r="C146" t="s">
+        <v>245</v>
+      </c>
+      <c r="D146">
+        <f>SUM(E146,G146,I146,K146,M146,O146)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A147" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B147" t="s">
+        <v>233</v>
+      </c>
+      <c r="C147" t="s">
+        <v>243</v>
+      </c>
+      <c r="D147">
+        <f>SUM(E147,G147,I147,K147,M147,O147)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A148" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B148" t="s">
+        <v>233</v>
+      </c>
+      <c r="C148" t="s">
+        <v>243</v>
+      </c>
+      <c r="D148">
+        <f>SUM(E148,G148,I148,K148,M148,O148)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A149" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
+        <v>233</v>
+      </c>
+      <c r="C149" t="s">
+        <v>243</v>
+      </c>
+      <c r="D149">
+        <f>SUM(E149,G149,I149,K149,M149,O149)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A150" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B150" t="s">
+        <v>233</v>
+      </c>
+      <c r="C150" t="s">
+        <v>243</v>
+      </c>
+      <c r="D150">
+        <f>SUM(E150,G150,I150,K150,M150,O150)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A151" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B151" t="s">
+        <v>233</v>
+      </c>
+      <c r="C151" t="s">
+        <v>243</v>
+      </c>
+      <c r="D151">
+        <f>SUM(E151,G151,I151,K151,M151,O151)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A152" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B152" t="s">
+        <v>233</v>
+      </c>
+      <c r="C152" t="s">
+        <v>243</v>
+      </c>
+      <c r="D152">
+        <f>SUM(E152,G152,I152,K152,M152,O152)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A153" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" t="s">
+        <v>233</v>
+      </c>
+      <c r="C153" t="s">
+        <v>243</v>
+      </c>
+      <c r="D153">
+        <f>SUM(E153,G153,I153,K153,M153,O153)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A154" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B154" t="s">
+        <v>233</v>
+      </c>
+      <c r="C154" t="s">
+        <v>243</v>
+      </c>
+      <c r="D154">
+        <f>SUM(E154,G154,I154,K154,M154,O154)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A155" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B155" t="s">
+        <v>253</v>
+      </c>
+      <c r="C155" t="s">
+        <v>243</v>
+      </c>
+      <c r="D155">
+        <f>SUM(E155,G155,I155,K155,M155,O155)</f>
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="F155" t="s">
+        <v>461</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155" t="s">
+        <v>461</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155" t="s">
+        <v>461</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155" t="s">
+        <v>461</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155" t="s">
+        <v>461</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A156" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B156" t="s">
+        <v>253</v>
+      </c>
+      <c r="C156" t="s">
+        <v>243</v>
+      </c>
+      <c r="D156">
+        <f>SUM(E156,G156,I156,K156,M156,O156)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A157" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B157" t="s">
+        <v>253</v>
+      </c>
+      <c r="C157" t="s">
+        <v>243</v>
+      </c>
+      <c r="D157">
+        <f>SUM(E157,G157,I157,K157,M157,O157)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A158" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B158" t="s">
+        <v>253</v>
+      </c>
+      <c r="C158" t="s">
+        <v>243</v>
+      </c>
+      <c r="D158">
+        <f>SUM(E158,G158,I158,K158,M158,O158)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A159" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B159" t="s">
+        <v>253</v>
+      </c>
+      <c r="C159" t="s">
+        <v>243</v>
+      </c>
+      <c r="D159">
+        <f>SUM(E159,G159,I159,K159,M159,O159)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A160" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B160" t="s">
+        <v>253</v>
+      </c>
+      <c r="C160" t="s">
+        <v>243</v>
+      </c>
+      <c r="D160">
+        <f>SUM(E160,G160,I160,K160,M160,O160)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A161" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B161" t="s">
+        <v>253</v>
+      </c>
+      <c r="C161" t="s">
+        <v>243</v>
+      </c>
+      <c r="D161">
+        <f>SUM(E161,G161,I161,K161,M161,O161)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A162" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B162" t="s">
+        <v>253</v>
+      </c>
+      <c r="C162" t="s">
+        <v>243</v>
+      </c>
+      <c r="D162">
+        <f>SUM(E162,G162,I162,K162,M162,O162)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A163" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B163" t="s">
+        <v>220</v>
+      </c>
+      <c r="C163" t="s">
+        <v>240</v>
+      </c>
+      <c r="D163">
+        <f>SUM(E163,G163,I163,K163,M163,O163)</f>
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A164" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B164" t="s">
+        <v>220</v>
+      </c>
+      <c r="C164" t="s">
+        <v>239</v>
+      </c>
+      <c r="D164">
+        <f>SUM(E164,G164,I164,K164,M164,O164)</f>
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A165" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B165" t="s">
+        <v>220</v>
+      </c>
+      <c r="C165" t="s">
+        <v>241</v>
+      </c>
+      <c r="D165">
+        <f>SUM(E165,G165,I165,K165,M165,O165)</f>
+        <v>3</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+      <c r="F165" t="s">
+        <v>446</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165" t="s">
+        <v>445</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A166" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B166" t="s">
+        <v>220</v>
+      </c>
+      <c r="C166" t="s">
+        <v>241</v>
+      </c>
+      <c r="D166">
+        <f>SUM(E166,G166,I166,K166,M166,O166)</f>
+        <v>1</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A167" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B167" t="s">
+        <v>220</v>
+      </c>
+      <c r="C167" t="s">
+        <v>471</v>
+      </c>
+      <c r="D167">
+        <f>SUM(E167,G167,I167,K167,M167,O167)</f>
+        <v>2</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167" t="s">
+        <v>416</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A168" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B168" t="s">
+        <v>220</v>
+      </c>
+      <c r="C168" t="s">
+        <v>471</v>
+      </c>
+      <c r="D168">
+        <f>SUM(E168,G168,I168,K168,M168,O168)</f>
+        <v>2</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168" t="s">
+        <v>496</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A169" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B169" t="s">
+        <v>220</v>
+      </c>
+      <c r="C169" t="s">
+        <v>471</v>
+      </c>
+      <c r="D169">
+        <f>SUM(E169,G169,I169,K169,M169,O169)</f>
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A170" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B170" t="s">
+        <v>220</v>
+      </c>
+      <c r="C170" t="s">
+        <v>471</v>
+      </c>
+      <c r="D170">
+        <f>SUM(E170,G170,I170,K170,M170,O170)</f>
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A171" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B171" t="s">
+        <v>220</v>
+      </c>
+      <c r="C171" t="s">
+        <v>471</v>
+      </c>
+      <c r="D171">
+        <f>SUM(E171,G171,I171,K171,M171,O171)</f>
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A172" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B172" t="s">
+        <v>220</v>
+      </c>
+      <c r="C172" t="s">
+        <v>471</v>
+      </c>
+      <c r="D172">
+        <f>SUM(E172,G172,I172,K172,M172,O172)</f>
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A173" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B173" t="s">
+        <v>220</v>
+      </c>
+      <c r="C173" t="s">
+        <v>242</v>
+      </c>
+      <c r="D173">
+        <f>SUM(E173,G173,I173,K173,M173,O173)</f>
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173" t="s">
+        <v>461</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173" t="s">
+        <v>461</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173" t="s">
+        <v>461</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173" t="s">
+        <v>444</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173" t="s">
+        <v>461</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A174" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B174" t="s">
+        <v>220</v>
+      </c>
+      <c r="C174" t="s">
+        <v>242</v>
+      </c>
+      <c r="D174">
+        <f>SUM(E174,G174,I174,K174,M174,O174)</f>
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174" t="s">
+        <v>461</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174" t="s">
+        <v>461</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174" t="s">
+        <v>461</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174" t="s">
+        <v>444</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174" t="s">
+        <v>461</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A175" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B175" t="s">
+        <v>220</v>
+      </c>
+      <c r="C175" t="s">
+        <v>242</v>
+      </c>
+      <c r="D175">
+        <f>SUM(E175,G175,I175,K175,M175,O175)</f>
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175" t="s">
+        <v>461</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175" t="s">
+        <v>461</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175" t="s">
+        <v>461</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175" t="s">
+        <v>461</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175" t="s">
+        <v>461</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A176" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B176" t="s">
+        <v>262</v>
+      </c>
+      <c r="C176" t="s">
+        <v>243</v>
+      </c>
+      <c r="D176">
+        <f>SUM(E176,G176,I176,K176,M176,O176)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A177" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B177" t="s">
+        <v>262</v>
+      </c>
+      <c r="C177" t="s">
+        <v>243</v>
+      </c>
+      <c r="D177">
+        <f>SUM(E177,G177,I177,K177,M177,O177)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A178" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B178" t="s">
+        <v>262</v>
+      </c>
+      <c r="C178" t="s">
+        <v>243</v>
+      </c>
+      <c r="D178">
+        <f>SUM(E178,G178,I178,K178,M178,O178)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A179" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B179" t="s">
+        <v>266</v>
+      </c>
+      <c r="C179" t="s">
+        <v>291</v>
+      </c>
+      <c r="D179">
+        <f>SUM(E179,G179,I179,K179,M179,O179)</f>
+        <v>3</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179" t="s">
+        <v>446</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>445</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A180" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B180" t="s">
+        <v>266</v>
+      </c>
+      <c r="C180" t="s">
+        <v>291</v>
+      </c>
+      <c r="D180">
+        <f>SUM(E180,G180,I180,K180,M180,O180)</f>
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A60" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B60" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" t="s">
-        <v>329</v>
-      </c>
-      <c r="D60">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A61" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B61" t="s">
-        <v>233</v>
-      </c>
-      <c r="C61" t="s">
-        <v>243</v>
-      </c>
-      <c r="D61">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A62" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B62" t="s">
-        <v>233</v>
-      </c>
-      <c r="C62" t="s">
-        <v>243</v>
-      </c>
-      <c r="D62">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A63" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B63" t="s">
-        <v>233</v>
-      </c>
-      <c r="C63" t="s">
-        <v>243</v>
-      </c>
-      <c r="D63">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K63">
-        <v>1</v>
-      </c>
-      <c r="L63" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A64" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B64" t="s">
-        <v>220</v>
-      </c>
-      <c r="C64" t="s">
-        <v>241</v>
-      </c>
-      <c r="D64">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A65" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B65" t="s">
-        <v>220</v>
-      </c>
-      <c r="C65" t="s">
-        <v>471</v>
-      </c>
-      <c r="D65">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>1</v>
-      </c>
-      <c r="L65" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A66" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B66" t="s">
-        <v>220</v>
-      </c>
-      <c r="C66" t="s">
-        <v>239</v>
-      </c>
-      <c r="D66">
-        <f t="shared" ref="D66:D129" si="1">SUM(E66,G66,I66,K66,M66,O66)</f>
-        <v>1</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A67" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B67" t="s">
-        <v>220</v>
-      </c>
-      <c r="C67" t="s">
-        <v>471</v>
-      </c>
-      <c r="D67">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K67">
-        <v>1</v>
-      </c>
-      <c r="L67" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A68" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B68" t="s">
-        <v>220</v>
-      </c>
-      <c r="C68" t="s">
-        <v>240</v>
-      </c>
-      <c r="D68">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A69" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B69" t="s">
-        <v>220</v>
-      </c>
-      <c r="C69" t="s">
-        <v>471</v>
-      </c>
-      <c r="D69">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K69">
-        <v>1</v>
-      </c>
-      <c r="L69" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A70" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B70" t="s">
-        <v>220</v>
-      </c>
-      <c r="C70" t="s">
-        <v>471</v>
-      </c>
-      <c r="D70">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K70">
-        <v>1</v>
-      </c>
-      <c r="L70" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A71" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B71" t="s">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A181" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B181" t="s">
         <v>266</v>
       </c>
-      <c r="C71" t="s">
-        <v>287</v>
-      </c>
-      <c r="D71">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G71">
-        <v>1</v>
-      </c>
-      <c r="H71" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A72" s="2" t="s">
+      <c r="C181" t="s">
+        <v>291</v>
+      </c>
+      <c r="D181">
+        <f>SUM(E181,G181,I181,K181,M181,O181)</f>
+        <v>3</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181" t="s">
+        <v>493</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>493</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A182" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B182" t="s">
+        <v>266</v>
+      </c>
+      <c r="C182" t="s">
+        <v>291</v>
+      </c>
+      <c r="D182">
+        <f>SUM(E182,G182,I182,K182,M182,O182)</f>
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182" t="s">
+        <v>457</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A183" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B183" t="s">
+        <v>266</v>
+      </c>
+      <c r="C183" t="s">
+        <v>291</v>
+      </c>
+      <c r="D183">
+        <f>SUM(E183,G183,I183,K183,M183,O183)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A184" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B184" t="s">
+        <v>266</v>
+      </c>
+      <c r="C184" t="s">
+        <v>291</v>
+      </c>
+      <c r="D184">
+        <f>SUM(E184,G184,I184,K184,M184,O184)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A185" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B185" t="s">
+        <v>266</v>
+      </c>
+      <c r="C185" t="s">
+        <v>291</v>
+      </c>
+      <c r="D185">
+        <f>SUM(E185,G185,I185,K185,M185,O185)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A186" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B186" t="s">
         <v>266</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C186" t="s">
         <v>311</v>
       </c>
-      <c r="D72">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
-      </c>
-      <c r="L72" t="s">
+      <c r="D186">
+        <f>SUM(E186,G186,I186,K186,M186,O186)</f>
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A73" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A187" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B187" t="s">
         <v>266</v>
       </c>
-      <c r="C73" t="s">
-        <v>268</v>
-      </c>
-      <c r="D73">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="O73">
-        <v>1</v>
-      </c>
-      <c r="P73" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A74" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="C187" t="s">
+        <v>311</v>
+      </c>
+      <c r="D187">
+        <f>SUM(E187,G187,I187,K187,M187,O187)</f>
+        <v>1</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A188" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B188" t="s">
         <v>266</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C188" t="s">
         <v>311</v>
       </c>
-      <c r="D74">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K74">
-        <v>1</v>
-      </c>
-      <c r="L74" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A75" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="D188">
+        <f>SUM(E188,G188,I188,K188,M188,O188)</f>
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A189" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B189" t="s">
         <v>266</v>
       </c>
-      <c r="C75" t="s">
-        <v>268</v>
-      </c>
-      <c r="D75">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K75">
-        <v>1</v>
-      </c>
-      <c r="L75" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A76" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="C189" t="s">
+        <v>311</v>
+      </c>
+      <c r="D189">
+        <f>SUM(E189,G189,I189,K189,M189,O189)</f>
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A190" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B190" t="s">
         <v>266</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C190" t="s">
         <v>311</v>
       </c>
-      <c r="D76">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K76">
-        <v>1</v>
-      </c>
-      <c r="L76" t="s">
+      <c r="D190">
+        <f>SUM(E190,G190,I190,K190,M190,O190)</f>
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A77" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B77" t="s">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A191" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B191" t="s">
         <v>266</v>
       </c>
-      <c r="C77" t="s">
-        <v>287</v>
-      </c>
-      <c r="D77">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K77">
-        <v>1</v>
-      </c>
-      <c r="L77" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A78" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="C191" t="s">
+        <v>311</v>
+      </c>
+      <c r="D191">
+        <f>SUM(E191,G191,I191,K191,M191,O191)</f>
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A192" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B192" t="s">
         <v>266</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C192" t="s">
         <v>311</v>
       </c>
-      <c r="D78">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K78">
-        <v>1</v>
-      </c>
-      <c r="L78" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B79" t="s">
-        <v>266</v>
-      </c>
-      <c r="C79" t="s">
-        <v>268</v>
-      </c>
-      <c r="D79">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K79">
-        <v>1</v>
-      </c>
-      <c r="L79" t="s">
+      <c r="D192">
+        <f>SUM(E192,G192,I192,K192,M192,O192)</f>
+        <v>1</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192" t="s">
         <v>490</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A80" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B80" t="s">
-        <v>266</v>
-      </c>
-      <c r="C80" t="s">
-        <v>311</v>
-      </c>
-      <c r="D80">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K80">
-        <v>1</v>
-      </c>
-      <c r="L80" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A81" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B81" t="s">
-        <v>266</v>
-      </c>
-      <c r="C81" t="s">
-        <v>311</v>
-      </c>
-      <c r="D81">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-      <c r="N81" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A82" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B82" t="s">
-        <v>266</v>
-      </c>
-      <c r="C82" t="s">
-        <v>311</v>
-      </c>
-      <c r="D82">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M82">
-        <v>1</v>
-      </c>
-      <c r="N82" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A83" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B83" t="s">
-        <v>266</v>
-      </c>
-      <c r="C83" t="s">
-        <v>291</v>
-      </c>
-      <c r="D83">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K83">
-        <v>1</v>
-      </c>
-      <c r="L83" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A84" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B84" t="s">
-        <v>266</v>
-      </c>
-      <c r="C84" t="s">
-        <v>287</v>
-      </c>
-      <c r="D84">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E84">
-        <v>1</v>
-      </c>
-      <c r="F84" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A85" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="B85" t="s">
-        <v>266</v>
-      </c>
-      <c r="C85" t="s">
-        <v>311</v>
-      </c>
-      <c r="D85">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K85">
-        <v>1</v>
-      </c>
-      <c r="L85" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A86" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B86" t="s">
-        <v>266</v>
-      </c>
-      <c r="C86" t="s">
-        <v>268</v>
-      </c>
-      <c r="D86">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A87" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B87" t="s">
-        <v>266</v>
-      </c>
-      <c r="C87" t="s">
-        <v>311</v>
-      </c>
-      <c r="D87">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
-      </c>
-      <c r="L87" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A88" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B88" t="s">
-        <v>266</v>
-      </c>
-      <c r="C88" t="s">
-        <v>287</v>
-      </c>
-      <c r="D88">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-      <c r="F88" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A89" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B89" t="s">
-        <v>266</v>
-      </c>
-      <c r="C89" t="s">
-        <v>311</v>
-      </c>
-      <c r="D89">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A90" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B90" t="s">
-        <v>266</v>
-      </c>
-      <c r="C90" t="s">
-        <v>311</v>
-      </c>
-      <c r="D90">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A91" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B91" t="s">
-        <v>266</v>
-      </c>
-      <c r="C91" t="s">
-        <v>311</v>
-      </c>
-      <c r="D91">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M91">
-        <v>1</v>
-      </c>
-      <c r="N91" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A92" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B92" t="s">
-        <v>266</v>
-      </c>
-      <c r="C92" t="s">
-        <v>268</v>
-      </c>
-      <c r="D92">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K92">
-        <v>1</v>
-      </c>
-      <c r="L92" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A93" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B93" t="s">
-        <v>266</v>
-      </c>
-      <c r="C93" t="s">
-        <v>268</v>
-      </c>
-      <c r="D93">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K93">
-        <v>1</v>
-      </c>
-      <c r="L93" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A94" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B94" t="s">
-        <v>266</v>
-      </c>
-      <c r="C94" t="s">
-        <v>311</v>
-      </c>
-      <c r="D94">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M94">
-        <v>1</v>
-      </c>
-      <c r="N94" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A95" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B95" t="s">
-        <v>266</v>
-      </c>
-      <c r="C95" t="s">
-        <v>311</v>
-      </c>
-      <c r="D95">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K95">
-        <v>1</v>
-      </c>
-      <c r="L95" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A96" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B96" t="s">
-        <v>266</v>
-      </c>
-      <c r="C96" t="s">
-        <v>287</v>
-      </c>
-      <c r="D96">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K96">
-        <v>1</v>
-      </c>
-      <c r="L96" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A97" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B97" t="s">
-        <v>266</v>
-      </c>
-      <c r="C97" t="s">
-        <v>311</v>
-      </c>
-      <c r="D97">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K97">
-        <v>1</v>
-      </c>
-      <c r="L97" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A98" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B98" t="s">
-        <v>294</v>
-      </c>
-      <c r="C98" t="s">
-        <v>296</v>
-      </c>
-      <c r="D98">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
-      <c r="F98" t="s">
-        <v>461</v>
-      </c>
-      <c r="G98">
-        <v>0</v>
-      </c>
-      <c r="H98" t="s">
-        <v>461</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98" t="s">
-        <v>461</v>
-      </c>
-      <c r="K98">
-        <v>0</v>
-      </c>
-      <c r="L98" t="s">
-        <v>461</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98" t="s">
-        <v>461</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A99" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B99" t="s">
-        <v>294</v>
-      </c>
-      <c r="C99" t="s">
-        <v>296</v>
-      </c>
-      <c r="D99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99" t="s">
-        <v>461</v>
-      </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99" t="s">
-        <v>461</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99" t="s">
-        <v>461</v>
-      </c>
-      <c r="K99">
-        <v>0</v>
-      </c>
-      <c r="L99" t="s">
-        <v>461</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99" t="s">
-        <v>461</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A100" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B100" t="s">
-        <v>294</v>
-      </c>
-      <c r="C100" t="s">
-        <v>296</v>
-      </c>
-      <c r="D100">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100" t="s">
-        <v>461</v>
-      </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
-      <c r="H100" t="s">
-        <v>461</v>
-      </c>
-      <c r="I100">
-        <v>0</v>
-      </c>
-      <c r="J100" t="s">
-        <v>461</v>
-      </c>
-      <c r="K100">
-        <v>0</v>
-      </c>
-      <c r="L100" t="s">
-        <v>461</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100" t="s">
-        <v>461</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A101" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B101" t="s">
-        <v>294</v>
-      </c>
-      <c r="C101" t="s">
-        <v>296</v>
-      </c>
-      <c r="D101">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A102" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B102" t="s">
-        <v>294</v>
-      </c>
-      <c r="C102" t="s">
-        <v>296</v>
-      </c>
-      <c r="D102">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A103" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B103" t="s">
-        <v>294</v>
-      </c>
-      <c r="C103" t="s">
-        <v>296</v>
-      </c>
-      <c r="D103">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A104" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B104" t="s">
-        <v>294</v>
-      </c>
-      <c r="C104" t="s">
-        <v>296</v>
-      </c>
-      <c r="D104">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A105" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B105" t="s">
-        <v>294</v>
-      </c>
-      <c r="C105" t="s">
-        <v>296</v>
-      </c>
-      <c r="D105">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A106" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B106" t="s">
-        <v>294</v>
-      </c>
-      <c r="C106" t="s">
-        <v>296</v>
-      </c>
-      <c r="D106">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A107" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B107" t="s">
-        <v>294</v>
-      </c>
-      <c r="C107" t="s">
-        <v>296</v>
-      </c>
-      <c r="D107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A108" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B108" t="s">
-        <v>294</v>
-      </c>
-      <c r="C108" t="s">
-        <v>296</v>
-      </c>
-      <c r="D108">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A109" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B109" t="s">
-        <v>406</v>
-      </c>
-      <c r="C109" t="s">
-        <v>478</v>
-      </c>
-      <c r="D109">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
-      <c r="F109" t="s">
-        <v>461</v>
-      </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-      <c r="H109" t="s">
-        <v>461</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109" t="s">
-        <v>461</v>
-      </c>
-      <c r="K109">
-        <v>0</v>
-      </c>
-      <c r="L109" t="s">
-        <v>461</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109" t="s">
-        <v>461</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A110" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B110" t="s">
-        <v>274</v>
-      </c>
-      <c r="C110" t="s">
-        <v>331</v>
-      </c>
-      <c r="D110">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A111" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B111" t="s">
-        <v>274</v>
-      </c>
-      <c r="C111" t="s">
-        <v>335</v>
-      </c>
-      <c r="D111">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A112" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B112" t="s">
-        <v>274</v>
-      </c>
-      <c r="C112" t="s">
-        <v>275</v>
-      </c>
-      <c r="D112">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A113" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B113" t="s">
-        <v>274</v>
-      </c>
-      <c r="C113" t="s">
-        <v>331</v>
-      </c>
-      <c r="D113">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A114" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B114" t="s">
-        <v>274</v>
-      </c>
-      <c r="C114" t="s">
-        <v>335</v>
-      </c>
-      <c r="D114">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A115" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B115" t="s">
-        <v>274</v>
-      </c>
-      <c r="C115" t="s">
-        <v>335</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A116" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B116" t="s">
-        <v>274</v>
-      </c>
-      <c r="C116" t="s">
-        <v>331</v>
-      </c>
-      <c r="D116">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A117" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B117" t="s">
-        <v>274</v>
-      </c>
-      <c r="C117" t="s">
-        <v>331</v>
-      </c>
-      <c r="D117">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A118" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B118" t="s">
-        <v>274</v>
-      </c>
-      <c r="C118" t="s">
-        <v>335</v>
-      </c>
-      <c r="D118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A119" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="B119" t="s">
-        <v>274</v>
-      </c>
-      <c r="C119" t="s">
-        <v>335</v>
-      </c>
-      <c r="D119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A120" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B120" t="s">
-        <v>274</v>
-      </c>
-      <c r="C120" t="s">
-        <v>335</v>
-      </c>
-      <c r="D120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A121" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B121" t="s">
-        <v>274</v>
-      </c>
-      <c r="C121" t="s">
-        <v>335</v>
-      </c>
-      <c r="D121">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A122" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B122" t="s">
-        <v>274</v>
-      </c>
-      <c r="C122" t="s">
-        <v>335</v>
-      </c>
-      <c r="D122">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A123" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B123" t="s">
-        <v>274</v>
-      </c>
-      <c r="C123" t="s">
-        <v>335</v>
-      </c>
-      <c r="D123">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A124" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B124" t="s">
-        <v>274</v>
-      </c>
-      <c r="C124" t="s">
-        <v>335</v>
-      </c>
-      <c r="D124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A125" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B125" t="s">
-        <v>274</v>
-      </c>
-      <c r="C125" t="s">
-        <v>331</v>
-      </c>
-      <c r="D125">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A126" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B126" t="s">
-        <v>274</v>
-      </c>
-      <c r="C126" t="s">
-        <v>275</v>
-      </c>
-      <c r="D126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A127" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B127" t="s">
-        <v>274</v>
-      </c>
-      <c r="C127" t="s">
-        <v>275</v>
-      </c>
-      <c r="D127">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A128" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B128" t="s">
-        <v>274</v>
-      </c>
-      <c r="C128" t="s">
-        <v>331</v>
-      </c>
-      <c r="D128">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A129" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B129" t="s">
-        <v>274</v>
-      </c>
-      <c r="C129" t="s">
-        <v>275</v>
-      </c>
-      <c r="D129">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A130" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B130" t="s">
-        <v>274</v>
-      </c>
-      <c r="C130" t="s">
-        <v>335</v>
-      </c>
-      <c r="D130">
-        <f t="shared" ref="D130:D193" si="2">SUM(E130,G130,I130,K130,M130,O130)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A131" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B131" t="s">
-        <v>274</v>
-      </c>
-      <c r="C131" t="s">
-        <v>335</v>
-      </c>
-      <c r="D131">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A132" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B132" t="s">
-        <v>274</v>
-      </c>
-      <c r="C132" t="s">
-        <v>331</v>
-      </c>
-      <c r="D132">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A133" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B133" t="s">
-        <v>274</v>
-      </c>
-      <c r="C133" t="s">
-        <v>331</v>
-      </c>
-      <c r="D133">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A134" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B134" t="s">
-        <v>274</v>
-      </c>
-      <c r="C134" t="s">
-        <v>331</v>
-      </c>
-      <c r="D134">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A135" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B135" t="s">
-        <v>274</v>
-      </c>
-      <c r="C135" t="s">
-        <v>335</v>
-      </c>
-      <c r="D135">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A136" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B136" t="s">
-        <v>274</v>
-      </c>
-      <c r="C136" t="s">
-        <v>331</v>
-      </c>
-      <c r="D136">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A137" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B137" t="s">
-        <v>274</v>
-      </c>
-      <c r="C137" t="s">
-        <v>331</v>
-      </c>
-      <c r="D137">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A138" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B138" t="s">
-        <v>274</v>
-      </c>
-      <c r="C138" t="s">
-        <v>275</v>
-      </c>
-      <c r="D138">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A139" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B139" t="s">
-        <v>274</v>
-      </c>
-      <c r="C139" t="s">
-        <v>335</v>
-      </c>
-      <c r="D139">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A140" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B140" t="s">
-        <v>274</v>
-      </c>
-      <c r="C140" t="s">
-        <v>331</v>
-      </c>
-      <c r="D140">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A141" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B141" t="s">
-        <v>274</v>
-      </c>
-      <c r="C141" t="s">
-        <v>335</v>
-      </c>
-      <c r="D141">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A142" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B142" t="s">
-        <v>274</v>
-      </c>
-      <c r="C142" t="s">
-        <v>331</v>
-      </c>
-      <c r="D142">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A143" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B143" t="s">
-        <v>274</v>
-      </c>
-      <c r="C143" t="s">
-        <v>331</v>
-      </c>
-      <c r="D143">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A144" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B144" t="s">
-        <v>274</v>
-      </c>
-      <c r="C144" t="s">
-        <v>331</v>
-      </c>
-      <c r="D144">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A145" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B145" t="s">
-        <v>274</v>
-      </c>
-      <c r="C145" t="s">
-        <v>275</v>
-      </c>
-      <c r="D145">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A146" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B146" t="s">
-        <v>274</v>
-      </c>
-      <c r="C146" t="s">
-        <v>275</v>
-      </c>
-      <c r="D146">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A147" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B147" t="s">
-        <v>274</v>
-      </c>
-      <c r="C147" t="s">
-        <v>335</v>
-      </c>
-      <c r="D147">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A148" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B148" t="s">
-        <v>274</v>
-      </c>
-      <c r="C148" t="s">
-        <v>335</v>
-      </c>
-      <c r="D148">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A149" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B149" t="s">
-        <v>274</v>
-      </c>
-      <c r="C149" t="s">
-        <v>335</v>
-      </c>
-      <c r="D149">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A150" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B150" t="s">
-        <v>274</v>
-      </c>
-      <c r="C150" t="s">
-        <v>331</v>
-      </c>
-      <c r="D150">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A151" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B151" t="s">
-        <v>274</v>
-      </c>
-      <c r="C151" t="s">
-        <v>331</v>
-      </c>
-      <c r="D151">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A152" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B152" t="s">
-        <v>274</v>
-      </c>
-      <c r="C152" t="s">
-        <v>335</v>
-      </c>
-      <c r="D152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A153" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B153" t="s">
-        <v>274</v>
-      </c>
-      <c r="C153" t="s">
-        <v>335</v>
-      </c>
-      <c r="D153">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A154" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B154" t="s">
-        <v>274</v>
-      </c>
-      <c r="C154" t="s">
-        <v>275</v>
-      </c>
-      <c r="D154">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A155" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B155" t="s">
-        <v>274</v>
-      </c>
-      <c r="C155" t="s">
-        <v>335</v>
-      </c>
-      <c r="D155">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A156" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B156" t="s">
-        <v>274</v>
-      </c>
-      <c r="C156" t="s">
-        <v>331</v>
-      </c>
-      <c r="D156">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A157" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B157" t="s">
-        <v>274</v>
-      </c>
-      <c r="C157" t="s">
-        <v>335</v>
-      </c>
-      <c r="D157">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A158" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B158" t="s">
-        <v>179</v>
-      </c>
-      <c r="C158" t="s">
-        <v>329</v>
-      </c>
-      <c r="D158">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A159" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B159" t="s">
-        <v>179</v>
-      </c>
-      <c r="C159" t="s">
-        <v>455</v>
-      </c>
-      <c r="D159">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A160" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B160" t="s">
-        <v>179</v>
-      </c>
-      <c r="C160" t="s">
-        <v>238</v>
-      </c>
-      <c r="D160">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A161" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B161" t="s">
-        <v>179</v>
-      </c>
-      <c r="C161" t="s">
-        <v>238</v>
-      </c>
-      <c r="D161">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A162" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B162" t="s">
-        <v>179</v>
-      </c>
-      <c r="C162" t="s">
-        <v>237</v>
-      </c>
-      <c r="D162">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A163" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B163" t="s">
-        <v>179</v>
-      </c>
-      <c r="C163" t="s">
-        <v>455</v>
-      </c>
-      <c r="D163">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A164" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B164" t="s">
-        <v>179</v>
-      </c>
-      <c r="C164" t="s">
-        <v>329</v>
-      </c>
-      <c r="D164">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A165" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B165" t="s">
-        <v>179</v>
-      </c>
-      <c r="C165" t="s">
-        <v>329</v>
-      </c>
-      <c r="D165">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A166" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B166" t="s">
-        <v>179</v>
-      </c>
-      <c r="C166" t="s">
-        <v>237</v>
-      </c>
-      <c r="D166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A167" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B167" t="s">
-        <v>179</v>
-      </c>
-      <c r="C167" t="s">
-        <v>238</v>
-      </c>
-      <c r="D167">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A168" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B168" t="s">
-        <v>179</v>
-      </c>
-      <c r="C168" t="s">
-        <v>237</v>
-      </c>
-      <c r="D168">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A169" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B169" t="s">
-        <v>179</v>
-      </c>
-      <c r="C169" t="s">
-        <v>329</v>
-      </c>
-      <c r="D169">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A170" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B170" t="s">
-        <v>179</v>
-      </c>
-      <c r="C170" t="s">
-        <v>237</v>
-      </c>
-      <c r="D170">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A171" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B171" t="s">
-        <v>179</v>
-      </c>
-      <c r="C171" t="s">
-        <v>238</v>
-      </c>
-      <c r="D171">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A172" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B172" t="s">
-        <v>179</v>
-      </c>
-      <c r="C172" t="s">
-        <v>329</v>
-      </c>
-      <c r="D172">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A173" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B173" t="s">
-        <v>179</v>
-      </c>
-      <c r="C173" t="s">
-        <v>237</v>
-      </c>
-      <c r="D173">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A174" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B174" t="s">
-        <v>179</v>
-      </c>
-      <c r="C174" t="s">
-        <v>455</v>
-      </c>
-      <c r="D174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A175" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B175" t="s">
-        <v>179</v>
-      </c>
-      <c r="C175" t="s">
-        <v>329</v>
-      </c>
-      <c r="D175">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A176" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B176" t="s">
-        <v>179</v>
-      </c>
-      <c r="C176" t="s">
-        <v>455</v>
-      </c>
-      <c r="D176">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A177" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B177" t="s">
-        <v>179</v>
-      </c>
-      <c r="C177" t="s">
-        <v>455</v>
-      </c>
-      <c r="D177">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A178" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B178" t="s">
-        <v>179</v>
-      </c>
-      <c r="C178" t="s">
-        <v>455</v>
-      </c>
-      <c r="D178">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A179" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B179" t="s">
-        <v>179</v>
-      </c>
-      <c r="C179" t="s">
-        <v>329</v>
-      </c>
-      <c r="D179">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A180" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B180" t="s">
-        <v>179</v>
-      </c>
-      <c r="C180" t="s">
-        <v>455</v>
-      </c>
-      <c r="D180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A181" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B181" t="s">
-        <v>179</v>
-      </c>
-      <c r="C181" t="s">
-        <v>455</v>
-      </c>
-      <c r="D181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A182" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B182" t="s">
-        <v>179</v>
-      </c>
-      <c r="C182" t="s">
-        <v>329</v>
-      </c>
-      <c r="D182">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A183" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B183" t="s">
-        <v>179</v>
-      </c>
-      <c r="C183" t="s">
-        <v>238</v>
-      </c>
-      <c r="D183">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A184" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B184" t="s">
-        <v>179</v>
-      </c>
-      <c r="C184" t="s">
-        <v>238</v>
-      </c>
-      <c r="D184">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A185" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B185" t="s">
-        <v>179</v>
-      </c>
-      <c r="C185" t="s">
-        <v>237</v>
-      </c>
-      <c r="D185">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A186" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B186" t="s">
-        <v>179</v>
-      </c>
-      <c r="C186" t="s">
-        <v>455</v>
-      </c>
-      <c r="D186">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A187" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B187" t="s">
-        <v>179</v>
-      </c>
-      <c r="C187" t="s">
-        <v>329</v>
-      </c>
-      <c r="D187">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A188" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B188" t="s">
-        <v>179</v>
-      </c>
-      <c r="C188" t="s">
-        <v>329</v>
-      </c>
-      <c r="D188">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A189" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B189" t="s">
-        <v>179</v>
-      </c>
-      <c r="C189" t="s">
-        <v>455</v>
-      </c>
-      <c r="D189">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A190" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B190" t="s">
-        <v>179</v>
-      </c>
-      <c r="C190" t="s">
-        <v>455</v>
-      </c>
-      <c r="D190">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A191" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B191" t="s">
-        <v>233</v>
-      </c>
-      <c r="C191" t="s">
-        <v>245</v>
-      </c>
-      <c r="D191">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A192" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B192" t="s">
-        <v>233</v>
-      </c>
-      <c r="C192" t="s">
-        <v>243</v>
-      </c>
-      <c r="D192">
-        <f t="shared" si="2"/>
-        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A193" s="2" t="s">
-        <v>249</v>
+        <v>411</v>
       </c>
       <c r="B193" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C193" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D193">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>SUM(E193,G193,I193,K193,M193,O193)</f>
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A194" s="2" t="s">
-        <v>250</v>
+        <v>404</v>
       </c>
       <c r="B194" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C194" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D194">
-        <f t="shared" ref="D194:D257" si="3">SUM(E194,G194,I194,K194,M194,O194)</f>
-        <v>0</v>
+        <f>SUM(E194,G194,I194,K194,M194,O194)</f>
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A195" s="2" t="s">
-        <v>248</v>
+        <v>383</v>
       </c>
       <c r="B195" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C195" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D195">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E195,G195,I195,K195,M195,O195)</f>
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>1</v>
+      </c>
+      <c r="N195" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A196" s="2" t="s">
-        <v>232</v>
+        <v>384</v>
       </c>
       <c r="B196" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C196" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D196">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E196,G196,I196,K196,M196,O196)</f>
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A197" s="2" t="s">
-        <v>235</v>
+        <v>391</v>
       </c>
       <c r="B197" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C197" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D197">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E197,G197,I197,K197,M197,O197)</f>
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A198" s="2" t="s">
-        <v>180</v>
+        <v>392</v>
       </c>
       <c r="B198" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C198" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D198">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E198,G198,I198,K198,M198,O198)</f>
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A199" s="2" t="s">
-        <v>234</v>
+        <v>379</v>
       </c>
       <c r="B199" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C199" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D199">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E199,G199,I199,K199,M199,O199)</f>
+        <v>1</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A200" s="2" t="s">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="B200" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C200" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D200">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E200,G200,I200,K200,M200,O200)</f>
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A201" s="2" t="s">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="B201" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C201" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D201">
-        <f t="shared" si="3"/>
+        <f>SUM(E201,G201,I201,K201,M201,O201)</f>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A202" s="2" t="s">
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="B202" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C202" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D202">
-        <f t="shared" si="3"/>
+        <f>SUM(E202,G202,I202,K202,M202,O202)</f>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A203" s="2" t="s">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="B203" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C203" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D203">
-        <f t="shared" si="3"/>
+        <f>SUM(E203,G203,I203,K203,M203,O203)</f>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A204" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B204" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C204" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="D204">
-        <f t="shared" si="3"/>
+        <f>SUM(E204,G204,I204,K204,M204,O204)</f>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A205" s="2" t="s">
-        <v>258</v>
+        <v>423</v>
       </c>
       <c r="B205" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C205" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="D205">
-        <f t="shared" si="3"/>
+        <f>SUM(E205,G205,I205,K205,M205,O205)</f>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A206" s="2" t="s">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="B206" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C206" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="D206">
-        <f t="shared" si="3"/>
+        <f>SUM(E206,G206,I206,K206,M206,O206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A207" s="2" t="s">
-        <v>231</v>
+        <v>441</v>
       </c>
       <c r="B207" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="C207" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D207">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E207">
-        <v>0</v>
-      </c>
-      <c r="F207" t="s">
-        <v>461</v>
-      </c>
-      <c r="G207">
-        <v>0</v>
-      </c>
-      <c r="H207" t="s">
-        <v>461</v>
-      </c>
-      <c r="I207">
-        <v>0</v>
-      </c>
-      <c r="J207" t="s">
-        <v>461</v>
+        <f>SUM(E207,G207,I207,K207,M207,O207)</f>
+        <v>2</v>
       </c>
       <c r="K207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" t="s">
-        <v>444</v>
-      </c>
-      <c r="M207">
-        <v>0</v>
-      </c>
-      <c r="N207" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A208" s="2" t="s">
-        <v>230</v>
+        <v>402</v>
       </c>
       <c r="B208" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="C208" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D208">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E208">
-        <v>0</v>
-      </c>
-      <c r="F208" t="s">
-        <v>461</v>
-      </c>
-      <c r="G208">
-        <v>0</v>
-      </c>
-      <c r="H208" t="s">
-        <v>461</v>
-      </c>
-      <c r="I208">
-        <v>0</v>
-      </c>
-      <c r="J208" t="s">
-        <v>461</v>
+        <f>SUM(E208,G208,I208,K208,M208,O208)</f>
+        <v>1</v>
       </c>
       <c r="K208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L208" t="s">
-        <v>444</v>
-      </c>
-      <c r="M208">
-        <v>0</v>
-      </c>
-      <c r="N208" t="s">
-        <v>461</v>
-      </c>
-      <c r="O208">
-        <v>0</v>
-      </c>
-      <c r="P208" t="s">
-        <v>461</v>
+        <v>331</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A209" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B209" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="C209" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D209">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E209">
-        <v>0</v>
-      </c>
-      <c r="F209" t="s">
-        <v>461</v>
-      </c>
-      <c r="G209">
-        <v>0</v>
-      </c>
-      <c r="H209" t="s">
-        <v>461</v>
-      </c>
-      <c r="I209">
-        <v>0</v>
-      </c>
-      <c r="J209" t="s">
-        <v>461</v>
+        <f>SUM(E209,G209,I209,K209,M209,O209)</f>
+        <v>1</v>
       </c>
       <c r="K209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L209" t="s">
-        <v>461</v>
-      </c>
-      <c r="M209">
-        <v>0</v>
-      </c>
-      <c r="N209" t="s">
-        <v>461</v>
-      </c>
-      <c r="O209">
-        <v>0</v>
-      </c>
-      <c r="P209" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A210" s="2" t="s">
-        <v>264</v>
+        <v>401</v>
       </c>
       <c r="B210" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C210" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="D210">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E210,G210,I210,K210,M210,O210)</f>
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A211" s="2" t="s">
-        <v>261</v>
+        <v>422</v>
       </c>
       <c r="B211" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C211" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="D211">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E211,G211,I211,K211,M211,O211)</f>
+        <v>1</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A212" s="2" t="s">
-        <v>263</v>
+        <v>400</v>
       </c>
       <c r="B212" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C212" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="D212">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E212,G212,I212,K212,M212,O212)</f>
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.45">
@@ -11908,7 +11883,7 @@
         <v>268</v>
       </c>
       <c r="D213">
-        <f t="shared" si="3"/>
+        <f>SUM(E213,G213,I213,K213,M213,O213)</f>
         <v>0</v>
       </c>
       <c r="E213">
@@ -11950,7 +11925,7 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A214" s="2" t="s">
-        <v>299</v>
+        <v>397</v>
       </c>
       <c r="B214" t="s">
         <v>266</v>
@@ -11959,13 +11934,25 @@
         <v>268</v>
       </c>
       <c r="D214">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E214,G214,I214,K214,M214,O214)</f>
+        <v>2</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214" t="s">
+        <v>431</v>
+      </c>
+      <c r="O214">
+        <v>1</v>
+      </c>
+      <c r="P214" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A215" s="2" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="B215" t="s">
         <v>266</v>
@@ -11974,13 +11961,25 @@
         <v>268</v>
       </c>
       <c r="D215">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E215,G215,I215,K215,M215,O215)</f>
+        <v>2</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+      <c r="F215" t="s">
+        <v>451</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A216" s="2" t="s">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="B216" t="s">
         <v>266</v>
@@ -11989,28 +11988,34 @@
         <v>268</v>
       </c>
       <c r="D216">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E216,G216,I216,K216,M216,O216)</f>
+        <v>1</v>
+      </c>
+      <c r="O216">
+        <v>1</v>
+      </c>
+      <c r="P216" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A217" s="2" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="B217" t="s">
         <v>266</v>
       </c>
       <c r="C217" t="s">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="D217">
-        <f t="shared" si="3"/>
+        <f>SUM(E217,G217,I217,K217,M217,O217)</f>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A218" s="2" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="B218" t="s">
         <v>266</v>
@@ -12019,13 +12024,13 @@
         <v>268</v>
       </c>
       <c r="D218">
-        <f t="shared" si="3"/>
+        <f>SUM(E218,G218,I218,K218,M218,O218)</f>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A219" s="2" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B219" t="s">
         <v>266</v>
@@ -12034,28 +12039,28 @@
         <v>268</v>
       </c>
       <c r="D219">
-        <f t="shared" si="3"/>
+        <f>SUM(E219,G219,I219,K219,M219,O219)</f>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A220" s="2" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B220" t="s">
         <v>266</v>
       </c>
       <c r="C220" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D220">
-        <f t="shared" si="3"/>
+        <f>SUM(E220,G220,I220,K220,M220,O220)</f>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A221" s="2" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="B221" t="s">
         <v>266</v>
@@ -12064,58 +12069,58 @@
         <v>268</v>
       </c>
       <c r="D221">
-        <f t="shared" si="3"/>
+        <f>SUM(E221,G221,I221,K221,M221,O221)</f>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A222" s="2" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B222" t="s">
         <v>266</v>
       </c>
       <c r="C222" t="s">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="D222">
-        <f t="shared" si="3"/>
+        <f>SUM(E222,G222,I222,K222,M222,O222)</f>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A223" s="2" t="s">
-        <v>423</v>
+        <v>301</v>
       </c>
       <c r="B223" t="s">
         <v>266</v>
       </c>
       <c r="C223" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D223">
-        <f t="shared" si="3"/>
+        <f>SUM(E223,G223,I223,K223,M223,O223)</f>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A224" s="2" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="B224" t="s">
         <v>266</v>
       </c>
       <c r="C224" t="s">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="D224">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E224,G224,I224,K224,M224,O224)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A225" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B225" t="s">
         <v>266</v>
@@ -12124,58 +12129,58 @@
         <v>268</v>
       </c>
       <c r="D225">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E225,G225,I225,K225,M225,O225)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A226" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B226" t="s">
         <v>266</v>
       </c>
       <c r="C226" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="D226">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E226,G226,I226,K226,M226,O226)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A227" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B227" t="s">
         <v>266</v>
       </c>
       <c r="C227" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="D227">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E227,G227,I227,K227,M227,O227)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A228" s="2" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="B228" t="s">
         <v>266</v>
       </c>
       <c r="C228" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="D228">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E228,G228,I228,K228,M228,O228)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A229" s="2" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="B229" t="s">
         <v>266</v>
@@ -12184,13 +12189,13 @@
         <v>268</v>
       </c>
       <c r="D229">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E229,G229,I229,K229,M229,O229)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A230" s="2" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="B230" t="s">
         <v>266</v>
@@ -12199,98 +12204,146 @@
         <v>268</v>
       </c>
       <c r="D230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E230,G230,I230,K230,M230,O230)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A231" s="2" t="s">
-        <v>302</v>
+        <v>428</v>
       </c>
       <c r="B231" t="s">
         <v>266</v>
       </c>
       <c r="C231" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D231">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E231,G231,I231,K231,M231,O231)</f>
+        <v>3</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231" t="s">
+        <v>459</v>
+      </c>
+      <c r="G231">
+        <v>1</v>
+      </c>
+      <c r="H231" t="s">
+        <v>459</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="L231" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A232" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B232" t="s">
         <v>266</v>
       </c>
       <c r="C232" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D232">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E232,G232,I232,K232,M232,O232)</f>
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A233" s="2" t="s">
-        <v>272</v>
+        <v>436</v>
       </c>
       <c r="B233" t="s">
         <v>266</v>
       </c>
       <c r="C233" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D233">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E233,G233,I233,K233,M233,O233)</f>
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A234" s="2" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B234" t="s">
         <v>266</v>
       </c>
       <c r="C234" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="D234">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E234,G234,I234,K234,M234,O234)</f>
+        <v>1</v>
+      </c>
+      <c r="G234">
+        <v>1</v>
+      </c>
+      <c r="H234" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A235" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B235" t="s">
         <v>266</v>
       </c>
       <c r="C235" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D235">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUM(E235,G235,I235,K235,M235,O235)</f>
+        <v>1</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="F235" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A236" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B236" t="s">
         <v>266</v>
       </c>
       <c r="C236" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D236">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM(E236,G236,I236,K236,M236,O236)</f>
+        <v>1</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="524">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Tzaangors</t>
   </si>
   <si>
-    <t xml:space="preserve">Sylvaneth Endless Spells</t>
+    <t xml:space="preserve">Ulthwé Farseer</t>
   </si>
   <si>
     <t xml:space="preserve">Ulthwé Army</t>
@@ -587,6 +587,9 @@
     <t xml:space="preserve">Awakened Wyldwood</t>
   </si>
   <si>
+    <t xml:space="preserve">Manifestations of the Deepwood</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paint</t>
   </si>
   <si>
@@ -978,6 +981,9 @@
   </si>
   <si>
     <t xml:space="preserve">Purple clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gladewyrm</t>
   </si>
   <si>
     <t xml:space="preserve">Deck Tan</t>
@@ -1597,7 +1603,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="mmm\-yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1619,6 +1625,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -1719,7 +1731,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1736,6 +1748,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1748,7 +1764,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3233,11 +3249,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="19749671"/>
-        <c:axId val="87392361"/>
+        <c:axId val="93101161"/>
+        <c:axId val="8498788"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="19749671"/>
+        <c:axId val="93101161"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3269,7 +3285,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87392361"/>
+        <c:crossAx val="8498788"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3277,7 +3293,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87392361"/>
+        <c:axId val="8498788"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3316,7 +3332,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19749671"/>
+        <c:crossAx val="93101161"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3357,9 +3373,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>622800</xdr:colOff>
+      <xdr:colOff>622440</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>25200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3367,8 +3383,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7723080" y="7024320"/>
-        <a:ext cx="7511040" cy="3179520"/>
+        <a:off x="7723080" y="7038360"/>
+        <a:ext cx="7510680" cy="3179160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3641,7 +3657,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1192"/>
+  <dimension ref="A1:J1193"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.67"/>
@@ -3700,8 +3716,8 @@
         <v>11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <f aca="false">SUM(C2:C1029)</f>
-        <v>548</v>
+        <f aca="false">SUM(C2:C1030)</f>
+        <v>551</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -3756,7 +3772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>43466</v>
       </c>
@@ -3775,7 +3791,7 @@
       <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
@@ -4105,7 +4121,7 @@
       <c r="F19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4128,7 +4144,7 @@
       <c r="F20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4151,7 +4167,7 @@
       <c r="F21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4174,7 +4190,7 @@
       <c r="F22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4197,7 +4213,7 @@
       <c r="F23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4220,7 +4236,7 @@
       <c r="F24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
@@ -4241,7 +4257,7 @@
       <c r="F25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
@@ -4262,7 +4278,7 @@
       <c r="F26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
@@ -7055,67 +7071,84 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B183" s="2"/>
+        <v>45809</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B184" s="2"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B185" s="2"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B186" s="2"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B187" s="2"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B188" s="2"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B189" s="2"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B190" s="2"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B191" s="2"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B192" s="2"/>
+    </row>
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B192" s="2"/>
-    </row>
-    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B193" s="2"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10114,6 +10147,9 @@
     </row>
     <row r="1192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1192" s="2"/>
+    </row>
+    <row r="1193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1193" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J11 B2:B1048576">
@@ -10149,7 +10185,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1192" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1193" type="list">
       <formula1>$J$2:$J$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10181,7 +10217,7 @@
   <dimension ref="A1:P250"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="19.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="19.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.07"/>
@@ -10198,64 +10234,64 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>188</v>
+      <c r="A1" s="8" t="s">
+        <v>189</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>201</v>
+      <c r="A2" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
@@ -10265,48 +10301,48 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>205</v>
+      <c r="A3" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10316,30 +10352,30 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>211</v>
+      <c r="A4" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
@@ -10349,30 +10385,30 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>216</v>
+      <c r="A5" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
@@ -10382,30 +10418,30 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>221</v>
+      <c r="A6" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
@@ -10415,48 +10451,48 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>223</v>
+      <c r="A7" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
@@ -10466,30 +10502,30 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>228</v>
+      <c r="A8" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10499,30 +10535,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>231</v>
+      <c r="A9" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10532,30 +10568,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>234</v>
+      <c r="A10" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10565,30 +10601,30 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
@@ -10598,7 +10634,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>1</v>
@@ -10607,18 +10643,18 @@
         <v>1</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>240</v>
+      <c r="A12" s="8" t="s">
+        <v>241</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
@@ -10628,30 +10664,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>244</v>
+      <c r="A13" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
@@ -10661,30 +10697,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>247</v>
+      <c r="A14" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -10694,30 +10730,30 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>252</v>
+      <c r="A15" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
@@ -10727,30 +10763,30 @@
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>254</v>
+      <c r="A16" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -10760,24 +10796,24 @@
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>257</v>
+      <c r="A17" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
@@ -10787,24 +10823,24 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>258</v>
+      <c r="A18" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
@@ -10814,24 +10850,24 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>261</v>
+      <c r="A19" s="8" t="s">
+        <v>262</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
@@ -10841,21 +10877,21 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>263</v>
+      <c r="A20" s="8" t="s">
+        <v>264</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
@@ -10865,24 +10901,24 @@
         <v>1</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>264</v>
+      <c r="A21" s="8" t="s">
+        <v>265</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
@@ -10892,24 +10928,24 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
@@ -10919,24 +10955,24 @@
         <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>271</v>
+      <c r="A23" s="8" t="s">
+        <v>272</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -10946,24 +10982,24 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>272</v>
+      <c r="A24" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
@@ -10973,21 +11009,21 @@
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M24" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>273</v>
+      <c r="A25" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
@@ -10997,24 +11033,24 @@
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>276</v>
+      <c r="A26" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
@@ -11024,24 +11060,24 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>278</v>
+      <c r="A27" s="8" t="s">
+        <v>279</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
@@ -11051,24 +11087,24 @@
         <v>1</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>280</v>
+      <c r="A28" s="8" t="s">
+        <v>281</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
@@ -11078,24 +11114,24 @@
         <v>1</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>281</v>
+      <c r="A29" s="8" t="s">
+        <v>282</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
@@ -11105,24 +11141,24 @@
         <v>1</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>282</v>
+      <c r="A30" s="8" t="s">
+        <v>283</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
@@ -11132,24 +11168,24 @@
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
-        <v>283</v>
+      <c r="A31" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
@@ -11159,24 +11195,24 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
@@ -11186,24 +11222,24 @@
         <v>1</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>285</v>
+      <c r="A33" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
@@ -11213,24 +11249,24 @@
         <v>1</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>286</v>
+      <c r="A34" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
@@ -11240,24 +11276,24 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
-        <v>287</v>
+      <c r="A35" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
@@ -11267,24 +11303,24 @@
         <v>1</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>289</v>
+      <c r="A36" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
@@ -11294,24 +11330,24 @@
         <v>1</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>291</v>
+      <c r="A37" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
@@ -11321,24 +11357,24 @@
         <v>1</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>293</v>
+      <c r="A38" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
@@ -11348,24 +11384,24 @@
         <v>1</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>294</v>
+      <c r="A39" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
@@ -11375,18 +11411,18 @@
         <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
-        <v>295</v>
+      <c r="A40" s="8" t="s">
+        <v>296</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
@@ -11396,18 +11432,18 @@
         <v>1</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
-        <v>298</v>
+      <c r="A41" s="8" t="s">
+        <v>299</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
@@ -11420,18 +11456,18 @@
         <v>1</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
-        <v>299</v>
+      <c r="A42" s="8" t="s">
+        <v>300</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
@@ -11441,18 +11477,18 @@
         <v>1</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
-        <v>300</v>
+      <c r="A43" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
@@ -11462,18 +11498,18 @@
         <v>1</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
@@ -11483,18 +11519,18 @@
         <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
-        <v>302</v>
+      <c r="A45" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
@@ -11504,18 +11540,18 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
-        <v>304</v>
+      <c r="A46" s="8" t="s">
+        <v>305</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
@@ -11525,18 +11561,18 @@
         <v>1</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
-        <v>306</v>
+      <c r="A47" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
@@ -11546,18 +11582,18 @@
         <v>1</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
-        <v>307</v>
+      <c r="A48" s="8" t="s">
+        <v>308</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
@@ -11567,18 +11603,18 @@
         <v>1</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>308</v>
+      <c r="A49" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
@@ -11588,18 +11624,18 @@
         <v>1</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
-        <v>310</v>
+      <c r="A50" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
@@ -11609,18 +11645,18 @@
         <v>1</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
-        <v>312</v>
+      <c r="A51" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
@@ -11630,18 +11666,18 @@
         <v>1</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
-        <v>313</v>
+      <c r="A52" s="8" t="s">
+        <v>314</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
@@ -11651,18 +11687,18 @@
         <v>1</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
-        <v>316</v>
+      <c r="A53" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
@@ -11672,39 +11708,45 @@
         <v>1</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>317</v>
+      <c r="A54" s="8" t="s">
+        <v>318</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
-        <v>319</v>
+      <c r="A55" s="8" t="s">
+        <v>321</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
@@ -11714,18 +11756,18 @@
         <v>1</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
-        <v>320</v>
+      <c r="A56" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
@@ -11735,18 +11777,18 @@
         <v>1</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
-        <v>321</v>
+      <c r="A57" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
@@ -11756,18 +11798,18 @@
         <v>1</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
-        <v>323</v>
+      <c r="A58" s="8" t="s">
+        <v>325</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
@@ -11777,18 +11819,18 @@
         <v>1</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
-        <v>325</v>
+      <c r="A59" s="8" t="s">
+        <v>327</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
@@ -11798,18 +11840,18 @@
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
-        <v>328</v>
+      <c r="A60" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
@@ -11819,18 +11861,18 @@
         <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
-        <v>329</v>
+      <c r="A61" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
@@ -11840,18 +11882,18 @@
         <v>1</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
-        <v>331</v>
+      <c r="A62" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
@@ -11861,18 +11903,18 @@
         <v>1</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
-        <v>332</v>
+      <c r="A63" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
@@ -11882,18 +11924,18 @@
         <v>1</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
-        <v>333</v>
+      <c r="A64" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
@@ -11903,18 +11945,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
-        <v>335</v>
+      <c r="A65" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
@@ -11924,18 +11966,18 @@
         <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
-        <v>336</v>
+      <c r="A66" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
@@ -11945,18 +11987,18 @@
         <v>1</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="s">
-        <v>337</v>
+      <c r="A67" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -11967,14 +12009,14 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="s">
-        <v>338</v>
+      <c r="A68" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -11984,18 +12026,18 @@
         <v>1</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="s">
-        <v>339</v>
+      <c r="A69" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
@@ -12005,18 +12047,18 @@
         <v>1</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
-        <v>340</v>
+      <c r="A70" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -12026,18 +12068,18 @@
         <v>1</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="s">
-        <v>342</v>
+      <c r="A71" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
@@ -12047,18 +12089,18 @@
         <v>1</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
-        <v>344</v>
+      <c r="A72" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
@@ -12068,18 +12110,18 @@
         <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
-        <v>345</v>
+      <c r="A73" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
@@ -12089,18 +12131,18 @@
         <v>1</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="s">
-        <v>346</v>
+      <c r="A74" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
@@ -12110,18 +12152,18 @@
         <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="s">
-        <v>347</v>
+      <c r="A75" s="8" t="s">
+        <v>349</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
@@ -12131,18 +12173,18 @@
         <v>1</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="s">
-        <v>348</v>
+      <c r="A76" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
@@ -12152,18 +12194,18 @@
         <v>1</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
-        <v>349</v>
+      <c r="A77" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12173,18 +12215,18 @@
         <v>1</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
-        <v>350</v>
+      <c r="A78" s="8" t="s">
+        <v>352</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12194,18 +12236,18 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="s">
-        <v>351</v>
+      <c r="A79" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12215,18 +12257,18 @@
         <v>1</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="s">
-        <v>353</v>
+      <c r="A80" s="8" t="s">
+        <v>355</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12236,18 +12278,18 @@
         <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="s">
-        <v>357</v>
+      <c r="A81" s="8" t="s">
+        <v>359</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
@@ -12257,18 +12299,18 @@
         <v>1</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="s">
-        <v>358</v>
+      <c r="A82" s="8" t="s">
+        <v>360</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
@@ -12278,18 +12320,18 @@
         <v>1</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="s">
-        <v>359</v>
+      <c r="A83" s="8" t="s">
+        <v>361</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
@@ -12299,18 +12341,18 @@
         <v>1</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="s">
-        <v>360</v>
+      <c r="A84" s="8" t="s">
+        <v>362</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
@@ -12320,18 +12362,18 @@
         <v>1</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="s">
-        <v>361</v>
+      <c r="A85" s="8" t="s">
+        <v>363</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12341,18 +12383,18 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="s">
-        <v>362</v>
+      <c r="A86" s="8" t="s">
+        <v>364</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
@@ -12362,18 +12404,18 @@
         <v>1</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="s">
-        <v>363</v>
+      <c r="A87" s="8" t="s">
+        <v>365</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
@@ -12383,18 +12425,18 @@
         <v>1</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="s">
-        <v>364</v>
+      <c r="A88" s="8" t="s">
+        <v>366</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
@@ -12404,18 +12446,18 @@
         <v>1</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="s">
-        <v>365</v>
+      <c r="A89" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
@@ -12425,18 +12467,18 @@
         <v>1</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="s">
-        <v>366</v>
+      <c r="A90" s="8" t="s">
+        <v>368</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
@@ -12446,18 +12488,18 @@
         <v>1</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="s">
-        <v>367</v>
+      <c r="A91" s="8" t="s">
+        <v>369</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
@@ -12467,18 +12509,18 @@
         <v>1</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="s">
-        <v>368</v>
+      <c r="A92" s="8" t="s">
+        <v>370</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12488,18 +12530,18 @@
         <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="s">
-        <v>369</v>
+      <c r="A93" s="8" t="s">
+        <v>371</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
@@ -12509,18 +12551,18 @@
         <v>1</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7" t="s">
-        <v>370</v>
+      <c r="A94" s="8" t="s">
+        <v>372</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
@@ -12530,18 +12572,18 @@
         <v>1</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="s">
-        <v>371</v>
+      <c r="A95" s="8" t="s">
+        <v>373</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
@@ -12551,18 +12593,18 @@
         <v>1</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7" t="s">
-        <v>372</v>
+      <c r="A96" s="8" t="s">
+        <v>374</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
@@ -12572,18 +12614,18 @@
         <v>1</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="s">
-        <v>373</v>
+      <c r="A97" s="8" t="s">
+        <v>375</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
@@ -12593,18 +12635,18 @@
         <v>1</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7" t="s">
-        <v>374</v>
+      <c r="A98" s="8" t="s">
+        <v>376</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12614,18 +12656,18 @@
         <v>1</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="s">
-        <v>375</v>
+      <c r="A99" s="8" t="s">
+        <v>377</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
@@ -12635,18 +12677,18 @@
         <v>1</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7" t="s">
-        <v>376</v>
+      <c r="A100" s="8" t="s">
+        <v>378</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
@@ -12656,18 +12698,18 @@
         <v>1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="s">
-        <v>377</v>
+      <c r="A101" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
@@ -12677,18 +12719,18 @@
         <v>1</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="s">
-        <v>378</v>
+      <c r="A102" s="8" t="s">
+        <v>380</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
@@ -12698,18 +12740,18 @@
         <v>1</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="s">
-        <v>379</v>
+      <c r="A103" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
@@ -12719,18 +12761,18 @@
         <v>1</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7" t="s">
-        <v>380</v>
+      <c r="A104" s="8" t="s">
+        <v>382</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -12740,18 +12782,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="s">
-        <v>381</v>
+      <c r="A105" s="8" t="s">
+        <v>383</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -12761,18 +12803,18 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7" t="s">
-        <v>382</v>
+      <c r="A106" s="8" t="s">
+        <v>384</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
@@ -12782,18 +12824,18 @@
         <v>1</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="s">
-        <v>383</v>
+      <c r="A107" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
@@ -12803,18 +12845,18 @@
         <v>1</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7" t="s">
-        <v>385</v>
+      <c r="A108" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
@@ -12824,18 +12866,18 @@
         <v>1</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="s">
-        <v>386</v>
+      <c r="A109" s="8" t="s">
+        <v>388</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
@@ -12845,18 +12887,18 @@
         <v>1</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="s">
-        <v>387</v>
+      <c r="A110" s="8" t="s">
+        <v>389</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
@@ -12864,14 +12906,14 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="s">
-        <v>388</v>
+      <c r="A111" s="8" t="s">
+        <v>390</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
@@ -12879,14 +12921,14 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7" t="s">
-        <v>389</v>
+      <c r="A112" s="8" t="s">
+        <v>391</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -12894,14 +12936,14 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="s">
-        <v>390</v>
+      <c r="A113" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
@@ -12909,14 +12951,14 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7" t="s">
-        <v>391</v>
+      <c r="A114" s="8" t="s">
+        <v>393</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
@@ -12924,14 +12966,14 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7" t="s">
-        <v>392</v>
+      <c r="A115" s="8" t="s">
+        <v>394</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
@@ -12939,14 +12981,14 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7" t="s">
-        <v>394</v>
+      <c r="A116" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -12954,14 +12996,14 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7" t="s">
-        <v>395</v>
+      <c r="A117" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
@@ -12969,14 +13011,14 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7" t="s">
-        <v>396</v>
+      <c r="A118" s="8" t="s">
+        <v>398</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
@@ -12984,14 +13026,14 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7" t="s">
-        <v>397</v>
+      <c r="A119" s="8" t="s">
+        <v>399</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
@@ -12999,14 +13041,14 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7" t="s">
-        <v>398</v>
+      <c r="A120" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
@@ -13014,14 +13056,14 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7" t="s">
-        <v>398</v>
+      <c r="A121" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
@@ -13029,14 +13071,14 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7" t="s">
-        <v>400</v>
+      <c r="A122" s="8" t="s">
+        <v>402</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
@@ -13044,14 +13086,14 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="s">
-        <v>401</v>
+      <c r="A123" s="8" t="s">
+        <v>403</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -13061,48 +13103,48 @@
         <v>0</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G123" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I123" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K123" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M123" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O123" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
@@ -13112,48 +13154,48 @@
         <v>0</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G124" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I124" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K124" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M124" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O124" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7" t="s">
-        <v>403</v>
+      <c r="A125" s="8" t="s">
+        <v>405</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13161,14 +13203,14 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="7" t="s">
-        <v>404</v>
+      <c r="A126" s="8" t="s">
+        <v>406</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13176,14 +13218,14 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="7" t="s">
-        <v>405</v>
+      <c r="A127" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -13191,14 +13233,14 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7" t="s">
-        <v>405</v>
+      <c r="A128" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
@@ -13206,14 +13248,14 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7" t="s">
-        <v>407</v>
+      <c r="A129" s="8" t="s">
+        <v>409</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -13221,14 +13263,14 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="7" t="s">
-        <v>408</v>
+      <c r="A130" s="8" t="s">
+        <v>410</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -13236,14 +13278,14 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7" t="s">
-        <v>409</v>
+      <c r="A131" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
@@ -13251,14 +13293,14 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="7" t="s">
-        <v>410</v>
+      <c r="A132" s="8" t="s">
+        <v>412</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -13266,14 +13308,14 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7" t="s">
-        <v>412</v>
+      <c r="A133" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -13281,14 +13323,14 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="7" t="s">
-        <v>413</v>
+      <c r="A134" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13296,14 +13338,14 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="7" t="s">
-        <v>414</v>
+      <c r="A135" s="8" t="s">
+        <v>416</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13311,14 +13353,14 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="7" t="s">
-        <v>415</v>
+      <c r="A136" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13326,14 +13368,14 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7" t="s">
-        <v>416</v>
+      <c r="A137" s="8" t="s">
+        <v>418</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13341,14 +13383,14 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7" t="s">
-        <v>417</v>
+      <c r="A138" s="8" t="s">
+        <v>419</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13356,14 +13398,14 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7" t="s">
-        <v>418</v>
+      <c r="A139" s="8" t="s">
+        <v>420</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13371,14 +13413,14 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="7" t="s">
-        <v>419</v>
+      <c r="A140" s="8" t="s">
+        <v>421</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13386,14 +13428,14 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7" t="s">
-        <v>321</v>
+      <c r="A141" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13401,14 +13443,14 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7" t="s">
-        <v>421</v>
+      <c r="A142" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13418,48 +13460,48 @@
         <v>0</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G142" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I142" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K142" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M142" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O142" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7" t="s">
-        <v>422</v>
+      <c r="A143" s="8" t="s">
+        <v>424</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13467,14 +13509,14 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7" t="s">
-        <v>423</v>
+      <c r="A144" s="8" t="s">
+        <v>425</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
@@ -13482,14 +13524,14 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7" t="s">
-        <v>424</v>
+      <c r="A145" s="8" t="s">
+        <v>426</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13497,14 +13539,14 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7" t="s">
-        <v>425</v>
+      <c r="A146" s="8" t="s">
+        <v>427</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13512,14 +13554,14 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7" t="s">
-        <v>426</v>
+      <c r="A147" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13527,14 +13569,14 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7" t="s">
-        <v>427</v>
+      <c r="A148" s="8" t="s">
+        <v>429</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13542,14 +13584,14 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7" t="s">
-        <v>428</v>
+      <c r="A149" s="8" t="s">
+        <v>430</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
@@ -13557,14 +13599,14 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="7" t="s">
-        <v>429</v>
+      <c r="A150" s="8" t="s">
+        <v>431</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13572,14 +13614,14 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="7" t="s">
-        <v>430</v>
+      <c r="A151" s="8" t="s">
+        <v>432</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13587,14 +13629,14 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="7" t="s">
-        <v>431</v>
+      <c r="A152" s="8" t="s">
+        <v>433</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13602,14 +13644,14 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="7" t="s">
-        <v>432</v>
+      <c r="A153" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13617,14 +13659,14 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="7" t="s">
-        <v>433</v>
+      <c r="A154" s="8" t="s">
+        <v>435</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13632,14 +13674,14 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="7" t="s">
-        <v>434</v>
+      <c r="A155" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13647,14 +13689,14 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="7" t="s">
-        <v>435</v>
+      <c r="A156" s="8" t="s">
+        <v>437</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13662,14 +13704,14 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="7" t="s">
-        <v>436</v>
+      <c r="A157" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13677,14 +13719,14 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="7" t="s">
-        <v>437</v>
+      <c r="A158" s="8" t="s">
+        <v>439</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13692,14 +13734,14 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="7" t="s">
-        <v>438</v>
+      <c r="A159" s="8" t="s">
+        <v>440</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13707,14 +13749,14 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="7" t="s">
-        <v>439</v>
+      <c r="A160" s="8" t="s">
+        <v>441</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13722,14 +13764,14 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="7" t="s">
-        <v>440</v>
+      <c r="A161" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13737,14 +13779,14 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="7" t="s">
-        <v>441</v>
+      <c r="A162" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13752,14 +13794,14 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7" t="s">
-        <v>442</v>
+      <c r="A163" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -13767,14 +13809,14 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="7" t="s">
-        <v>443</v>
+      <c r="A164" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -13782,14 +13824,14 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="7" t="s">
-        <v>444</v>
+      <c r="A165" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -13797,14 +13839,14 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="7" t="s">
-        <v>445</v>
+      <c r="A166" s="8" t="s">
+        <v>447</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -13812,14 +13854,14 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7" t="s">
-        <v>446</v>
+      <c r="A167" s="8" t="s">
+        <v>448</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -13827,14 +13869,14 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7" t="s">
-        <v>447</v>
+      <c r="A168" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -13842,14 +13884,14 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7" t="s">
-        <v>448</v>
+      <c r="A169" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -13857,14 +13899,14 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7" t="s">
-        <v>449</v>
+      <c r="A170" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -13874,48 +13916,48 @@
         <v>0</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G170" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I170" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K170" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M170" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O170" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7" t="s">
-        <v>450</v>
+      <c r="A171" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -13923,14 +13965,14 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7" t="s">
-        <v>451</v>
+      <c r="A172" s="8" t="s">
+        <v>453</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -13938,14 +13980,14 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7" t="s">
-        <v>452</v>
+      <c r="A173" s="8" t="s">
+        <v>454</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -13953,14 +13995,14 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7" t="s">
-        <v>452</v>
+      <c r="A174" s="8" t="s">
+        <v>454</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -13970,48 +14012,48 @@
         <v>0</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G174" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I174" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K174" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M174" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O174" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="s">
-        <v>453</v>
+      <c r="A175" s="8" t="s">
+        <v>455</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14019,14 +14061,14 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7" t="s">
-        <v>454</v>
+      <c r="A176" s="8" t="s">
+        <v>456</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14034,14 +14076,14 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7" t="s">
-        <v>455</v>
+      <c r="A177" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14049,14 +14091,14 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7" t="s">
-        <v>456</v>
+      <c r="A178" s="8" t="s">
+        <v>458</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14064,14 +14106,14 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="s">
-        <v>457</v>
+      <c r="A179" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -14079,14 +14121,14 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7" t="s">
-        <v>458</v>
+      <c r="A180" s="8" t="s">
+        <v>460</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
@@ -14096,48 +14138,48 @@
         <v>0</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G180" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I180" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K180" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M180" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O180" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7" t="s">
+      <c r="A181" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14147,48 +14189,48 @@
         <v>0</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G181" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I181" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K181" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M181" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O181" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7" t="s">
+      <c r="A182" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14198,48 +14240,48 @@
         <v>0</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G182" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I182" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K182" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M182" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O182" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="s">
-        <v>459</v>
+      <c r="A183" s="8" t="s">
+        <v>461</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -14247,14 +14289,14 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7" t="s">
-        <v>460</v>
+      <c r="A184" s="8" t="s">
+        <v>462</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -14262,14 +14304,14 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7" t="s">
-        <v>461</v>
+      <c r="A185" s="8" t="s">
+        <v>463</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -14277,14 +14319,14 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7" t="s">
-        <v>462</v>
+      <c r="A186" s="8" t="s">
+        <v>464</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14292,14 +14334,14 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7" t="s">
-        <v>463</v>
+      <c r="A187" s="8" t="s">
+        <v>465</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14307,14 +14349,14 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7" t="s">
-        <v>464</v>
+      <c r="A188" s="8" t="s">
+        <v>466</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14322,14 +14364,14 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7" t="s">
-        <v>465</v>
+      <c r="A189" s="8" t="s">
+        <v>467</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14337,14 +14379,14 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7" t="s">
-        <v>466</v>
+      <c r="A190" s="8" t="s">
+        <v>468</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14352,14 +14394,14 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7" t="s">
-        <v>467</v>
+      <c r="A191" s="8" t="s">
+        <v>469</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14367,14 +14409,14 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="7" t="s">
-        <v>468</v>
+      <c r="A192" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14382,14 +14424,14 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7" t="s">
-        <v>469</v>
+      <c r="A193" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
@@ -14397,14 +14439,14 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="7" t="s">
-        <v>470</v>
+      <c r="A194" s="8" t="s">
+        <v>472</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
@@ -14412,14 +14454,14 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7" t="s">
-        <v>471</v>
+      <c r="A195" s="8" t="s">
+        <v>473</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14427,14 +14469,14 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="7" t="s">
-        <v>472</v>
+      <c r="A196" s="8" t="s">
+        <v>474</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
@@ -14442,14 +14484,14 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="7" t="s">
-        <v>473</v>
+      <c r="A197" s="8" t="s">
+        <v>475</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
@@ -14457,14 +14499,14 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="7" t="s">
-        <v>474</v>
+      <c r="A198" s="8" t="s">
+        <v>476</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
@@ -14472,14 +14514,14 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="7" t="s">
-        <v>475</v>
+      <c r="A199" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14487,14 +14529,14 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="7" t="s">
-        <v>476</v>
+      <c r="A200" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14502,14 +14544,14 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="7" t="s">
-        <v>477</v>
+      <c r="A201" s="8" t="s">
+        <v>479</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
@@ -14517,14 +14559,14 @@
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="7" t="s">
-        <v>478</v>
+      <c r="A202" s="8" t="s">
+        <v>480</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14532,14 +14574,14 @@
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="7" t="s">
-        <v>479</v>
+      <c r="A203" s="8" t="s">
+        <v>481</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14547,14 +14589,14 @@
       </c>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="7" t="s">
-        <v>480</v>
+      <c r="A204" s="8" t="s">
+        <v>482</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14562,14 +14604,14 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="7" t="s">
-        <v>481</v>
+      <c r="A205" s="8" t="s">
+        <v>483</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14577,14 +14619,14 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="7" t="s">
-        <v>482</v>
+      <c r="A206" s="8" t="s">
+        <v>484</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
@@ -14592,14 +14634,14 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="7" t="s">
-        <v>483</v>
+      <c r="A207" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14607,14 +14649,14 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="7" t="s">
-        <v>484</v>
+      <c r="A208" s="8" t="s">
+        <v>486</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14622,14 +14664,14 @@
       </c>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="7" t="s">
-        <v>485</v>
+      <c r="A209" s="8" t="s">
+        <v>487</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
@@ -14637,14 +14679,14 @@
       </c>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="7" t="s">
-        <v>486</v>
+      <c r="A210" s="8" t="s">
+        <v>488</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14652,14 +14694,14 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="7" t="s">
-        <v>487</v>
+      <c r="A211" s="8" t="s">
+        <v>489</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14667,14 +14709,14 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="7" t="s">
-        <v>488</v>
+      <c r="A212" s="8" t="s">
+        <v>490</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14682,14 +14724,14 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="7" t="s">
-        <v>488</v>
+      <c r="A213" s="8" t="s">
+        <v>490</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14697,14 +14739,14 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="7" t="s">
-        <v>489</v>
+      <c r="A214" s="8" t="s">
+        <v>491</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
@@ -14712,14 +14754,14 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="7" t="s">
-        <v>490</v>
+      <c r="A215" s="8" t="s">
+        <v>492</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14727,14 +14769,14 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="7" t="s">
-        <v>491</v>
+      <c r="A216" s="8" t="s">
+        <v>493</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
@@ -14742,14 +14784,14 @@
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="7" t="s">
-        <v>492</v>
+      <c r="A217" s="8" t="s">
+        <v>494</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
@@ -14757,14 +14799,14 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="7" t="s">
-        <v>493</v>
+      <c r="A218" s="8" t="s">
+        <v>495</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14772,14 +14814,14 @@
       </c>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="7" t="s">
-        <v>494</v>
+      <c r="A219" s="8" t="s">
+        <v>496</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14787,14 +14829,14 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="7" t="s">
-        <v>495</v>
+      <c r="A220" s="8" t="s">
+        <v>497</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14802,14 +14844,14 @@
       </c>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="7" t="s">
-        <v>496</v>
+      <c r="A221" s="8" t="s">
+        <v>498</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
@@ -14817,14 +14859,14 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="7" t="s">
-        <v>497</v>
+      <c r="A222" s="8" t="s">
+        <v>499</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
@@ -14832,14 +14874,14 @@
       </c>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="7" t="s">
-        <v>291</v>
+      <c r="A223" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -14847,14 +14889,14 @@
       </c>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="7" t="s">
-        <v>498</v>
+      <c r="A224" s="8" t="s">
+        <v>500</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
@@ -14862,14 +14904,14 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="7" t="s">
-        <v>499</v>
+      <c r="A225" s="8" t="s">
+        <v>501</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
@@ -14877,14 +14919,14 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="7" t="s">
-        <v>500</v>
+      <c r="A226" s="8" t="s">
+        <v>502</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
@@ -14892,14 +14934,14 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="7" t="s">
-        <v>501</v>
+      <c r="A227" s="8" t="s">
+        <v>503</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -14907,14 +14949,14 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="7" t="s">
-        <v>502</v>
+      <c r="A228" s="8" t="s">
+        <v>504</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -14922,14 +14964,14 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="7" t="s">
-        <v>503</v>
+      <c r="A229" s="8" t="s">
+        <v>505</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -14937,14 +14979,14 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="7" t="s">
-        <v>504</v>
+      <c r="A230" s="8" t="s">
+        <v>506</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -14952,14 +14994,14 @@
       </c>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="7" t="s">
-        <v>505</v>
+      <c r="A231" s="8" t="s">
+        <v>507</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -14967,14 +15009,14 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="7" t="s">
+      <c r="A232" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
@@ -14984,48 +15026,48 @@
         <v>0</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="7" t="s">
-        <v>506</v>
+      <c r="A233" s="8" t="s">
+        <v>508</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -15033,14 +15075,14 @@
       </c>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="7" t="s">
-        <v>507</v>
+      <c r="A234" s="8" t="s">
+        <v>509</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
@@ -15048,14 +15090,14 @@
       </c>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="7" t="s">
-        <v>508</v>
+      <c r="A235" s="8" t="s">
+        <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
@@ -15063,14 +15105,14 @@
       </c>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="7" t="s">
-        <v>509</v>
+      <c r="A236" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
@@ -15078,14 +15120,14 @@
       </c>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="7" t="s">
-        <v>509</v>
+      <c r="A237" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15093,14 +15135,14 @@
       </c>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="7" t="s">
-        <v>510</v>
+      <c r="A238" s="8" t="s">
+        <v>512</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
@@ -15108,14 +15150,14 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="7" t="s">
-        <v>511</v>
+      <c r="A239" s="8" t="s">
+        <v>513</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
@@ -15123,14 +15165,14 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="7" t="s">
-        <v>512</v>
+      <c r="A240" s="8" t="s">
+        <v>514</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
@@ -15138,14 +15180,14 @@
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="7" t="s">
-        <v>513</v>
+      <c r="A241" s="8" t="s">
+        <v>515</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15153,14 +15195,14 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="7" t="s">
-        <v>514</v>
+      <c r="A242" s="8" t="s">
+        <v>516</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
@@ -15168,14 +15210,14 @@
       </c>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="7" t="s">
-        <v>515</v>
+      <c r="A243" s="8" t="s">
+        <v>517</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15183,14 +15225,14 @@
       </c>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="7" t="s">
-        <v>516</v>
+      <c r="A244" s="8" t="s">
+        <v>518</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15198,14 +15240,14 @@
       </c>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="7" t="s">
-        <v>517</v>
+      <c r="A245" s="8" t="s">
+        <v>519</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
@@ -15213,14 +15255,14 @@
       </c>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="7" t="s">
-        <v>233</v>
+      <c r="A246" s="8" t="s">
+        <v>234</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15228,14 +15270,14 @@
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="7" t="s">
-        <v>518</v>
+      <c r="A247" s="8" t="s">
+        <v>520</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15243,14 +15285,14 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="7" t="s">
-        <v>519</v>
+      <c r="A248" s="8" t="s">
+        <v>521</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15258,14 +15300,14 @@
       </c>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="7" t="s">
-        <v>520</v>
+      <c r="A249" s="8" t="s">
+        <v>522</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15273,14 +15315,14 @@
       </c>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="7" t="s">
-        <v>521</v>
+      <c r="A250" s="8" t="s">
+        <v>523</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="528">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Tzaangors</t>
   </si>
   <si>
-    <t xml:space="preserve">Ulthwé Farseer</t>
+    <t xml:space="preserve">Warsong Revenant</t>
   </si>
   <si>
     <t xml:space="preserve">Ulthwé Army</t>
@@ -590,6 +590,9 @@
     <t xml:space="preserve">Manifestations of the Deepwood</t>
   </si>
   <si>
+    <t xml:space="preserve">Farseer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paint</t>
   </si>
   <si>
@@ -629,367 +632,589 @@
     <t xml:space="preserve">Details H2</t>
   </si>
   <si>
+    <t xml:space="preserve">Dark Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Acryl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogue Hobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grimy Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3rd Gen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wine Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaves (up Yellow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afro Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color Punch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Bluegrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra Opaque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Warmgrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Dragon Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair /  Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basilisk Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Army Painter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warpaints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japanese Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold NMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White NMMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daemonette Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citadel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Templar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratling Grime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorgon Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grunge Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturnal Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model (old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mocca Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">British Khaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Charcoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitallier Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xpress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mummy White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Scarlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bold Titanium White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM / W. Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraken Lavender</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wicked Purple</t>
   </si>
   <si>
-    <t xml:space="preserve">Vallejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xpress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afro Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color Punch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whole Wood</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anthracite Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">3rd Gen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dragonfly</t>
   </si>
   <si>
     <t xml:space="preserve">Up NMM</t>
   </si>
   <si>
-    <t xml:space="preserve">Gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basilisk Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Army Painter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warpaints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Wash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Acryl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rogue Hobby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems Main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grimy Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Bluegrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra Opaque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Silver</t>
-  </si>
-  <si>
     <t xml:space="preserve">Heavy Siena</t>
   </si>
   <si>
-    <t xml:space="preserve">Gold NMM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Under gold</t>
   </si>
   <si>
-    <t xml:space="preserve">Heavy Warmgrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Dragon Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninjon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair /  Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kimera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wine Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaves (up Yellow)</t>
+    <t xml:space="preserve">Aquatic Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green NMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lilac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddish Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violed Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drab Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adepticon</t>
   </si>
   <si>
     <t xml:space="preserve">Aethermatic Blue</t>
   </si>
   <si>
-    <t xml:space="preserve">Citadel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aquatic Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green NMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Templar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow Tenebrous</t>
+    <t xml:space="preserve">Corvus Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cygor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burnt Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloth / Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard / NMM Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Plum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gladewyrm</t>
   </si>
   <si>
     <t xml:space="preserve">Bright Green</t>
   </si>
   <si>
-    <t xml:space="preserve">Brown Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model (old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burnt Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloth / Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard / NMM Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corvus Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cygor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leather Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daemonette Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drab Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adepticon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorgon Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grunge Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japanese Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lilac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magenta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Orange Red</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratling Grime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reddish Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White NMMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violed Red</t>
+    <t xml:space="preserve">French Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahara Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sand Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barak-Nar Burgundy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bugman's Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey Seer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jokaero Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel Legion Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wraithbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zandri Dust</t>
   </si>
   <si>
     <t xml:space="preserve">Aldeari Emerald</t>
   </si>
   <si>
+    <t xml:space="preserve">Gore-Grunta Fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nazdreg Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartacci Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danilo Cartacci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobalt Bluegreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp. Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Yellow Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flameon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbarian Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charred Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elfic Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scrofulous Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Succubus Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toxic Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warlock Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Violed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquitex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparent Raw Umber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivid Lime Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorn Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulthuan Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ushabti Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metallic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Scales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck Tan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middlestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone Grey</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aluminium</t>
   </si>
   <si>
     <t xml:space="preserve">Model Air (old)</t>
   </si>
   <si>
-    <t xml:space="preserve">Armor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barak-Nar Burgundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbarian Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beige Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Scales</t>
+    <t xml:space="preserve">Dark Hot Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultramarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carroburg Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reikland Fleshshade</t>
   </si>
   <si>
     <t xml:space="preserve">Bold Pyrrole Red</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Yellow Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flameon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">British Khaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bugman's Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carroburg Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartacci Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danilo Cartacci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charred Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobalt Bluegreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp. Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Hot Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Plum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gladewyrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck Tan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Magenta</t>
+    <t xml:space="preserve">Doomfire Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexed Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weird Elixir</t>
   </si>
   <si>
     <t xml:space="preserve">Deep Purple</t>
@@ -998,480 +1223,369 @@
     <t xml:space="preserve">Skin / Leaves / Gems</t>
   </si>
   <si>
-    <t xml:space="preserve">Doomfire Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorn Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elfic Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evil Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Olive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gore-Grunta Fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey Seer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexed Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospitallier Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jade Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jokaero Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Middlestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midnight Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mocca Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mummy White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Violed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquitex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nazdreg Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nocturnal Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reikland Fleshshade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahara Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sand Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scarlet Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scrofulous Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel Legion Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Succubus Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toxic Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transparent Raw Umber</t>
-  </si>
-  <si>
     <t xml:space="preserve">Twilight Rose</t>
   </si>
   <si>
-    <t xml:space="preserve">Ulthuan Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultramarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ushabti Bone</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vampiric Purple</t>
   </si>
   <si>
-    <t xml:space="preserve">Vivid Lime Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volcanic Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warlock Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weird Elixir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metallic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wraithbone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zandri Dust</t>
+    <t xml:space="preserve">Deep Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hull Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistachio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purulent Yellow</t>
   </si>
   <si>
     <t xml:space="preserve">Abaddon Black</t>
   </si>
   <si>
+    <t xml:space="preserve">Averland Sunset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celestra Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corax White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gal Vorbak Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incubi Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khorne Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macragge Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mephiston Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morghast Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mournfang Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenician Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rakarth Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhinox Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screamer Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thousand Sons blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XV-88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apothecary White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryph-Charger Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryph-Hound Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iyanden Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeleton Horde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snakebite Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volupus Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caucasian Skintone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiwi Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samurai Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alizarin Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diarylide Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honey Moon Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mars Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluidine Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultramarine Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Goldbrown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronze Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghost Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game (old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghost Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scorpena Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naphthol Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalocyanine Blue (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titanium White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow Medium Azo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asphalt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiery Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale 75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chesnut</t>
+  </si>
+  <si>
     <t xml:space="preserve">Administratum Grey</t>
   </si>
   <si>
+    <t xml:space="preserve">Baharroth Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Reaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dawnstone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor's Children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Sunz Scarlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenrisian Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Dragon Bright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash Gitz Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabalite Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakophoni Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moot Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phalanx Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pink Horror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squig Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sybarite Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temple Guard Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thunderhawk Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trollslayer Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild Rider Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yriel Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Pisarski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fallen Grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron Hue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morning Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun Ray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basalt Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Blue Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Sea Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ger. C. Beige WWII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luftwafe Unif. WWII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pale Grey Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prussian Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Skin tone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunset Red</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agrax Earthshade</t>
   </si>
   <si>
-    <t xml:space="preserve">Alizarin Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apothecary White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asphalt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nocturna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Averland Sunset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baharroth Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basalt Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale 75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bold Titanium White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM / W. Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronze Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown Beast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carbon Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caucasian Skintone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celestra Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chesnut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Sky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Pisarski</t>
+    <t xml:space="preserve">Drakenhof Nightshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Druchii Violet</t>
   </si>
   <si>
     <t xml:space="preserve">Cold Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Corax White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Blue Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Reaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Sea Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dawnstone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game (old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Scarlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diarylide Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drakenhof Nightshade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Druchii Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emperor's Children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evil Sunz Scarlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fallen Grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fenrisian Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiery Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Dragon Bright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flash Gitz Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gal Vorbak Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ger. C. Beige WWII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghost Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghost Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graphite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryph-Charger Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryph-Hound Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Charcoal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Goldbrown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honey Moon Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hull Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incubi Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iron Hue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyanden Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabalite Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kakophoni Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khorne Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiwi Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kraken Lavender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luftwafe Unif. WWII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macragge Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mars Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mephiston Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midnight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moot Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morghast Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morning Sky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mournfang Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naphthol Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olive</t>
-  </si>
-  <si>
     <t xml:space="preserve">Orange</t>
   </si>
   <si>
-    <t xml:space="preserve">Oxide Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pale Grey Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Park Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phalanx Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenician Purple</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phthalo Blue G.</t>
   </si>
   <si>
@@ -1481,118 +1595,16 @@
     <t xml:space="preserve">Phthalo Green</t>
   </si>
   <si>
-    <t xml:space="preserve">Phthalocyanine Blue (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pink Horror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pistachio </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prussian Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purulent Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rakarth Flesh</t>
-  </si>
-  <si>
     <t xml:space="preserve">Red</t>
   </si>
   <si>
     <t xml:space="preserve">Red Oxide</t>
   </si>
   <si>
-    <t xml:space="preserve">Rhinox Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samurai Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scorpena Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screamer Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skeleton Horde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snakebite Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squig Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun Ray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunny Skin tone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunset Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sybarite Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temple Guard Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Fang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thousand Sons blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thunderhawk Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titanium White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluidine Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trollslayer Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultramarine Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volupus Pink</t>
-  </si>
-  <si>
     <t xml:space="preserve">Warm Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Wild Rider Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XV-88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow Medium Azo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yellow Oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yriel Yellow</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1615,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="mmm\-yy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1625,12 +1637,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -1731,7 +1737,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1748,10 +1754,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1764,7 +1766,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3249,11 +3251,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="93101161"/>
-        <c:axId val="8498788"/>
+        <c:axId val="77307701"/>
+        <c:axId val="91160261"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="93101161"/>
+        <c:axId val="77307701"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3285,7 +3287,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8498788"/>
+        <c:crossAx val="91160261"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3293,7 +3295,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8498788"/>
+        <c:axId val="91160261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3332,7 +3334,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93101161"/>
+        <c:crossAx val="77307701"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3373,9 +3375,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>622440</xdr:colOff>
+      <xdr:colOff>622080</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>25200</xdr:rowOff>
+      <xdr:rowOff>24840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3383,8 +3385,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7723080" y="7038360"/>
-        <a:ext cx="7510680" cy="3179160"/>
+        <a:off x="7723080" y="7024320"/>
+        <a:ext cx="7510320" cy="3178800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3439,8 +3441,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:P250" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:P250"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:P251" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:P251"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Paint"/>
     <tableColumn id="2" name="Brand"/>
@@ -3657,7 +3659,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1193"/>
+  <dimension ref="A1:J1194"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.67"/>
@@ -3716,8 +3718,8 @@
         <v>11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <f aca="false">SUM(C2:C1030)</f>
-        <v>551</v>
+        <f aca="false">SUM(C2:C1031)</f>
+        <v>552</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -3772,7 +3774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>43466</v>
       </c>
@@ -3791,7 +3793,7 @@
       <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
@@ -3868,7 +3870,7 @@
       </c>
       <c r="H8" s="1" t="str">
         <f aca="false">INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 1), Paints!D:D, 0))</f>
-        <v>Afro Shadow</v>
+        <v>Dark Turquoise</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>29</v>
@@ -3895,7 +3897,7 @@
       </c>
       <c r="H9" s="2" t="str">
         <f aca="false" t="array" ref="H9:H9">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 2), ROW(Paints!D:D), ""), 2)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 3), Paints!D:D, 0)))</f>
-        <v>Anthracite Grey</v>
+        <v>Wine Red</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>20</v>
@@ -3922,7 +3924,7 @@
       </c>
       <c r="H10" s="2" t="str">
         <f aca="false" t="array" ref="H10:H10">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 3), ROW(Paints!D:D), ""), 3)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 4), Paints!D:D, 0)))</f>
-        <v>Basilisk Red</v>
+        <v>Afro Shadow</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>33</v>
@@ -3949,7 +3951,7 @@
       </c>
       <c r="H11" s="2" t="str">
         <f aca="false" t="array" ref="H11:H11">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 4), ROW(Paints!D:D), ""), 4)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 5), Paints!D:D, 0)))</f>
-        <v>Dark Turquoise</v>
+        <v>Dragon Blood</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>35</v>
@@ -3976,7 +3978,7 @@
       </c>
       <c r="H12" s="2" t="str">
         <f aca="false" t="array" ref="H12:H12">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 5), ROW(Paints!D:D), ""), 5)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 6), Paints!D:D, 0)))</f>
-        <v>Dragon Blood</v>
+        <v>Heavy Bluegrey</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4121,7 +4123,7 @@
       <c r="F19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4144,7 +4146,7 @@
       <c r="F20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4167,7 +4169,7 @@
       <c r="F21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4190,7 +4192,7 @@
       <c r="F22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4213,7 +4215,7 @@
       <c r="F23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="6" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4236,7 +4238,7 @@
       <c r="F24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
@@ -4257,7 +4259,7 @@
       <c r="F25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
@@ -4278,7 +4280,7 @@
       <c r="F26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="7"/>
+      <c r="H26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
@@ -7091,67 +7093,84 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B184" s="2"/>
+        <v>45809</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B185" s="2"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B186" s="2"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B187" s="2"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B188" s="2"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B189" s="2"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B190" s="2"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B191" s="2"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B192" s="2"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B193" s="2"/>
+    </row>
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B193" s="2"/>
-    </row>
-    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B194" s="2"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10150,6 +10169,9 @@
     </row>
     <row r="1193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1193" s="2"/>
+    </row>
+    <row r="1194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1194" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J11 B2:B1048576">
@@ -10185,7 +10207,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1193" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1194" type="list">
       <formula1>$J$2:$J$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10214,10 +10236,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P250"/>
+  <dimension ref="A1:P251"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="19.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="19.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.07"/>
@@ -10234,115 +10256,103 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>189</v>
+      <c r="A1" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>202</v>
+      <c r="A2" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>205</v>
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>206</v>
+      <c r="A3" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10352,60 +10362,60 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="C4" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
         <v>3</v>
       </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>217</v>
+      <c r="A5" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>219</v>
@@ -10424,108 +10434,90 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>222</v>
+      <c r="A6" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>224</v>
+      <c r="A7" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
         <v>3</v>
       </c>
+      <c r="E7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="K7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10535,30 +10527,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>232</v>
+      <c r="A9" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10568,30 +10560,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>235</v>
+      <c r="A10" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10601,256 +10593,250 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>238</v>
+      <c r="A11" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
         <v>3</v>
       </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>240</v>
+        <v>216</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>241</v>
+      <c r="A12" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
         <v>3</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>242</v>
+      <c r="E12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>244</v>
+        <v>221</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>245</v>
+      <c r="A13" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>248</v>
+      <c r="A14" s="7" t="s">
+        <v>251</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>220</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
         <v>2</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>216</v>
+      <c r="E16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>258</v>
+      <c r="A17" s="7" t="s">
+        <v>259</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
-        <v>2</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>231</v>
+        <v>3</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>259</v>
+      <c r="A18" s="7" t="s">
+        <v>262</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
-        <v>2</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>260</v>
+        <v>3</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
@@ -10860,119 +10846,122 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>262</v>
+      <c r="A19" s="7" t="s">
+        <v>263</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
         <v>2</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>1</v>
+      <c r="E19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>264</v>
+      <c r="A20" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
         <v>2</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="E20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>228</v>
+      <c r="M20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>265</v>
+      <c r="A21" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
         <v>2</v>
       </c>
+      <c r="E21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="M21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>268</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
         <v>2</v>
       </c>
-      <c r="K22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>271</v>
+      <c r="E22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>272</v>
+      <c r="A23" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -10982,876 +10971,1231 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>273</v>
+      <c r="A24" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
         <v>2</v>
       </c>
+      <c r="E24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="K24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>1</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>274</v>
+      <c r="A25" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
         <v>2</v>
       </c>
-      <c r="K25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>276</v>
+      <c r="E25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>277</v>
+      <c r="A26" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
-        <v>2</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>278</v>
+        <v>1</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>279</v>
+      <c r="A27" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>280</v>
+        <v>228</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
-        <v>2</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="O27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>281</v>
-      </c>
       <c r="B28" s="2" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
-        <v>2</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>276</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>282</v>
+      <c r="A29" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
-        <v>2</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>276</v>
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>283</v>
+      <c r="A30" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
-        <v>2</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="O30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>239</v>
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>284</v>
+      <c r="A31" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>215</v>
+        <v>282</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>285</v>
+      <c r="A32" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>286</v>
+      <c r="A33" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>251</v>
+        <v>282</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>287</v>
+      <c r="A34" s="7" t="s">
+        <v>283</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>228</v>
+        <v>282</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>288</v>
+      <c r="A35" s="7" t="s">
+        <v>284</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>233</v>
+        <v>282</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
-        <v>290</v>
+      <c r="A36" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
-        <v>292</v>
+      <c r="A37" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>242</v>
+        <v>282</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>294</v>
+      <c r="A38" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>243</v>
+        <v>282</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>267</v>
+        <v>290</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
-        <v>295</v>
+      <c r="A39" s="7" t="s">
+        <v>291</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>216</v>
+        <v>282</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>296</v>
+      <c r="A40" s="7" t="s">
+        <v>292</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>297</v>
+        <v>244</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>299</v>
+      <c r="A41" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
-        <v>1</v>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>300</v>
+      <c r="A42" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>234</v>
+        <v>295</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
-        <v>301</v>
+      <c r="A43" s="7" t="s">
+        <v>297</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="M43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>51</v>
+      <c r="A44" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>303</v>
+      <c r="A45" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>301</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>220</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
-        <v>305</v>
+      <c r="A46" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>306</v>
+        <v>212</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
-        <v>1</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>210</v>
+        <v>2</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
-        <v>307</v>
+      <c r="A47" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
-        <v>1</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>210</v>
+        <v>2</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>308</v>
+      <c r="A48" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>309</v>
+      <c r="A49" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>310</v>
+        <v>212</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
-        <v>1</v>
-      </c>
-      <c r="O49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>220</v>
+        <v>2</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
-        <v>311</v>
+      <c r="A50" s="7" t="s">
+        <v>307</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>313</v>
+      <c r="A51" s="7" t="s">
+        <v>309</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
-        <v>1</v>
-      </c>
-      <c r="K51" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>234</v>
+        <v>2</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
-        <v>314</v>
+      <c r="A52" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
-        <v>1</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>316</v>
+        <v>2</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
-        <v>317</v>
+      <c r="A53" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>228</v>
+        <v>312</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
-        <v>318</v>
+      <c r="A54" s="7" t="s">
+        <v>313</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
         <v>2</v>
       </c>
-      <c r="G54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>320</v>
+      <c r="M54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="s">
-        <v>321</v>
+      <c r="A55" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>252</v>
+        <v>316</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
-        <v>322</v>
+      <c r="A56" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>267</v>
+      <c r="L56" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="s">
-        <v>323</v>
+      <c r="A57" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>324</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
-        <v>325</v>
+      <c r="A58" s="7" t="s">
+        <v>322</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>326</v>
+        <v>208</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
-        <v>327</v>
+      <c r="A59" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>328</v>
+        <v>212</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
         <v>1</v>
       </c>
-      <c r="K59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>329</v>
+      <c r="G59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="s">
-        <v>330</v>
+      <c r="A60" s="7" t="s">
+        <v>324</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
@@ -11861,39 +12205,39 @@
         <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>331</v>
+      <c r="A61" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
         <v>1</v>
       </c>
-      <c r="K61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>332</v>
+      <c r="O61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8" t="s">
-        <v>333</v>
+      <c r="A62" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
@@ -11903,60 +12247,60 @@
         <v>1</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="8" t="s">
-        <v>334</v>
+      <c r="A63" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
         <v>1</v>
       </c>
-      <c r="G63" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>237</v>
+      <c r="O63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="8" t="s">
-        <v>335</v>
+      <c r="A64" s="7" t="s">
+        <v>329</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>336</v>
+        <v>212</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
         <v>1</v>
       </c>
-      <c r="O64" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>298</v>
+      <c r="M64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="8" t="s">
-        <v>337</v>
+      <c r="A65" s="7" t="s">
+        <v>330</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
@@ -11966,39 +12310,42 @@
         <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="8" t="s">
-        <v>338</v>
+      <c r="A66" s="7" t="s">
+        <v>331</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
         <v>1</v>
       </c>
+      <c r="H66" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="O66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>239</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="8" t="s">
-        <v>339</v>
+      <c r="A67" s="7" t="s">
+        <v>332</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -12007,16 +12354,19 @@
       <c r="M67" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="N67" s="2" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="8" t="s">
-        <v>340</v>
+      <c r="A68" s="7" t="s">
+        <v>333</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -12026,39 +12376,39 @@
         <v>1</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="8" t="s">
-        <v>341</v>
+      <c r="A69" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
         <v>1</v>
       </c>
-      <c r="K69" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="2" t="s">
+      <c r="M69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -12068,165 +12418,162 @@
         <v>1</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>343</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="8" t="s">
-        <v>344</v>
+      <c r="A71" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
         <v>1</v>
       </c>
-      <c r="E71" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>345</v>
+      <c r="O71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8" t="s">
-        <v>346</v>
+      <c r="A72" s="7" t="s">
+        <v>337</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
         <v>1</v>
       </c>
-      <c r="K72" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>332</v>
+      <c r="O72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
-        <v>347</v>
+      <c r="A73" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
         <v>1</v>
       </c>
-      <c r="M73" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" s="2" t="s">
-        <v>210</v>
+      <c r="G73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8" t="s">
-        <v>348</v>
+      <c r="A74" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
         <v>1</v>
       </c>
-      <c r="K74" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>289</v>
+      <c r="M74" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="8" t="s">
-        <v>349</v>
+      <c r="A75" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
         <v>1</v>
       </c>
-      <c r="K75" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>329</v>
+      <c r="O75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="8" t="s">
-        <v>350</v>
+      <c r="A76" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
         <v>1</v>
       </c>
-      <c r="K76" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>252</v>
+      <c r="O76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="8" t="s">
-        <v>351</v>
+      <c r="A77" s="7" t="s">
+        <v>343</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>223</v>
+        <v>344</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
         <v>1</v>
       </c>
-      <c r="K77" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>332</v>
+      <c r="I77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8" t="s">
-        <v>352</v>
+      <c r="A78" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12236,102 +12583,102 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8" t="s">
-        <v>353</v>
+      <c r="A79" s="7" t="s">
+        <v>347</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
         <v>1</v>
       </c>
-      <c r="E79" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>354</v>
+      <c r="K79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="8" t="s">
-        <v>355</v>
+      <c r="A80" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>356</v>
+        <v>238</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
         <v>1</v>
       </c>
-      <c r="G80" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>358</v>
+      <c r="K80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8" t="s">
-        <v>359</v>
+      <c r="A81" s="7" t="s">
+        <v>349</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
         <v>1</v>
       </c>
-      <c r="O81" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" s="2" t="s">
-        <v>335</v>
+      <c r="K81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="8" t="s">
-        <v>360</v>
+      <c r="A82" s="7" t="s">
+        <v>350</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>223</v>
+        <v>351</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
         <v>1</v>
       </c>
-      <c r="M82" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>220</v>
+      <c r="G82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="8" t="s">
-        <v>361</v>
+      <c r="A83" s="7" t="s">
+        <v>352</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
@@ -12341,18 +12688,18 @@
         <v>1</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="8" t="s">
-        <v>362</v>
+      <c r="A84" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
@@ -12362,18 +12709,18 @@
         <v>1</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8" t="s">
-        <v>363</v>
+      <c r="A85" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12383,102 +12730,102 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="8" t="s">
-        <v>364</v>
+      <c r="A86" s="7" t="s">
+        <v>355</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
         <v>1</v>
       </c>
-      <c r="O86" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" s="2" t="s">
-        <v>267</v>
+      <c r="K86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="8" t="s">
-        <v>365</v>
+      <c r="A87" s="7" t="s">
+        <v>356</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
         <v>1</v>
       </c>
-      <c r="O87" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" s="2" t="s">
-        <v>239</v>
+      <c r="K87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="8" t="s">
-        <v>366</v>
+      <c r="A88" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
         <v>1</v>
       </c>
-      <c r="M88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" s="2" t="s">
-        <v>215</v>
+      <c r="K88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8" t="s">
-        <v>367</v>
+      <c r="A89" s="7" t="s">
+        <v>359</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
         <v>1</v>
       </c>
-      <c r="M89" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>220</v>
+      <c r="K89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="8" t="s">
-        <v>368</v>
+      <c r="A90" s="7" t="s">
+        <v>360</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
@@ -12488,39 +12835,39 @@
         <v>1</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="8" t="s">
-        <v>369</v>
+      <c r="A91" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>336</v>
+        <v>260</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
         <v>1</v>
       </c>
-      <c r="O91" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" s="2" t="s">
-        <v>298</v>
+      <c r="M91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="8" t="s">
-        <v>370</v>
+      <c r="A92" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12530,18 +12877,18 @@
         <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="8" t="s">
-        <v>371</v>
+      <c r="A93" s="7" t="s">
+        <v>363</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
@@ -12551,60 +12898,60 @@
         <v>1</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>289</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="8" t="s">
-        <v>372</v>
+      <c r="A94" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
         <v>1</v>
       </c>
-      <c r="K94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>252</v>
+      <c r="G94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="8" t="s">
-        <v>373</v>
+      <c r="A95" s="7" t="s">
+        <v>367</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>223</v>
+        <v>286</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
         <v>1</v>
       </c>
-      <c r="M95" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" s="2" t="s">
-        <v>276</v>
+      <c r="G95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="8" t="s">
-        <v>374</v>
+      <c r="A96" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>223</v>
+        <v>286</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
@@ -12614,102 +12961,102 @@
         <v>1</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>260</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="8" t="s">
-        <v>375</v>
+      <c r="A97" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
         <v>1</v>
       </c>
-      <c r="G97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>276</v>
+      <c r="K97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="8" t="s">
-        <v>376</v>
+      <c r="A98" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>204</v>
+        <v>370</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>358</v>
+      <c r="M98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="8" t="s">
-        <v>377</v>
+      <c r="A99" s="7" t="s">
+        <v>372</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
         <v>1</v>
       </c>
-      <c r="M99" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>291</v>
+      <c r="O99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="8" t="s">
-        <v>378</v>
+      <c r="A100" s="7" t="s">
+        <v>247</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>226</v>
+        <v>373</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
         <v>1</v>
       </c>
-      <c r="K100" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>228</v>
+      <c r="O100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="8" t="s">
-        <v>379</v>
+      <c r="A101" s="7" t="s">
+        <v>375</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
@@ -12719,60 +13066,60 @@
         <v>1</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>233</v>
+        <v>374</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="8" t="s">
-        <v>380</v>
+      <c r="A102" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>204</v>
+        <v>377</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
         <v>1</v>
       </c>
-      <c r="K102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>267</v>
+      <c r="O102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="8" t="s">
-        <v>381</v>
+      <c r="A103" s="7" t="s">
+        <v>378</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>356</v>
+        <v>227</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>357</v>
+        <v>268</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
         <v>1</v>
       </c>
-      <c r="K103" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>228</v>
+      <c r="O103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="8" t="s">
-        <v>382</v>
+      <c r="A104" s="7" t="s">
+        <v>380</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -12782,18 +13129,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>329</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="8" t="s">
-        <v>383</v>
+      <c r="A105" s="7" t="s">
+        <v>381</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -12803,18 +13150,18 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="8" t="s">
-        <v>384</v>
+      <c r="A106" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>219</v>
+        <v>268</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
@@ -12824,60 +13171,60 @@
         <v>1</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>326</v>
+        <v>241</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="8" t="s">
-        <v>385</v>
+      <c r="A107" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>386</v>
+        <v>268</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
         <v>1</v>
       </c>
-      <c r="O107" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" s="2" t="s">
-        <v>298</v>
+      <c r="K107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="8" t="s">
-        <v>387</v>
+      <c r="A108" s="7" t="s">
+        <v>384</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
         <v>1</v>
       </c>
-      <c r="O108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" s="2" t="s">
-        <v>233</v>
+      <c r="K108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="8" t="s">
-        <v>388</v>
+      <c r="A109" s="7" t="s">
+        <v>385</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>252</v>
+        <v>386</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
@@ -12887,198 +13234,270 @@
         <v>1</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>233</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="8" t="s">
-        <v>389</v>
+      <c r="A110" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="8" t="s">
-        <v>390</v>
+      <c r="A111" s="7" t="s">
+        <v>387</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>328</v>
+        <v>205</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="8" t="s">
-        <v>391</v>
+      <c r="A112" s="7" t="s">
+        <v>388</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="8" t="s">
-        <v>392</v>
+      <c r="A113" s="7" t="s">
+        <v>389</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>315</v>
+        <v>390</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="8" t="s">
-        <v>393</v>
+      <c r="A114" s="7" t="s">
+        <v>391</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>257</v>
+        <v>390</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="8" t="s">
-        <v>394</v>
+      <c r="A115" s="7" t="s">
+        <v>392</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>395</v>
+        <v>204</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>357</v>
+        <v>289</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="8" t="s">
-        <v>396</v>
+      <c r="A116" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="8" t="s">
-        <v>397</v>
+      <c r="A117" s="7" t="s">
+        <v>395</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>328</v>
+        <v>244</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="8" t="s">
-        <v>398</v>
+      <c r="A118" s="7" t="s">
+        <v>397</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>328</v>
+        <v>244</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="8" t="s">
-        <v>399</v>
+      <c r="A119" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="7" t="s">
         <v>400</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>401</v>
+        <v>227</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>357</v>
+        <v>278</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="8" t="s">
-        <v>400</v>
+      <c r="A121" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="8" t="s">
-        <v>402</v>
+      <c r="A122" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
@@ -13086,116 +13505,44 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="8" t="s">
-        <v>403</v>
+      <c r="A123" s="7" t="s">
+        <v>402</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="8" t="s">
-        <v>45</v>
+      <c r="A124" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="s">
+    </row>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="M124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="8" t="s">
-        <v>405</v>
-      </c>
       <c r="B125" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13203,14 +13550,14 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="8" t="s">
-        <v>406</v>
+      <c r="A126" s="7" t="s">
+        <v>405</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>395</v>
+        <v>211</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>357</v>
+        <v>212</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13218,14 +13565,14 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="8" t="s">
-        <v>407</v>
+      <c r="A127" s="7" t="s">
+        <v>406</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>356</v>
+        <v>211</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>408</v>
+        <v>212</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -13233,14 +13580,14 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="8" t="s">
+      <c r="A128" s="7" t="s">
         <v>407</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
@@ -13248,14 +13595,14 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="8" t="s">
-        <v>409</v>
+      <c r="A129" s="7" t="s">
+        <v>408</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>312</v>
+        <v>241</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -13263,14 +13610,14 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="8" t="s">
-        <v>410</v>
+      <c r="A130" s="7" t="s">
+        <v>409</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -13278,14 +13625,14 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="8" t="s">
-        <v>411</v>
+      <c r="A131" s="7" t="s">
+        <v>410</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>401</v>
+        <v>252</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>357</v>
+        <v>241</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
@@ -13293,14 +13640,14 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="8" t="s">
-        <v>412</v>
+      <c r="A132" s="7" t="s">
+        <v>411</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>413</v>
+        <v>241</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -13308,14 +13655,14 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="8" t="s">
-        <v>414</v>
+      <c r="A133" s="7" t="s">
+        <v>412</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -13323,14 +13670,14 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="8" t="s">
-        <v>415</v>
+      <c r="A134" s="7" t="s">
+        <v>413</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13338,14 +13685,14 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="8" t="s">
-        <v>416</v>
+      <c r="A135" s="7" t="s">
+        <v>414</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13353,14 +13700,14 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="8" t="s">
-        <v>417</v>
+      <c r="A136" s="7" t="s">
+        <v>415</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>315</v>
+        <v>241</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13368,14 +13715,14 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="8" t="s">
-        <v>418</v>
+      <c r="A137" s="7" t="s">
+        <v>416</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13383,14 +13730,14 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="8" t="s">
-        <v>419</v>
+      <c r="A138" s="7" t="s">
+        <v>417</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13398,14 +13745,14 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="8" t="s">
-        <v>420</v>
+      <c r="A139" s="7" t="s">
+        <v>418</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13413,14 +13760,14 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="8" t="s">
-        <v>421</v>
+      <c r="A140" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>422</v>
+        <v>241</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13428,14 +13775,14 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="8" t="s">
-        <v>323</v>
+      <c r="A141" s="7" t="s">
+        <v>420</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13443,65 +13790,29 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="8" t="s">
-        <v>423</v>
+      <c r="A142" s="7" t="s">
+        <v>421</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>395</v>
+        <v>252</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>357</v>
+        <v>241</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
         <v>0</v>
       </c>
-      <c r="E142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="8" t="s">
-        <v>424</v>
+      <c r="A143" s="7" t="s">
+        <v>422</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13509,14 +13820,14 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="8" t="s">
-        <v>425</v>
+      <c r="A144" s="7" t="s">
+        <v>423</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>315</v>
+        <v>241</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
@@ -13524,14 +13835,14 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="8" t="s">
-        <v>426</v>
+      <c r="A145" s="7" t="s">
+        <v>424</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13539,14 +13850,14 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="8" t="s">
-        <v>427</v>
+      <c r="A146" s="7" t="s">
+        <v>425</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13554,14 +13865,14 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="8" t="s">
-        <v>428</v>
+      <c r="A147" s="7" t="s">
+        <v>426</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13569,14 +13880,14 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="8" t="s">
-        <v>429</v>
+      <c r="A148" s="7" t="s">
+        <v>427</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13584,14 +13895,14 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="8" t="s">
-        <v>430</v>
+      <c r="A149" s="7" t="s">
+        <v>428</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>413</v>
+        <v>255</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
@@ -13599,14 +13910,14 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="8" t="s">
-        <v>431</v>
+      <c r="A150" s="7" t="s">
+        <v>429</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13614,14 +13925,14 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="8" t="s">
-        <v>432</v>
+      <c r="A151" s="7" t="s">
+        <v>430</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>395</v>
+        <v>252</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>357</v>
+        <v>255</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13629,14 +13940,14 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="8" t="s">
-        <v>433</v>
+      <c r="A152" s="7" t="s">
+        <v>431</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13644,14 +13955,14 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="8" t="s">
-        <v>434</v>
+      <c r="A153" s="7" t="s">
+        <v>432</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13659,14 +13970,14 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="8" t="s">
-        <v>435</v>
+      <c r="A154" s="7" t="s">
+        <v>433</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>252</v>
+        <v>342</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13674,14 +13985,14 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="8" t="s">
-        <v>436</v>
+      <c r="A155" s="7" t="s">
+        <v>434</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13689,14 +14000,14 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="8" t="s">
-        <v>437</v>
+      <c r="A156" s="7" t="s">
+        <v>435</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>223</v>
+        <v>342</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13704,14 +14015,14 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="8" t="s">
-        <v>438</v>
+      <c r="A157" s="7" t="s">
+        <v>436</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>422</v>
+        <v>342</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13719,14 +14030,14 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="8" t="s">
-        <v>439</v>
+      <c r="A158" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>223</v>
+        <v>342</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13734,14 +14045,14 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="8" t="s">
-        <v>440</v>
+      <c r="A159" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13749,14 +14060,14 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="8" t="s">
-        <v>441</v>
+      <c r="A160" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>213</v>
+        <v>344</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13764,14 +14075,14 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="8" t="s">
-        <v>442</v>
+      <c r="A161" s="7" t="s">
+        <v>439</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13779,14 +14090,14 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="8" t="s">
-        <v>443</v>
+      <c r="A162" s="7" t="s">
+        <v>440</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13794,14 +14105,14 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="8" t="s">
-        <v>444</v>
+      <c r="A163" s="7" t="s">
+        <v>441</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>257</v>
+        <v>344</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -13809,14 +14120,14 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="8" t="s">
-        <v>445</v>
+      <c r="A164" s="7" t="s">
+        <v>442</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>257</v>
+        <v>344</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -13824,14 +14135,14 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="8" t="s">
-        <v>446</v>
+      <c r="A165" s="7" t="s">
+        <v>406</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -13839,14 +14150,14 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="8" t="s">
-        <v>447</v>
+      <c r="A166" s="7" t="s">
+        <v>443</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -13854,14 +14165,14 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="8" t="s">
-        <v>448</v>
+      <c r="A167" s="7" t="s">
+        <v>444</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -13869,14 +14180,14 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="8" t="s">
-        <v>449</v>
+      <c r="A168" s="7" t="s">
+        <v>445</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -13884,14 +14195,14 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="8" t="s">
-        <v>450</v>
+      <c r="A169" s="7" t="s">
+        <v>446</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -13899,65 +14210,29 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="8" t="s">
-        <v>451</v>
+      <c r="A170" s="7" t="s">
+        <v>447</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
         <v>0</v>
       </c>
-      <c r="E170" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G170" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I170" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J170" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K170" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M170" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N170" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O170" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="8" t="s">
-        <v>452</v>
+      <c r="A171" s="7" t="s">
+        <v>448</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -13965,14 +14240,14 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="8" t="s">
-        <v>453</v>
+      <c r="A172" s="7" t="s">
+        <v>449</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>413</v>
+        <v>260</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -13980,14 +14255,14 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="8" t="s">
-        <v>454</v>
+      <c r="A173" s="7" t="s">
+        <v>450</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -13995,65 +14270,29 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="8" t="s">
-        <v>454</v>
+      <c r="A174" s="7" t="s">
+        <v>451</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>304</v>
+        <v>452</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
         <v>0</v>
       </c>
-      <c r="E174" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G174" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I174" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K174" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M174" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N174" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O174" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="8" t="s">
-        <v>455</v>
+      <c r="A175" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>257</v>
+        <v>452</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14061,14 +14300,14 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="8" t="s">
-        <v>456</v>
+      <c r="A176" s="7" t="s">
+        <v>454</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>328</v>
+        <v>452</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14076,14 +14315,14 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="8" t="s">
-        <v>457</v>
+      <c r="A177" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>256</v>
+        <v>365</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>328</v>
+        <v>456</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14091,14 +14330,14 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="8" t="s">
-        <v>458</v>
+      <c r="A178" s="7" t="s">
+        <v>457</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>256</v>
+        <v>365</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14106,14 +14345,14 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="8" t="s">
-        <v>459</v>
+      <c r="A179" s="7" t="s">
+        <v>458</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>249</v>
+        <v>365</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -14121,167 +14360,59 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="8" t="s">
-        <v>460</v>
+      <c r="A180" s="7" t="s">
+        <v>459</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
         <v>0</v>
       </c>
-      <c r="E180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="8" t="s">
-        <v>50</v>
+      <c r="A181" s="7" t="s">
+        <v>460</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>207</v>
+        <v>365</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>213</v>
+        <v>286</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
         <v>0</v>
       </c>
-      <c r="E181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="8" t="s">
-        <v>47</v>
+      <c r="A182" s="7" t="s">
+        <v>461</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>207</v>
+        <v>365</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>213</v>
+        <v>286</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
         <v>0</v>
       </c>
-      <c r="E182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="8" t="s">
-        <v>461</v>
+      <c r="A183" s="7" t="s">
+        <v>462</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -14289,14 +14420,14 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="8" t="s">
-        <v>462</v>
+      <c r="A184" s="7" t="s">
+        <v>463</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>207</v>
+        <v>365</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>213</v>
+        <v>286</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -14304,14 +14435,14 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="8" t="s">
-        <v>463</v>
+      <c r="A185" s="7" t="s">
+        <v>464</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>256</v>
+        <v>365</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -14319,14 +14450,14 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="8" t="s">
-        <v>464</v>
+      <c r="A186" s="7" t="s">
+        <v>465</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14334,14 +14465,14 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="8" t="s">
-        <v>465</v>
+      <c r="A187" s="7" t="s">
+        <v>466</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14349,14 +14480,14 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="8" t="s">
-        <v>466</v>
+      <c r="A188" s="7" t="s">
+        <v>467</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>395</v>
+        <v>285</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14364,14 +14495,14 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="8" t="s">
-        <v>467</v>
+      <c r="A189" s="7" t="s">
+        <v>468</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>328</v>
+        <v>286</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14379,14 +14510,14 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="8" t="s">
-        <v>468</v>
+      <c r="A190" s="7" t="s">
+        <v>469</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14394,14 +14525,14 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="8" t="s">
-        <v>469</v>
+      <c r="A191" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>413</v>
+        <v>286</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14409,14 +14540,14 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="8" t="s">
-        <v>470</v>
+      <c r="A192" s="7" t="s">
+        <v>471</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14424,14 +14555,14 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="8" t="s">
-        <v>471</v>
+      <c r="A193" s="7" t="s">
+        <v>472</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>356</v>
+        <v>473</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
@@ -14439,14 +14570,14 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="8" t="s">
-        <v>472</v>
+      <c r="A194" s="7" t="s">
+        <v>474</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>356</v>
+        <v>473</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
@@ -14454,14 +14585,14 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="8" t="s">
+      <c r="A195" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="C195" s="2" t="s">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14469,14 +14600,14 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="8" t="s">
-        <v>474</v>
+      <c r="A196" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
@@ -14484,14 +14615,14 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="8" t="s">
-        <v>475</v>
+      <c r="A197" s="7" t="s">
+        <v>476</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
@@ -14499,14 +14630,14 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="8" t="s">
-        <v>476</v>
+      <c r="A198" s="7" t="s">
+        <v>477</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>395</v>
+        <v>252</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
@@ -14514,14 +14645,14 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="8" t="s">
-        <v>477</v>
+      <c r="A199" s="7" t="s">
+        <v>478</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14529,14 +14660,14 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="8" t="s">
-        <v>478</v>
+      <c r="A200" s="7" t="s">
+        <v>479</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14544,14 +14675,14 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="8" t="s">
-        <v>479</v>
+      <c r="A201" s="7" t="s">
+        <v>480</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>266</v>
+        <v>370</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
@@ -14559,14 +14690,14 @@
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="8" t="s">
-        <v>480</v>
+      <c r="A202" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>266</v>
+        <v>370</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14574,14 +14705,14 @@
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="8" t="s">
-        <v>481</v>
+      <c r="A203" s="7" t="s">
+        <v>482</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14589,14 +14720,14 @@
       </c>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="8" t="s">
-        <v>482</v>
+      <c r="A204" s="7" t="s">
+        <v>483</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>252</v>
+        <v>370</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14604,14 +14735,14 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="8" t="s">
-        <v>483</v>
+      <c r="A205" s="7" t="s">
+        <v>484</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14619,14 +14750,14 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="8" t="s">
-        <v>484</v>
+      <c r="A206" s="7" t="s">
+        <v>485</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
@@ -14634,14 +14765,14 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="8" t="s">
-        <v>485</v>
+      <c r="A207" s="7" t="s">
+        <v>486</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14649,14 +14780,14 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="8" t="s">
-        <v>486</v>
+      <c r="A208" s="7" t="s">
+        <v>487</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14664,14 +14795,14 @@
       </c>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="8" t="s">
-        <v>487</v>
+      <c r="A209" s="7" t="s">
+        <v>488</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
@@ -14679,14 +14810,14 @@
       </c>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="8" t="s">
-        <v>488</v>
+      <c r="A210" s="7" t="s">
+        <v>489</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>213</v>
+        <v>370</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14694,14 +14825,14 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="8" t="s">
-        <v>489</v>
+      <c r="A211" s="7" t="s">
+        <v>490</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>266</v>
+        <v>370</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14709,14 +14840,14 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="8" t="s">
-        <v>490</v>
+      <c r="A212" s="7" t="s">
+        <v>491</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>213</v>
+        <v>370</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14724,14 +14855,14 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="8" t="s">
-        <v>490</v>
+      <c r="A213" s="7" t="s">
+        <v>492</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14739,14 +14870,14 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="8" t="s">
-        <v>491</v>
+      <c r="A214" s="7" t="s">
+        <v>493</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>213</v>
+        <v>370</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
@@ -14754,14 +14885,14 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="8" t="s">
-        <v>492</v>
+      <c r="A215" s="7" t="s">
+        <v>494</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>252</v>
+        <v>370</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14769,14 +14900,14 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="8" t="s">
-        <v>493</v>
+      <c r="A216" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
@@ -14784,14 +14915,14 @@
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="8" t="s">
-        <v>494</v>
+      <c r="A217" s="7" t="s">
+        <v>496</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
@@ -14799,14 +14930,14 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="8" t="s">
-        <v>495</v>
+      <c r="A218" s="7" t="s">
+        <v>497</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>252</v>
+        <v>498</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14814,14 +14945,14 @@
       </c>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="8" t="s">
-        <v>496</v>
+      <c r="A219" s="7" t="s">
+        <v>499</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>315</v>
+        <v>498</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14829,14 +14960,14 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="8" t="s">
-        <v>497</v>
+      <c r="A220" s="7" t="s">
+        <v>500</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>312</v>
+        <v>498</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14844,14 +14975,14 @@
       </c>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="8" t="s">
+      <c r="A221" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C221" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
@@ -14859,14 +14990,14 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="8" t="s">
-        <v>499</v>
+      <c r="A222" s="7" t="s">
+        <v>502</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>252</v>
+        <v>498</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
@@ -14874,14 +15005,14 @@
       </c>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="8" t="s">
-        <v>292</v>
+      <c r="A223" s="7" t="s">
+        <v>503</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>312</v>
+        <v>498</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -14889,14 +15020,14 @@
       </c>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="8" t="s">
-        <v>500</v>
+      <c r="A224" s="7" t="s">
+        <v>504</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
@@ -14904,14 +15035,14 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="8" t="s">
-        <v>501</v>
+      <c r="A225" s="7" t="s">
+        <v>472</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
@@ -14919,14 +15050,14 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="8" t="s">
-        <v>502</v>
+      <c r="A226" s="7" t="s">
+        <v>505</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
@@ -14934,14 +15065,14 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="8" t="s">
-        <v>503</v>
+      <c r="A227" s="7" t="s">
+        <v>506</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>413</v>
+        <v>268</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -14949,14 +15080,14 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="8" t="s">
-        <v>504</v>
+      <c r="A228" s="7" t="s">
+        <v>507</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -14964,14 +15095,14 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="8" t="s">
-        <v>505</v>
+      <c r="A229" s="7" t="s">
+        <v>508</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -14979,14 +15110,14 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="8" t="s">
-        <v>506</v>
+      <c r="A230" s="7" t="s">
+        <v>509</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -14994,14 +15125,14 @@
       </c>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="8" t="s">
-        <v>507</v>
+      <c r="A231" s="7" t="s">
+        <v>291</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -15009,65 +15140,29 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="8" t="s">
-        <v>53</v>
+      <c r="A232" s="7" t="s">
+        <v>510</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
         <v>0</v>
       </c>
-      <c r="E232" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G232" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I232" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K232" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L232" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M232" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N232" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O232" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P232" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="8" t="s">
-        <v>508</v>
+      <c r="A233" s="7" t="s">
+        <v>511</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -15075,14 +15170,14 @@
       </c>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="8" t="s">
-        <v>509</v>
+      <c r="A234" s="7" t="s">
+        <v>512</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
@@ -15090,14 +15185,14 @@
       </c>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="8" t="s">
-        <v>510</v>
+      <c r="A235" s="7" t="s">
+        <v>513</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
@@ -15105,14 +15200,14 @@
       </c>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="8" t="s">
-        <v>511</v>
+      <c r="A236" s="7" t="s">
+        <v>514</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>356</v>
+        <v>227</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>357</v>
+        <v>268</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
@@ -15120,14 +15215,14 @@
       </c>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="8" t="s">
-        <v>511</v>
+      <c r="A237" s="7" t="s">
+        <v>515</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15135,14 +15230,14 @@
       </c>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="8" t="s">
-        <v>512</v>
+      <c r="A238" s="7" t="s">
+        <v>516</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>315</v>
+        <v>390</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
@@ -15150,14 +15245,14 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="8" t="s">
-        <v>513</v>
+      <c r="A239" s="7" t="s">
+        <v>517</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
@@ -15165,14 +15260,14 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="8" t="s">
-        <v>514</v>
+      <c r="A240" s="7" t="s">
+        <v>518</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>395</v>
+        <v>252</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
@@ -15180,14 +15275,14 @@
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="8" t="s">
-        <v>515</v>
+      <c r="A241" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15195,14 +15290,14 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="8" t="s">
-        <v>516</v>
+      <c r="A242" s="7" t="s">
+        <v>519</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>395</v>
+        <v>238</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
@@ -15210,14 +15305,14 @@
       </c>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="8" t="s">
-        <v>517</v>
+      <c r="A243" s="7" t="s">
+        <v>520</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15225,14 +15320,14 @@
       </c>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="8" t="s">
-        <v>518</v>
+      <c r="A244" s="7" t="s">
+        <v>521</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15240,14 +15335,14 @@
       </c>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="8" t="s">
-        <v>519</v>
+      <c r="A245" s="7" t="s">
+        <v>522</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
@@ -15255,14 +15350,14 @@
       </c>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="8" t="s">
-        <v>234</v>
+      <c r="A246" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15270,14 +15365,14 @@
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="8" t="s">
-        <v>520</v>
+      <c r="A247" s="7" t="s">
+        <v>524</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15285,14 +15380,14 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="8" t="s">
-        <v>521</v>
+      <c r="A248" s="7" t="s">
+        <v>525</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>356</v>
+        <v>238</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15300,14 +15395,14 @@
       </c>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="8" t="s">
-        <v>522</v>
+      <c r="A249" s="7" t="s">
+        <v>463</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15315,17 +15410,32 @@
       </c>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="8" t="s">
-        <v>523</v>
+      <c r="A250" s="7" t="s">
+        <v>526</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
         <v>0</v>
       </c>
     </row>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="547">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -635,6 +635,27 @@
     <t xml:space="preserve">Details H2</t>
   </si>
   <si>
+    <t xml:space="preserve">Dark Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Acryl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogue Hobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems</t>
+  </si>
+  <si>
     <t xml:space="preserve">Afro Shadow</t>
   </si>
   <si>
@@ -665,18 +686,129 @@
     <t xml:space="preserve">Up NMM</t>
   </si>
   <si>
-    <t xml:space="preserve">Gems</t>
+    <t xml:space="preserve">Dragon Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grimy Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japanese Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold NMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wine Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaves (up Yellow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basilisk Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Army Painter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warpaints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Dragon Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair /  Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorgon Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grunge Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluegrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra Opaque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warmgrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Skin</t>
   </si>
   <si>
     <t xml:space="preserve">Aquatic Turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">Leaves</t>
-  </si>
-  <si>
     <t xml:space="preserve">Black Red</t>
   </si>
   <si>
+    <t xml:space="preserve">Shadows</t>
+  </si>
+  <si>
     <t xml:space="preserve">Green NMM</t>
   </si>
   <si>
@@ -686,81 +818,405 @@
     <t xml:space="preserve">British Khaki</t>
   </si>
   <si>
-    <t xml:space="preserve">Gold</t>
+    <t xml:space="preserve">Lilac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddish Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White NMMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violed Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mocca Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aethermatic Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citadel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Templar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corvus Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cygor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daemonette Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratling Grime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Plum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gladewyrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drab Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adepticon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model (old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burnt Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloth / Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard / NMM Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturnal Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahara Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sand Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doomfire Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexed Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weird Elixir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aldeari Emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barak-Nar Burgundy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bugman's Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carroburg Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorn Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gore-Grunta Fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey Seer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jokaero Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nazdreg Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reikland Fleshshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel Legion Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulthuan Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ushabti Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wraithbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zandri Dust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartacci Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danilo Cartacci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobalt Bluegreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp. Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Violed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquitex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparent Raw Umber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivid Lime Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bold Pyrrole Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Yellow Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flameon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Hot Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultramarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metallic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Air (old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbarian Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Scales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charred Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck Tan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Magenta</t>
   </si>
   <si>
     <t xml:space="preserve">Deep Purple</t>
   </si>
   <si>
+    <t xml:space="preserve">Xpress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin / Leaves / Gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elfic Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charcoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitallier Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middlestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mummy White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scrofulous Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Succubus Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toxic Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twilight Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vampiric Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warlock Purple</t>
+  </si>
+  <si>
     <t xml:space="preserve">Deep Violet</t>
   </si>
   <si>
-    <t xml:space="preserve">Dragon Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Olive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold NMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graphite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grimy Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hull Red</t>
   </si>
   <si>
-    <t xml:space="preserve">Japanese Brown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Must</t>
   </si>
   <si>
-    <t xml:space="preserve">Lilac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Luminous Green</t>
   </si>
   <si>
-    <t xml:space="preserve">Luminous Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pistachio </t>
   </si>
   <si>
@@ -770,66 +1226,12 @@
     <t xml:space="preserve">Purulent Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Reddish Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahara Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sand Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White NMMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violed Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Dragon Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volcanic Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wine Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaves (up Yellow)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basilisk Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Army Painter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warpaints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blood Chalice</t>
   </si>
   <si>
     <t xml:space="preserve">Carnelian Skin</t>
   </si>
   <si>
-    <t xml:space="preserve">Doomfire Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lights</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dragon Red</t>
   </si>
   <si>
@@ -842,12 +1244,6 @@
     <t xml:space="preserve">Forbidden Fruit</t>
   </si>
   <si>
-    <t xml:space="preserve">Hexed Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jasper Skin</t>
   </si>
   <si>
@@ -857,21 +1253,12 @@
     <t xml:space="preserve">Leopard Stone Skin</t>
   </si>
   <si>
-    <t xml:space="preserve">Mocca Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Wood</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moldy Wine</t>
   </si>
   <si>
     <t xml:space="preserve">Mulled Berry</t>
   </si>
   <si>
-    <t xml:space="preserve">Onyx Skin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pure Red</t>
   </si>
   <si>
@@ -887,9 +1274,6 @@
     <t xml:space="preserve">Tourmaline Skin</t>
   </si>
   <si>
-    <t xml:space="preserve">Weird Elixir</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wilted Rose</t>
   </si>
   <si>
@@ -899,33 +1283,12 @@
     <t xml:space="preserve">Abaddon Black</t>
   </si>
   <si>
-    <t xml:space="preserve">Citadel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base</t>
-  </si>
-  <si>
     <t xml:space="preserve">Administratum Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">Layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aethermatic Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrast</t>
-  </si>
-  <si>
     <t xml:space="preserve">Agrax Earthshade</t>
   </si>
   <si>
-    <t xml:space="preserve">Shade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aldeari Emerald</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apothecary White</t>
   </si>
   <si>
@@ -938,57 +1301,18 @@
     <t xml:space="preserve">Balor Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Barak-Nar Burgundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Templar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bugman's Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carroburg Crimson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Celestra Grey</t>
   </si>
   <si>
     <t xml:space="preserve">Corax White</t>
   </si>
   <si>
-    <t xml:space="preserve">Corvus Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cygor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leather Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daemonette Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dark Reaper</t>
   </si>
   <si>
     <t xml:space="preserve">Dawnstone</t>
   </si>
   <si>
-    <t xml:space="preserve">Dorn Yellow</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drakenhof Nightshade</t>
   </si>
   <si>
@@ -1013,12 +1337,6 @@
     <t xml:space="preserve">Gal Vorbak Red</t>
   </si>
   <si>
-    <t xml:space="preserve">Gore-Grunta Fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey Seer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gryph-Charger Grey</t>
   </si>
   <si>
@@ -1031,9 +1349,6 @@
     <t xml:space="preserve">Iyanden Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Jokaero Orange</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kabalite Green</t>
   </si>
   <si>
@@ -1058,9 +1373,6 @@
     <t xml:space="preserve">Mournfang Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Nazdreg Yellow</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phalanx Yellow</t>
   </si>
   <si>
@@ -1073,12 +1385,6 @@
     <t xml:space="preserve">Rakarth Flesh</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratling Grime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reikland Fleshshade</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rhinox Hide</t>
   </si>
   <si>
@@ -1094,9 +1400,6 @@
     <t xml:space="preserve">Squig Orange</t>
   </si>
   <si>
-    <t xml:space="preserve">Steel Legion Drab</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sybarite Green</t>
   </si>
   <si>
@@ -1115,51 +1418,24 @@
     <t xml:space="preserve">Trollslayer Orange</t>
   </si>
   <si>
-    <t xml:space="preserve">Ulthuan Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ushabti Bone</t>
-  </si>
-  <si>
     <t xml:space="preserve">Volupus Pink</t>
   </si>
   <si>
     <t xml:space="preserve">Wild Rider Red</t>
   </si>
   <si>
-    <t xml:space="preserve">Wraithbone</t>
-  </si>
-  <si>
     <t xml:space="preserve">XV-88</t>
   </si>
   <si>
     <t xml:space="preserve">Yriel Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Zandri Dust</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alizarin Crimson</t>
   </si>
   <si>
-    <t xml:space="preserve">Kimera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp. Pack</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carbon Black</t>
   </si>
   <si>
-    <t xml:space="preserve">Start Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartacci Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danilo Cartacci</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caucasian Skintone</t>
   </si>
   <si>
@@ -1169,12 +1445,6 @@
     <t xml:space="preserve">Michal Pisarski</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobalt Bluegreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Energy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cold Yellow</t>
   </si>
   <si>
@@ -1202,12 +1472,6 @@
     <t xml:space="preserve">Kiwi Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Mix</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mars Orange</t>
   </si>
   <si>
@@ -1217,15 +1481,6 @@
     <t xml:space="preserve">Orange</t>
   </si>
   <si>
-    <t xml:space="preserve">Oxide Brown Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Medium</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oxide Green</t>
   </si>
   <si>
@@ -1262,27 +1517,18 @@
     <t xml:space="preserve">Ultramarine Blue</t>
   </si>
   <si>
-    <t xml:space="preserve">Violet</t>
-  </si>
-  <si>
     <t xml:space="preserve">Warm Yellow</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow Oxide</t>
   </si>
   <si>
-    <t xml:space="preserve">Liquitex</t>
-  </si>
-  <si>
     <t xml:space="preserve">ink</t>
   </si>
   <si>
     <t xml:space="preserve">Muted Green</t>
   </si>
   <si>
-    <t xml:space="preserve">Ink</t>
-  </si>
-  <si>
     <t xml:space="preserve">Muted Grey</t>
   </si>
   <si>
@@ -1292,27 +1538,12 @@
     <t xml:space="preserve">Muted Turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">Muted Violed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Dragon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Naphthol Crimson</t>
   </si>
   <si>
     <t xml:space="preserve">Phthalocyanine Blue (g)</t>
   </si>
   <si>
-    <t xml:space="preserve">Transparent Raw Umber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vivid Lime Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yellow Medium Azo</t>
   </si>
   <si>
@@ -1343,87 +1574,15 @@
     <t xml:space="preserve">Umber</t>
   </si>
   <si>
-    <t xml:space="preserve">Pro Acryl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rogue Hobby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bold Pyrrole Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bold Titanium White</t>
   </si>
   <si>
     <t xml:space="preserve">NMM / W. Wood</t>
   </si>
   <si>
-    <t xml:space="preserve">Bright Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Yellow Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flameon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Hot Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Plum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninjon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gladewyrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems Main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drab Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adepticon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ivory</t>
   </si>
   <si>
-    <t xml:space="preserve">Orange Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair /  Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultramarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metallic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Black</t>
   </si>
   <si>
@@ -1433,33 +1592,9 @@
     <t xml:space="preserve">Chesnut</t>
   </si>
   <si>
-    <t xml:space="preserve">Aluminium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vallejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model Air (old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbarian Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game</t>
-  </si>
-  <si>
     <t xml:space="preserve">Basalt Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">Model (old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beige Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Scales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Black Wash</t>
   </si>
   <si>
@@ -1469,24 +1604,6 @@
     <t xml:space="preserve">Bronze Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Brown Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burnt Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloth / Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard / NMM Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charred Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Brown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dark Blue Grey</t>
   </si>
   <si>
@@ -1499,30 +1616,6 @@
     <t xml:space="preserve">Game (old)</t>
   </si>
   <si>
-    <t xml:space="preserve">Deck Tan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xpress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin / Leaves / Gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elfic Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evil Red</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ger. C. Beige WWII</t>
   </si>
   <si>
@@ -1532,84 +1625,24 @@
     <t xml:space="preserve">Ghost Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">Metal Color</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gold Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Gorgon Brown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Green Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">Grunge Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Bluegrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra Opaque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Charcoal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Goldbrown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Siena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Warmgrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospitallier Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenebrous</t>
+    <t xml:space="preserve">Goldbrown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ochre</t>
   </si>
   <si>
     <t xml:space="preserve">Ice Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Jade Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khaki</t>
-  </si>
-  <si>
     <t xml:space="preserve">Luftwafe Unif. WWII</t>
   </si>
   <si>
-    <t xml:space="preserve">Middlestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midnight Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mummy White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nocturnal Red</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pale Grey Blue</t>
   </si>
   <si>
@@ -1619,43 +1652,13 @@
     <t xml:space="preserve">Prussian Blue</t>
   </si>
   <si>
-    <t xml:space="preserve">Scarlet Red</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scorpena Green</t>
   </si>
   <si>
-    <t xml:space="preserve">Scrofulous Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Succubus Skin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sunny Skin tone</t>
   </si>
   <si>
     <t xml:space="preserve">Sunset Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toxic Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twilight Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vampiric Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warlock Purple</t>
   </si>
   <si>
     <t xml:space="preserve">Wicked Purple</t>
@@ -3305,11 +3308,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="72974915"/>
-        <c:axId val="22679837"/>
+        <c:axId val="34066192"/>
+        <c:axId val="23506324"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="72974915"/>
+        <c:axId val="34066192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3341,7 +3344,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22679837"/>
+        <c:crossAx val="23506324"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3349,7 +3352,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22679837"/>
+        <c:axId val="23506324"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3388,7 +3391,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72974915"/>
+        <c:crossAx val="34066192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3429,9 +3432,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>621720</xdr:colOff>
+      <xdr:colOff>621360</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3440,7 +3443,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7723080" y="7024320"/>
-        <a:ext cx="7509960" cy="3178440"/>
+        <a:ext cx="7509600" cy="3178080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3713,7 +3716,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1195"/>
+  <dimension ref="A1:J1196"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.67"/>
@@ -3772,8 +3775,8 @@
         <v>11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <f aca="false">SUM(C2:C1032)</f>
-        <v>553</v>
+        <f aca="false">SUM(C2:C1033)</f>
+        <v>554</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -3951,7 +3954,7 @@
       </c>
       <c r="H9" s="2" t="str">
         <f aca="false" t="array" ref="H9:H9">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 2), ROW(Paints!D:D), ""), 2)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 3), Paints!D:D, 0)))</f>
-        <v>Anthracite Grey</v>
+        <v>Black Red</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>20</v>
@@ -7187,67 +7190,84 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B186" s="2"/>
+        <v>45809</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B187" s="2"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B188" s="2"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B189" s="2"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B190" s="2"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B191" s="2"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B192" s="2"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B193" s="2"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B194" s="2"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B195" s="2"/>
+    </row>
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B195" s="2"/>
-    </row>
-    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B196" s="2"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10246,6 +10266,9 @@
     </row>
     <row r="1195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1195" s="2"/>
+    </row>
+    <row r="1196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1196" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J11 B2:B1048576">
@@ -10281,7 +10304,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1195" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1196" type="list">
       <formula1>$J$2:$J$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10391,12 +10414,12 @@
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>207</v>
       </c>
       <c r="G2" s="1" t="n">
@@ -10411,160 +10434,220 @@
       <c r="L2" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="O2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
         <v>3</v>
       </c>
+      <c r="E3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>214</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>208</v>
+      <c r="F6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10574,114 +10657,162 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>233</v>
+        <v>250</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -10691,45 +10822,60 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>235</v>
+        <v>254</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -10738,1169 +10884,1307 @@
       <c r="E16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>221</v>
+      <c r="F16" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>239</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>47</v>
+        <v>260</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>239</v>
+        <v>4</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>239</v>
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
         <v>2</v>
       </c>
-      <c r="K19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>213</v>
+      <c r="E19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
         <v>2</v>
       </c>
+      <c r="K20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="M20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
-        <v>1</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>245</v>
+        <v>2</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
         <v>2</v>
       </c>
-      <c r="M26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>250</v>
+      <c r="G26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
-        <v>1</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>231</v>
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
         <v>2</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="K29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>255</v>
+        <v>282</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
         <v>2</v>
       </c>
-      <c r="G31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>257</v>
+      <c r="E31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
-        <v>1</v>
-      </c>
-      <c r="K32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>245</v>
+        <v>2</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>225</v>
+        <v>2</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
-        <v>3</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>264</v>
+      <c r="L34" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>263</v>
+        <v>291</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>263</v>
+        <v>293</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
-        <v>1</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>268</v>
+        <v>2</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>263</v>
+        <v>297</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>263</v>
+        <v>300</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>263</v>
+        <v>301</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>263</v>
+        <v>302</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
-        <v>1</v>
-      </c>
-      <c r="K42" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>274</v>
+        <v>2</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>263</v>
+        <v>304</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>239</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>263</v>
+        <v>306</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="K46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>263</v>
+        <v>309</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>263</v>
+        <v>311</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
         <v>1</v>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L49" s="2"/>
+      <c r="M49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>263</v>
+        <v>313</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>263</v>
+        <v>314</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>263</v>
+        <v>316</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>263</v>
+        <v>318</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>263</v>
+        <v>319</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
         <v>1</v>
       </c>
-      <c r="K55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>268</v>
+      <c r="G55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>263</v>
+        <v>321</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>263</v>
+        <v>322</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
-        <v>2</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" s="2" t="s">
-        <v>214</v>
+        <v>1</v>
+      </c>
+      <c r="M60" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
         <v>1</v>
       </c>
-      <c r="G62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>214</v>
+      <c r="M62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
         <v>1</v>
       </c>
-      <c r="H67" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>306</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
-        <v>2</v>
-      </c>
-      <c r="E68" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="M68" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="O68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>293</v>
+        <v>241</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
         <v>1</v>
       </c>
-      <c r="M69" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" s="2" t="s">
-        <v>242</v>
+      <c r="O69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -11910,156 +12194,165 @@
         <v>1</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K73" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="M73" s="1" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="O74" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P74" s="2" t="s">
-        <v>316</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>293</v>
+        <v>347</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
-        <v>2</v>
-      </c>
-      <c r="E75" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K75" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>318</v>
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>321</v>
+        <v>51</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12069,537 +12362,690 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>299</v>
+        <v>354</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>295</v>
+        <v>358</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
         <v>1</v>
       </c>
-      <c r="M87" s="1" t="n">
-        <v>1</v>
+      <c r="K87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
         <v>1</v>
       </c>
-      <c r="M88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" s="2" t="s">
-        <v>250</v>
+      <c r="K88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>297</v>
+        <v>369</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>336</v>
+        <v>229</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>293</v>
+        <v>374</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
         <v>1</v>
       </c>
-      <c r="M93" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" s="2" t="s">
-        <v>208</v>
+      <c r="O93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>295</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>345</v>
+        <v>385</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
         <v>1</v>
       </c>
-      <c r="O102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" s="2" t="s">
-        <v>221</v>
+      <c r="M102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>295</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
-        <v>2</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="K107" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>351</v>
+        <v>391</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>299</v>
+        <v>369</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
         <v>1</v>
       </c>
-      <c r="O108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" s="2" t="s">
-        <v>242</v>
+      <c r="G108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
@@ -12608,13 +13054,13 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -12623,13 +13069,13 @@
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
@@ -12638,49 +13084,115 @@
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>357</v>
+        <v>50</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>279</v>
+        <v>396</v>
+      </c>
+      <c r="M114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>358</v>
+        <v>47</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
         <v>0</v>
       </c>
+      <c r="E115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="M115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -12689,13 +13201,13 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
@@ -12704,13 +13216,13 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
@@ -12719,13 +13231,13 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
@@ -12734,70 +13246,94 @@
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>363</v>
+        <v>53</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
         <v>0</v>
       </c>
+      <c r="E120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="M120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="2" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>295</v>
+        <v>401</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
-        <v>1</v>
-      </c>
-      <c r="M121" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N121" s="2" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>295</v>
+        <v>402</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
-        <v>1</v>
-      </c>
-      <c r="O122" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P122" s="2" t="s">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>297</v>
+        <v>403</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -12806,13 +13342,13 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>295</v>
+        <v>404</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
@@ -12821,34 +13357,28 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>293</v>
+        <v>405</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
-        <v>1</v>
-      </c>
-      <c r="O125" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P125" s="2" t="s">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>293</v>
+        <v>406</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -12857,13 +13387,13 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>295</v>
+        <v>407</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -12872,34 +13402,64 @@
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="M128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="O128" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>235</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>374</v>
+        <v>409</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -12908,13 +13468,13 @@
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>376</v>
+        <v>410</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -12923,34 +13483,28 @@
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>378</v>
+        <v>411</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
-        <v>1</v>
-      </c>
-      <c r="O131" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P131" s="2" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>378</v>
+        <v>412</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -12959,13 +13513,13 @@
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>381</v>
+        <v>413</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -12974,34 +13528,28 @@
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>374</v>
+        <v>414</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
-        <v>1</v>
-      </c>
-      <c r="I134" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>376</v>
+        <v>415</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13010,13 +13558,13 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>374</v>
+        <v>416</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13025,13 +13573,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>374</v>
+        <v>417</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13040,13 +13588,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>381</v>
+        <v>418</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13055,13 +13603,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>378</v>
+        <v>241</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13070,13 +13618,13 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>381</v>
+        <v>326</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13085,13 +13633,13 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13100,13 +13648,13 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13115,13 +13663,13 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>392</v>
+        <v>423</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>378</v>
+        <v>241</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13130,40 +13678,28 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
-        <v>2</v>
-      </c>
-      <c r="E144" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G144" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13172,13 +13708,13 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>381</v>
+        <v>241</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13187,13 +13723,13 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>376</v>
+        <v>241</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13202,76 +13738,58 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
-        <v>1</v>
-      </c>
-      <c r="K148" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
-        <v>1</v>
-      </c>
-      <c r="K149" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
-        <v>1</v>
-      </c>
-      <c r="K150" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L150" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13280,13 +13798,13 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13295,13 +13813,13 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13310,13 +13828,13 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13325,13 +13843,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>247</v>
+        <v>435</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13340,13 +13858,13 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13355,13 +13873,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>376</v>
+        <v>241</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13370,13 +13888,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>374</v>
+        <v>277</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13385,13 +13903,13 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13400,13 +13918,13 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>253</v>
+        <v>440</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>378</v>
+        <v>241</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13415,13 +13933,13 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13430,13 +13948,13 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13445,13 +13963,13 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -13460,13 +13978,13 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>374</v>
+        <v>241</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -13475,46 +13993,28 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>376</v>
+        <v>241</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
-        <v>3</v>
-      </c>
-      <c r="E165" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G165" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H165" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I165" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>376</v>
+        <v>241</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -13523,13 +14023,13 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>373</v>
+        <v>276</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>376</v>
+        <v>326</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -13538,13 +14038,13 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>375</v>
+        <v>448</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>417</v>
+        <v>241</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -13553,13 +14053,13 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -13568,13 +14068,13 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -13583,13 +14083,13 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -13598,13 +14098,13 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -13613,34 +14113,28 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
-        <v>1</v>
-      </c>
-      <c r="G173" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H173" s="2" t="s">
-        <v>424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -13649,13 +14143,13 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -13664,13 +14158,13 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>410</v>
+        <v>456</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>419</v>
+        <v>277</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -13679,55 +14173,43 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>419</v>
+        <v>277</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
-        <v>1</v>
-      </c>
-      <c r="G177" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H177" s="2" t="s">
-        <v>316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
-        <v>1</v>
-      </c>
-      <c r="K178" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L178" s="2" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -13736,13 +14218,13 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
@@ -13751,13 +14233,13 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -13766,64 +14248,28 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
         <v>0</v>
       </c>
-      <c r="E182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" s="2" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -13832,13 +14278,13 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -13847,13 +14293,13 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>419</v>
+        <v>277</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -13862,13 +14308,13 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -13877,13 +14323,13 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -13892,472 +14338,238 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>51</v>
+        <v>468</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>440</v>
+        <v>276</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>441</v>
+        <v>326</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
-        <v>1</v>
-      </c>
-      <c r="K188" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L188" s="2" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>443</v>
+        <v>340</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
-        <v>1</v>
-      </c>
-      <c r="O189" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P189" s="2" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>443</v>
+        <v>239</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
         <v>0</v>
       </c>
-      <c r="E190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H190" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="M190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N190" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P190" s="2" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>441</v>
+        <v>338</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
-        <v>2</v>
-      </c>
-      <c r="G191" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="K191" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L191" s="2" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>45</v>
+        <v>472</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
         <v>0</v>
       </c>
-      <c r="E192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="M192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P192" s="2" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>448</v>
+        <v>239</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
-        <v>1</v>
-      </c>
-      <c r="G193" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>441</v>
+        <v>340</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
-        <v>1</v>
-      </c>
-      <c r="K194" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L194" s="2" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>451</v>
+        <v>340</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
-        <v>2</v>
-      </c>
-      <c r="G195" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H195" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="K195" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
-        <v>4</v>
-      </c>
-      <c r="E196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="G196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="K196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L196" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="O196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P196" s="2" t="s">
-        <v>214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>458</v>
+        <v>338</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
-        <v>2</v>
-      </c>
-      <c r="G197" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O197" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P197" s="2" t="s">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
         <v>0</v>
       </c>
-      <c r="E198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H198" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P198" s="2" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>441</v>
+        <v>340</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
-        <v>2</v>
-      </c>
-      <c r="K199" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L199" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="O199" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P199" s="2" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
-        <v>3</v>
-      </c>
-      <c r="E200" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G200" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K200" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L200" s="2" t="s">
-        <v>462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>441</v>
+        <v>338</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
-        <v>1</v>
-      </c>
-      <c r="K201" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L201" s="2" t="s">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>465</v>
+        <v>340</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
-        <v>1</v>
-      </c>
-      <c r="O202" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P202" s="2" t="s">
-        <v>466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>468</v>
+        <v>238</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>419</v>
+        <v>473</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14366,13 +14578,13 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>468</v>
+        <v>238</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>419</v>
+        <v>239</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14381,13 +14593,13 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>236</v>
+        <v>486</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>468</v>
+        <v>238</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>419</v>
+        <v>340</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14396,55 +14608,43 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>472</v>
+        <v>239</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
-        <v>1</v>
-      </c>
-      <c r="O206" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P206" s="2" t="s">
-        <v>466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
-        <v>1</v>
-      </c>
-      <c r="K207" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L207" s="2" t="s">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>476</v>
+        <v>239</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14453,34 +14653,28 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>477</v>
+        <v>399</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>476</v>
+        <v>340</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
-        <v>1</v>
-      </c>
-      <c r="O209" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P209" s="2" t="s">
-        <v>478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>476</v>
+        <v>239</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14489,64 +14683,28 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
         <v>0</v>
       </c>
-      <c r="E211" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G211" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I211" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K211" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M211" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O211" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" s="2" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>476</v>
+        <v>340</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14555,13 +14713,13 @@
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>474</v>
+        <v>338</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14570,115 +14728,73 @@
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>476</v>
+        <v>338</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
-        <v>2</v>
-      </c>
-      <c r="M214" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N214" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O214" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P214" s="2" t="s">
-        <v>306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
-        <v>2</v>
-      </c>
-      <c r="K215" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L215" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="O215" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P215" s="2" t="s">
-        <v>485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
-        <v>1</v>
-      </c>
-      <c r="K216" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L216" s="2" t="s">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>476</v>
+        <v>340</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
-        <v>2</v>
-      </c>
-      <c r="E217" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G217" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H217" s="2" t="s">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>476</v>
+        <v>340</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14687,13 +14803,13 @@
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>476</v>
+        <v>239</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14702,13 +14818,13 @@
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14717,145 +14833,103 @@
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
-        <v>1</v>
-      </c>
-      <c r="K221" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L221" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
-        <v>1</v>
-      </c>
-      <c r="K222" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L222" s="2" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>222</v>
+        <v>502</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>494</v>
+        <v>347</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
-        <v>1</v>
-      </c>
-      <c r="K223" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L223" s="2" t="s">
-        <v>495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
-        <v>1</v>
-      </c>
-      <c r="K224" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L224" s="2" t="s">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>476</v>
+        <v>347</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
-        <v>1</v>
-      </c>
-      <c r="K225" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L225" s="2" t="s">
-        <v>498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
-        <v>2</v>
-      </c>
-      <c r="E226" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F226" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K226" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L226" s="2" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>476</v>
+        <v>347</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -14864,13 +14938,13 @@
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -14879,13 +14953,13 @@
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>491</v>
+        <v>347</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -14894,34 +14968,28 @@
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>221</v>
+        <v>508</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>503</v>
+        <v>347</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
-        <v>1</v>
-      </c>
-      <c r="O230" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P230" s="2" t="s">
-        <v>466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -14930,46 +14998,64 @@
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F232" s="1" t="s">
-        <v>316</v>
+        <v>0</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="M232" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="O232" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>316</v>
+        <v>396</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>476</v>
+        <v>347</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -14978,100 +15064,58 @@
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>474</v>
+        <v>347</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
-        <v>3</v>
-      </c>
-      <c r="E234" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="M234" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N234" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O234" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P234" s="2" t="s">
-        <v>316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>509</v>
+        <v>347</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
-        <v>3</v>
-      </c>
-      <c r="E235" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G235" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I235" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J235" s="2" t="s">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>509</v>
+        <v>347</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
-        <v>1</v>
-      </c>
-      <c r="E236" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F236" s="1" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>509</v>
+        <v>347</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15080,184 +15124,211 @@
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>471</v>
+        <v>205</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>509</v>
+        <v>352</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>293</v>
+        <v>518</v>
+      </c>
+      <c r="M238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="7" t="s">
-        <v>513</v>
+        <v>45</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>471</v>
+        <v>205</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>509</v>
+        <v>352</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
         <v>0</v>
       </c>
+      <c r="E239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="M239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" s="2" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>471</v>
+        <v>205</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>509</v>
+        <v>352</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="G240" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>231</v>
+        <v>396</v>
+      </c>
+      <c r="I240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="M240" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N240" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="O240" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>515</v>
+        <v>396</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>471</v>
+        <v>521</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>509</v>
+        <v>347</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
-        <v>3</v>
-      </c>
-      <c r="E241" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G241" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K241" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L241" s="2" t="s">
-        <v>517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>471</v>
+        <v>521</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>494</v>
+        <v>347</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
-        <v>1</v>
-      </c>
-      <c r="E242" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>520</v>
+        <v>227</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>471</v>
+        <v>521</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>476</v>
+        <v>347</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
         <v>0</v>
       </c>
-      <c r="E243" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G243" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I243" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K243" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L243" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M243" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O243" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P243" s="2" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>459</v>
+        <v>523</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15266,55 +15337,79 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>474</v>
+        <v>295</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
-        <v>1</v>
-      </c>
-      <c r="K245" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L245" s="2" t="s">
-        <v>498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>474</v>
+        <v>249</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>279</v>
+        <v>396</v>
+      </c>
+      <c r="M246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15323,103 +15418,73 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>476</v>
+        <v>249</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
-        <v>1</v>
-      </c>
-      <c r="K248" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L248" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>474</v>
+        <v>295</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
-        <v>1</v>
-      </c>
-      <c r="K249" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L249" s="2" t="s">
-        <v>498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>494</v>
+        <v>295</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
-        <v>1</v>
-      </c>
-      <c r="E250" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
-        <v>2</v>
-      </c>
-      <c r="E251" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F251" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="M251" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N251" s="2" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
@@ -15428,13 +15493,13 @@
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>476</v>
+        <v>249</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
@@ -15443,13 +15508,13 @@
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>476</v>
+        <v>530</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15458,40 +15523,28 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>474</v>
+        <v>249</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
-        <v>2</v>
-      </c>
-      <c r="E255" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F255" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="M255" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N255" s="2" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>491</v>
+        <v>295</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
@@ -15500,118 +15553,124 @@
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>474</v>
+        <v>253</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
-        <v>1</v>
-      </c>
-      <c r="M257" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N257" s="2" t="s">
-        <v>231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>503</v>
+        <v>253</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
-        <v>1</v>
-      </c>
-      <c r="O258" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P258" s="2" t="s">
-        <v>466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>293</v>
+        <v>396</v>
+      </c>
+      <c r="M259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
-        <v>1</v>
-      </c>
-      <c r="K260" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L260" s="2" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>474</v>
+        <v>295</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
-        <v>1</v>
-      </c>
-      <c r="M261" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N261" s="2" t="s">
-        <v>316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
@@ -15620,13 +15679,13 @@
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
@@ -15635,97 +15694,73 @@
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>474</v>
+        <v>295</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
-        <v>1</v>
-      </c>
-      <c r="K264" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L264" s="2" t="s">
-        <v>218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
-        <v>1</v>
-      </c>
-      <c r="G265" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H265" s="2" t="s">
-        <v>424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>494</v>
+        <v>295</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
-        <v>1</v>
-      </c>
-      <c r="K266" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L266" s="2" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>474</v>
+        <v>295</v>
       </c>
       <c r="D267" s="2" t="n">
         <f aca="false">SUM(E267,G267,I267,K267,M267,O267)</f>
-        <v>1</v>
-      </c>
-      <c r="K267" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L267" s="2" t="s">
-        <v>214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>471</v>
+        <v>248</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>494</v>
+        <v>369</v>
       </c>
       <c r="D268" s="2" t="n">
         <f aca="false">SUM(E268,G268,I268,K268,M268,O268)</f>
@@ -15735,37 +15770,37 @@
         <v>0</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
       <c r="G268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
       <c r="I268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
       <c r="K268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
       <c r="M268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N268" s="2" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
       <c r="O268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P268" s="2" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="548">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -77,523 +77,526 @@
     <t xml:space="preserve">Tzaangors</t>
   </si>
   <si>
+    <t xml:space="preserve">Short Break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulthwé Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35mm Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Elves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harlequins Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Familliars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most Used Paints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumineth Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodletters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khorne Bloodbound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Elves Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lothern Seaguard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Elves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodreavers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunguska Warband</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodwarriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvaneth Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrathmongers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodstoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter Priest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flesh Hounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodsecrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karanak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migthy Lord of Khorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Must-Have Paints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skullcrushers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Ivory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khorgorath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Guardians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aldeari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laser Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bismuth Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgements of Khorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenebrous Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windriders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skullgrinder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exalted Deathbringer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave Serpents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rangers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Howling Banshees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warlock Conclave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Prisms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corvus Belli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Space Marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Scars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberator Prime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stormcasts Eternals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Reapers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemlock Wraithfighter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plage Marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortisan Soulmason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ossiarch Boneripers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosecutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chief Librarian Tigurius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultramarines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heroes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blackstone Fortress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Marines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fungoid Cave Shaman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloomspite Gitz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle Sisters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adepta Sororitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repentias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penitent Engines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canoness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-Ball Greenskin Oni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristeia!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level up Tau Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T'au</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renegade Guardsmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exorcist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritseer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eisenhorn and Daemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imperium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autarch Skyrunner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space Marine Terminator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator Captain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator Librarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator Chaplain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roboute Guilliman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garrek's Reavers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayvaan Shrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raven Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inquisitor Karamazov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inquisitor Greyfax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seraphims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lothern Seahelm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amalia Novena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Intercessors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Angels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech-Priest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adeptus Mechanicus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydonian Dragoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech-Priest Dominus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belisarius Cawl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaves to Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katakros Mortach of the Necropolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ephrael Stern and Kyganil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marneus Calgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Apothecary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator Apothecary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Captain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Librarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serberys Raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serberys Sulphurhounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skorpius Desintegrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skorpius Dunerider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archaeopter Fusilave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archaeopter Transvector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pteraxii Sterylizors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pteraxii Skystalkers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech-Priest Manipulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthas (Abaddon Conversion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Space Marines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knight Questor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord Inquisitor Kyria Draxus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryevh Leonhart, Chrace Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soulfinder (Illic Conversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skullreapers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neave Blacktalon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spektr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nomads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenzer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollow Man</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Securitate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heckler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kriza Borac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Sorcerer Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanari Auralan Wardens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumineth Realm-Lords</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lady of the Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echoes of Camelot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgana le Fay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farseer Skyrunner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troupe Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troupe Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadowseer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Jester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Lieutenant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaris Assault Intercessors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sons of the Phoenix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ynnari Storm Guardians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winged Autarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagarythe Princess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanary Bladelord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurnoth Hunters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvaneth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenant Seekers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Revenants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arch-Revenant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ynnari Warlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gossamid Archers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chracian Archer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chracian Spearmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awakened Wyldwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manifestations of the Deepwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farseer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warsong Revenant</t>
+  </si>
+  <si>
     <t xml:space="preserve">Belthanos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ulthwé Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35mm Models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Elves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harlequins Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Familliars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Most Used Paints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumineth Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodletters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khorne Bloodbound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Elves Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lothern Seaguard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Elves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodreavers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunguska Warband</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodwarriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sylvaneth Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrathmongers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodstoker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slaughter Priest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flesh Hounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodsecrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karanak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migthy Lord of Khorne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Must-Have Paints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skullcrushers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Ivory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khorgorath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Guardians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aldeari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laser Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bismuth Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Judgements of Khorne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenebrous Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windriders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skullgrinder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exalted Deathbringer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wave Serpents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rangers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Howling Banshees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warlock Conclave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Prisms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aquiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corvus Belli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Space Marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Scars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liberator Prime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stormcasts Eternals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Reapers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hemlock Wraithfighter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plage Marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortisan Soulmason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ossiarch Boneripers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prosecutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chief Librarian Tigurius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultramarines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heroes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blackstone Fortress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Marines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fungoid Cave Shaman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloomspite Gitz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battle Sisters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adepta Sororitas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repentias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penitent Engines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canoness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8-Ball Greenskin Oni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristeia!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level up Tau Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T'au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renegade Guardsmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exorcist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiritseer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autarch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eisenhorn and Daemon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imperium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autarch Skyrunner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space Marine Terminator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminator Captain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminator Librarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminator Chaplain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboute Guilliman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garrek's Reavers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayvaan Shrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raven Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inquisitor Karamazov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inquisitor Greyfax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seraphims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lothern Seahelm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amalia Novena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Intercessors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood Angels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech-Priest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adeptus Mechanicus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydonian Dragoon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech-Priest Dominus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belisarius Cawl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slaves to Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katakros Mortach of the Necropolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ephrael Stern and Kyganil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marneus Calgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Apothecary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminator Apothecary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Captain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Librarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serberys Raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serberys Sulphurhounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skorpius Desintegrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skorpius Dunerider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archaeopter Fusilave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archaeopter Transvector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pteraxii Sterylizors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pteraxii Skystalkers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech-Priest Manipulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthas (Abaddon Conversion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Space Marines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knight Questor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lord Inquisitor Kyria Draxus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryevh Leonhart, Chrace Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soulfinder (Illic Conversion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skullreapers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neave Blacktalon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spektr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nomads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenzer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hollow Man</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Securitate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heckler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kriza Borac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Sorcerer Lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanari Auralan Wardens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumineth Realm-Lords</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lady of the Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echoes of Camelot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgana le Fay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farseer Skyrunner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troupe Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troupe Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadowseer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death Jester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Lieutenant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primaris Assault Intercessors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sons of the Phoenix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ynnari Storm Guardians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winged Autarch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagarythe Princess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanary Bladelord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurnoth Hunters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sylvaneth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenant Seekers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree-Revenants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arch-Revenant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ynnari Warlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gossamid Archers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chracian Archer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chracian Spearmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awakened Wyldwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manifestations of the Deepwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farseer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warsong Revenant</t>
   </si>
   <si>
     <t xml:space="preserve">Paint</t>
@@ -3308,11 +3311,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="34066192"/>
-        <c:axId val="23506324"/>
+        <c:axId val="59813894"/>
+        <c:axId val="57884149"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="34066192"/>
+        <c:axId val="59813894"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,7 +3347,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23506324"/>
+        <c:crossAx val="57884149"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3352,7 +3355,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23506324"/>
+        <c:axId val="57884149"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3391,7 +3394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34066192"/>
+        <c:crossAx val="59813894"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7201,7 +7204,7 @@
         <v>1</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>179</v>
@@ -10354,63 +10357,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
@@ -10420,36 +10423,36 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10459,30 +10462,30 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
@@ -10492,30 +10495,30 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
@@ -10525,30 +10528,30 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
@@ -10558,30 +10561,30 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
@@ -10591,30 +10594,30 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10624,30 +10627,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10657,30 +10660,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10690,30 +10693,30 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
@@ -10723,30 +10726,30 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
@@ -10756,30 +10759,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
@@ -10789,30 +10792,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -10822,30 +10825,30 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
@@ -10855,7 +10858,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>1</v>
@@ -10864,18 +10867,18 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -10885,30 +10888,30 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
@@ -10918,24 +10921,24 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
@@ -10945,36 +10948,36 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
@@ -10984,24 +10987,24 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
@@ -11011,24 +11014,24 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
@@ -11038,24 +11041,24 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
@@ -11065,24 +11068,24 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -11092,24 +11095,24 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
@@ -11119,24 +11122,24 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
@@ -11146,24 +11149,24 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
@@ -11173,24 +11176,24 @@
         <v>1</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
@@ -11200,7 +11203,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>1</v>
@@ -11208,13 +11211,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
@@ -11224,7 +11227,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>1</v>
@@ -11232,13 +11235,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
@@ -11248,24 +11251,24 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
@@ -11275,24 +11278,24 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
@@ -11302,24 +11305,24 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
@@ -11329,24 +11332,24 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
@@ -11356,24 +11359,24 @@
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="K33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
@@ -11383,24 +11386,24 @@
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
@@ -11410,24 +11413,24 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
@@ -11437,24 +11440,24 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
@@ -11464,24 +11467,24 @@
         <v>1</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
@@ -11491,24 +11494,24 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
@@ -11518,24 +11521,24 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
@@ -11545,24 +11548,24 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
@@ -11572,24 +11575,24 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
@@ -11599,24 +11602,24 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
@@ -11626,18 +11629,18 @@
         <v>1</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
@@ -11647,18 +11650,18 @@
         <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
@@ -11668,18 +11671,18 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
@@ -11689,18 +11692,18 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
@@ -11710,18 +11713,18 @@
         <v>1</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
@@ -11731,18 +11734,18 @@
         <v>1</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
@@ -11752,18 +11755,18 @@
         <v>1</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
@@ -11773,18 +11776,18 @@
         <v>1</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
@@ -11794,18 +11797,18 @@
         <v>1</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
@@ -11815,18 +11818,18 @@
         <v>1</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
@@ -11836,19 +11839,19 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
@@ -11858,18 +11861,18 @@
         <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
@@ -11879,18 +11882,18 @@
         <v>1</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
@@ -11903,18 +11906,18 @@
         <v>1</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
@@ -11924,18 +11927,18 @@
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
@@ -11945,18 +11948,18 @@
         <v>1</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
@@ -11966,18 +11969,18 @@
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
@@ -11989,13 +11992,13 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
@@ -12005,18 +12008,18 @@
         <v>1</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
@@ -12026,18 +12029,18 @@
         <v>1</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
@@ -12047,18 +12050,18 @@
         <v>1</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
@@ -12068,18 +12071,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
@@ -12089,18 +12092,18 @@
         <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
@@ -12110,18 +12113,18 @@
         <v>1</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -12131,18 +12134,18 @@
         <v>1</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -12152,18 +12155,18 @@
         <v>1</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
@@ -12173,18 +12176,18 @@
         <v>1</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -12194,18 +12197,18 @@
         <v>1</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
@@ -12215,18 +12218,18 @@
         <v>1</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
@@ -12236,18 +12239,18 @@
         <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
@@ -12257,18 +12260,18 @@
         <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
@@ -12278,18 +12281,18 @@
         <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
@@ -12299,18 +12302,18 @@
         <v>1</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
@@ -12320,18 +12323,18 @@
         <v>1</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12341,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12349,10 +12352,10 @@
         <v>51</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12362,18 +12365,18 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12383,18 +12386,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12404,18 +12407,18 @@
         <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
@@ -12425,18 +12428,18 @@
         <v>1</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
@@ -12446,18 +12449,18 @@
         <v>1</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
@@ -12467,18 +12470,18 @@
         <v>1</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
@@ -12488,18 +12491,18 @@
         <v>1</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12509,18 +12512,18 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
@@ -12530,18 +12533,18 @@
         <v>1</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
@@ -12551,18 +12554,18 @@
         <v>1</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
@@ -12572,18 +12575,18 @@
         <v>1</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
@@ -12593,18 +12596,18 @@
         <v>1</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
@@ -12614,18 +12617,18 @@
         <v>1</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
@@ -12635,18 +12638,18 @@
         <v>1</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12656,18 +12659,18 @@
         <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
@@ -12677,18 +12680,18 @@
         <v>1</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
@@ -12698,18 +12701,18 @@
         <v>1</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
@@ -12719,18 +12722,18 @@
         <v>1</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
@@ -12740,18 +12743,18 @@
         <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
@@ -12761,18 +12764,18 @@
         <v>1</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12782,18 +12785,18 @@
         <v>1</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
@@ -12803,18 +12806,18 @@
         <v>1</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
@@ -12824,18 +12827,18 @@
         <v>1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
@@ -12845,18 +12848,18 @@
         <v>1</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
@@ -12866,18 +12869,18 @@
         <v>1</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
@@ -12887,18 +12890,18 @@
         <v>1</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -12908,18 +12911,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -12929,18 +12932,18 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
@@ -12950,18 +12953,18 @@
         <v>1</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
@@ -12971,18 +12974,18 @@
         <v>1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
@@ -12992,18 +12995,18 @@
         <v>1</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
@@ -13013,18 +13016,18 @@
         <v>1</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
@@ -13034,18 +13037,18 @@
         <v>1</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
@@ -13054,13 +13057,13 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -13069,13 +13072,13 @@
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
@@ -13087,10 +13090,10 @@
         <v>50</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
@@ -13100,37 +13103,37 @@
         <v>0</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13138,10 +13141,10 @@
         <v>47</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
@@ -13151,48 +13154,48 @@
         <v>0</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -13201,13 +13204,13 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
@@ -13216,13 +13219,13 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
@@ -13231,13 +13234,13 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
@@ -13249,10 +13252,10 @@
         <v>53</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
@@ -13262,48 +13265,48 @@
         <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
@@ -13312,13 +13315,13 @@
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
@@ -13327,13 +13330,13 @@
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -13342,13 +13345,13 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
@@ -13357,13 +13360,13 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13372,13 +13375,13 @@
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13387,13 +13390,13 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -13402,13 +13405,13 @@
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
@@ -13418,48 +13421,48 @@
         <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -13468,13 +13471,13 @@
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -13483,13 +13486,13 @@
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
@@ -13498,13 +13501,13 @@
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -13513,13 +13516,13 @@
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -13528,13 +13531,13 @@
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13543,13 +13546,13 @@
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13558,13 +13561,13 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13573,13 +13576,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13588,13 +13591,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13603,13 +13606,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13618,13 +13621,13 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13633,13 +13636,13 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13648,13 +13651,13 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13663,13 +13666,13 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13678,13 +13681,13 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
@@ -13693,13 +13696,13 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13708,13 +13711,13 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13723,13 +13726,13 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13738,13 +13741,13 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13753,13 +13756,13 @@
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
@@ -13768,13 +13771,13 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13783,13 +13786,13 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13798,13 +13801,13 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13813,13 +13816,13 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13828,13 +13831,13 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13843,13 +13846,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13858,13 +13861,13 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13873,13 +13876,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13888,13 +13891,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13903,13 +13906,13 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13918,13 +13921,13 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13933,13 +13936,13 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13948,13 +13951,13 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13963,13 +13966,13 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -13978,13 +13981,13 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -13993,13 +13996,13 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -14008,13 +14011,13 @@
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -14023,13 +14026,13 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -14038,13 +14041,13 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -14053,13 +14056,13 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -14068,13 +14071,13 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -14083,13 +14086,13 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -14098,13 +14101,13 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -14113,13 +14116,13 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -14128,13 +14131,13 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -14143,13 +14146,13 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14158,13 +14161,13 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14173,13 +14176,13 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14188,13 +14191,13 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14203,13 +14206,13 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -14218,13 +14221,13 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
@@ -14233,13 +14236,13 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14248,13 +14251,13 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14263,13 +14266,13 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -14278,13 +14281,13 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -14293,13 +14296,13 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -14308,13 +14311,13 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14323,13 +14326,13 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14338,13 +14341,13 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14353,13 +14356,13 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14368,13 +14371,13 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14383,13 +14386,13 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14398,13 +14401,13 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14413,13 +14416,13 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
@@ -14428,13 +14431,13 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
@@ -14443,13 +14446,13 @@
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14458,13 +14461,13 @@
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
@@ -14473,13 +14476,13 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
@@ -14488,13 +14491,13 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
@@ -14503,13 +14506,13 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14518,13 +14521,13 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14533,13 +14536,13 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
@@ -14548,13 +14551,13 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14563,13 +14566,13 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14578,13 +14581,13 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14593,13 +14596,13 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14608,13 +14611,13 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
@@ -14623,13 +14626,13 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14638,13 +14641,13 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14653,13 +14656,13 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
@@ -14668,13 +14671,13 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14683,13 +14686,13 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14698,13 +14701,13 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14713,13 +14716,13 @@
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14728,13 +14731,13 @@
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
@@ -14743,13 +14746,13 @@
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14758,13 +14761,13 @@
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
@@ -14773,13 +14776,13 @@
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
@@ -14788,13 +14791,13 @@
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14803,13 +14806,13 @@
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14818,13 +14821,13 @@
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14833,13 +14836,13 @@
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
@@ -14848,13 +14851,13 @@
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
@@ -14863,13 +14866,13 @@
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -14878,13 +14881,13 @@
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
@@ -14893,13 +14896,13 @@
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
@@ -14908,13 +14911,13 @@
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
@@ -14923,13 +14926,13 @@
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -14938,13 +14941,13 @@
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -14953,13 +14956,13 @@
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -14968,13 +14971,13 @@
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -14983,13 +14986,13 @@
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>509</v>
-      </c>
       <c r="C231" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -14998,13 +15001,13 @@
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
@@ -15014,48 +15017,48 @@
         <v>0</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -15064,13 +15067,13 @@
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
@@ -15079,13 +15082,13 @@
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
@@ -15094,13 +15097,13 @@
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
@@ -15109,13 +15112,13 @@
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15124,13 +15127,13 @@
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
@@ -15140,37 +15143,37 @@
         <v>0</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P238" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15178,10 +15181,10 @@
         <v>45</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
@@ -15191,48 +15194,48 @@
         <v>0</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N239" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P239" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
@@ -15242,48 +15245,48 @@
         <v>0</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N240" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15292,13 +15295,13 @@
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B242" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="C242" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
@@ -15307,13 +15310,13 @@
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15322,13 +15325,13 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15337,13 +15340,13 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
@@ -15352,13 +15355,13 @@
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15368,48 +15371,48 @@
         <v>0</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15418,13 +15421,13 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15433,13 +15436,13 @@
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15448,13 +15451,13 @@
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
@@ -15463,13 +15466,13 @@
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
@@ -15478,13 +15481,13 @@
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
@@ -15493,13 +15496,13 @@
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
@@ -15508,13 +15511,13 @@
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15523,13 +15526,13 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
@@ -15538,13 +15541,13 @@
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
@@ -15553,13 +15556,13 @@
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
@@ -15568,13 +15571,13 @@
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
@@ -15583,13 +15586,13 @@
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
@@ -15599,48 +15602,48 @@
         <v>0</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N259" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P259" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
@@ -15649,13 +15652,13 @@
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
@@ -15664,13 +15667,13 @@
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
@@ -15679,13 +15682,13 @@
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
@@ -15694,13 +15697,13 @@
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
@@ -15709,13 +15712,13 @@
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
@@ -15724,13 +15727,13 @@
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
@@ -15739,13 +15742,13 @@
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D267" s="2" t="n">
         <f aca="false">SUM(E267,G267,I267,K267,M267,O267)</f>
@@ -15754,13 +15757,13 @@
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D268" s="2" t="n">
         <f aca="false">SUM(E268,G268,I268,K268,M268,O268)</f>
@@ -15770,37 +15773,37 @@
         <v>0</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N268" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P268" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="557">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">Gossamid Archers</t>
   </si>
   <si>
-    <t xml:space="preserve">Chracian Archer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chracian Spearmen</t>
+    <t xml:space="preserve">Chracian Archer Sentinel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chracian Spearmen Sentinel</t>
   </si>
   <si>
     <t xml:space="preserve">Awakened Wyldwood</t>
@@ -599,6 +599,15 @@
     <t xml:space="preserve">Belthanos</t>
   </si>
   <si>
+    <t xml:space="preserve">Chracian Archers G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chracian Spearmen G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chracian Noble 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paint</t>
   </si>
   <si>
@@ -1665,6 +1674,24 @@
   </si>
   <si>
     <t xml:space="preserve">Wicked Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancient Honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed Paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter Red</t>
   </si>
 </sst>
 </file>
@@ -3299,7 +3326,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>6</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>9</c:v>
@@ -3311,11 +3338,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="59813894"/>
-        <c:axId val="57884149"/>
+        <c:axId val="40720927"/>
+        <c:axId val="8761026"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="59813894"/>
+        <c:axId val="40720927"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3347,7 +3374,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57884149"/>
+        <c:crossAx val="8761026"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3355,7 +3382,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57884149"/>
+        <c:axId val="8761026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3394,7 +3421,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59813894"/>
+        <c:crossAx val="40720927"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3435,9 +3462,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>621360</xdr:colOff>
+      <xdr:colOff>621000</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>24120</xdr:rowOff>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3446,7 +3473,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7723080" y="7024320"/>
-        <a:ext cx="7509600" cy="3178080"/>
+        <a:ext cx="7509240" cy="3177720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3719,7 +3746,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1196"/>
+  <dimension ref="A1:J1198"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.67"/>
@@ -3778,8 +3805,8 @@
         <v>11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <f aca="false">SUM(C2:C1033)</f>
-        <v>554</v>
+        <f aca="false">SUM(C2:C1035)</f>
+        <v>568</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -7081,7 +7108,7 @@
         <v>29</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>186</v>
@@ -7213,70 +7240,118 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="n">
         <v>45839</v>
       </c>
-      <c r="B187" s="2"/>
-    </row>
-    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B187" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B188" s="2"/>
-    </row>
-    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45839</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B189" s="2"/>
+        <v>45839</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="B190" s="2"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="B191" s="2"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="B192" s="2"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="B193" s="2"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="n">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="B194" s="2"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="B195" s="2"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B196" s="2"/>
+    </row>
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B197" s="2"/>
+    </row>
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B196" s="2"/>
-    </row>
-    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="2"/>
-    </row>
-    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B198" s="2"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10272,6 +10347,12 @@
     </row>
     <row r="1196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1196" s="2"/>
+    </row>
+    <row r="1197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1197" s="2"/>
+    </row>
+    <row r="1198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1198" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J11 B2:B1048576">
@@ -10307,7 +10388,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1196" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1198" type="list">
       <formula1>$J$2:$J$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10357,63 +10438,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
@@ -10423,36 +10504,36 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10462,30 +10543,30 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
@@ -10495,30 +10576,30 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
@@ -10528,30 +10609,30 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
@@ -10561,30 +10642,30 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
@@ -10594,30 +10675,30 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10627,30 +10708,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10660,30 +10741,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10693,30 +10774,30 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
@@ -10726,30 +10807,30 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
@@ -10759,30 +10840,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
@@ -10792,30 +10873,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -10825,30 +10906,30 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
@@ -10858,7 +10939,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>1</v>
@@ -10867,18 +10948,18 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -10888,30 +10969,30 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
@@ -10921,63 +11002,63 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
         <v>4</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
@@ -10987,24 +11068,24 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
@@ -11014,24 +11095,24 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
@@ -11041,24 +11122,24 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
@@ -11068,24 +11149,24 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -11095,24 +11176,24 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
@@ -11122,24 +11203,24 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
@@ -11149,24 +11230,24 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
@@ -11176,24 +11257,24 @@
         <v>1</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
@@ -11203,7 +11284,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>1</v>
@@ -11211,13 +11292,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
@@ -11227,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>1</v>
@@ -11235,13 +11316,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
@@ -11251,24 +11332,24 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
@@ -11278,24 +11359,24 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
@@ -11305,24 +11386,24 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
@@ -11332,24 +11413,24 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
@@ -11359,24 +11440,24 @@
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
@@ -11386,24 +11467,24 @@
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
@@ -11413,24 +11494,24 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
@@ -11440,24 +11521,24 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
@@ -11467,24 +11548,24 @@
         <v>1</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
@@ -11494,24 +11575,24 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
@@ -11521,24 +11602,24 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
@@ -11548,24 +11629,24 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
@@ -11575,24 +11656,24 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
@@ -11602,24 +11683,24 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
@@ -11629,18 +11710,18 @@
         <v>1</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
@@ -11650,18 +11731,18 @@
         <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
@@ -11671,18 +11752,18 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
@@ -11692,18 +11773,18 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
@@ -11713,18 +11794,18 @@
         <v>1</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
@@ -11734,18 +11815,18 @@
         <v>1</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
@@ -11755,18 +11836,18 @@
         <v>1</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
@@ -11776,18 +11857,18 @@
         <v>1</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
@@ -11797,18 +11878,18 @@
         <v>1</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
@@ -11818,18 +11899,18 @@
         <v>1</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
@@ -11839,19 +11920,19 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
@@ -11861,18 +11942,18 @@
         <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
@@ -11882,18 +11963,18 @@
         <v>1</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
@@ -11906,18 +11987,18 @@
         <v>1</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
@@ -11927,18 +12008,18 @@
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
@@ -11948,18 +12029,18 @@
         <v>1</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
@@ -11969,18 +12050,18 @@
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
@@ -11992,13 +12073,13 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
@@ -12008,18 +12089,18 @@
         <v>1</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
@@ -12029,18 +12110,18 @@
         <v>1</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
@@ -12050,18 +12131,18 @@
         <v>1</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
@@ -12071,18 +12152,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
@@ -12092,18 +12173,18 @@
         <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
@@ -12113,18 +12194,18 @@
         <v>1</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -12134,18 +12215,18 @@
         <v>1</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -12155,18 +12236,18 @@
         <v>1</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
@@ -12176,18 +12257,18 @@
         <v>1</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -12197,18 +12278,18 @@
         <v>1</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
@@ -12218,18 +12299,18 @@
         <v>1</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
@@ -12239,18 +12320,18 @@
         <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
@@ -12260,18 +12341,18 @@
         <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
@@ -12281,18 +12362,18 @@
         <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
@@ -12302,18 +12383,18 @@
         <v>1</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="C76" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
@@ -12323,18 +12404,18 @@
         <v>1</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12344,7 +12425,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12352,10 +12433,10 @@
         <v>51</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12365,18 +12446,18 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12386,18 +12467,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12407,18 +12488,18 @@
         <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
@@ -12428,18 +12509,18 @@
         <v>1</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
@@ -12449,18 +12530,18 @@
         <v>1</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
@@ -12470,18 +12551,18 @@
         <v>1</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
@@ -12491,18 +12572,18 @@
         <v>1</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12512,18 +12593,18 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
@@ -12533,18 +12614,18 @@
         <v>1</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
@@ -12554,18 +12635,18 @@
         <v>1</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
@@ -12575,18 +12656,18 @@
         <v>1</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
@@ -12596,18 +12677,18 @@
         <v>1</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
@@ -12617,18 +12698,18 @@
         <v>1</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
@@ -12638,18 +12719,18 @@
         <v>1</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12659,18 +12740,18 @@
         <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
@@ -12680,18 +12761,18 @@
         <v>1</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
@@ -12701,18 +12782,18 @@
         <v>1</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
@@ -12722,18 +12803,18 @@
         <v>1</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
@@ -12743,18 +12824,18 @@
         <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
@@ -12764,18 +12845,18 @@
         <v>1</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12785,18 +12866,18 @@
         <v>1</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
@@ -12806,18 +12887,18 @@
         <v>1</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
@@ -12827,18 +12908,18 @@
         <v>1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
@@ -12848,18 +12929,18 @@
         <v>1</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
@@ -12869,18 +12950,18 @@
         <v>1</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
@@ -12890,18 +12971,18 @@
         <v>1</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -12911,18 +12992,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -12932,18 +13013,18 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
@@ -12953,18 +13034,18 @@
         <v>1</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
@@ -12974,18 +13055,18 @@
         <v>1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
@@ -12995,18 +13076,18 @@
         <v>1</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
@@ -13016,18 +13097,18 @@
         <v>1</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
@@ -13037,18 +13118,18 @@
         <v>1</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
@@ -13057,13 +13138,13 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -13072,13 +13153,13 @@
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
@@ -13090,10 +13171,10 @@
         <v>50</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
@@ -13103,37 +13184,37 @@
         <v>0</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13141,10 +13222,10 @@
         <v>47</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
@@ -13154,48 +13235,48 @@
         <v>0</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -13204,13 +13285,13 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
@@ -13219,13 +13300,13 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
@@ -13234,13 +13315,13 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
@@ -13252,10 +13333,10 @@
         <v>53</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
@@ -13265,48 +13346,48 @@
         <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
@@ -13315,13 +13396,13 @@
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
@@ -13330,13 +13411,13 @@
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -13345,13 +13426,13 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
@@ -13360,13 +13441,13 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13375,13 +13456,13 @@
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13390,13 +13471,13 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -13405,13 +13486,13 @@
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
@@ -13421,48 +13502,48 @@
         <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -13471,13 +13552,13 @@
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -13486,13 +13567,13 @@
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
@@ -13501,13 +13582,13 @@
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -13516,13 +13597,13 @@
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -13531,13 +13612,13 @@
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13546,13 +13627,13 @@
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13561,13 +13642,13 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13576,13 +13657,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13591,13 +13672,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13606,13 +13687,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13621,13 +13702,13 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13636,13 +13717,13 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13651,13 +13732,13 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13666,13 +13747,13 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13681,13 +13762,13 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
@@ -13696,13 +13777,13 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13711,13 +13792,13 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13726,13 +13807,13 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13741,13 +13822,13 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13756,13 +13837,13 @@
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
@@ -13771,13 +13852,13 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13786,13 +13867,13 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13801,13 +13882,13 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13816,13 +13897,13 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13831,13 +13912,13 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13846,13 +13927,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13861,13 +13942,13 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13876,13 +13957,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13891,13 +13972,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13906,13 +13987,13 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13921,13 +14002,13 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13936,13 +14017,13 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13951,13 +14032,13 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13966,13 +14047,13 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -13981,13 +14062,13 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -13996,13 +14077,13 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -14011,13 +14092,13 @@
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -14026,13 +14107,13 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -14041,13 +14122,13 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -14056,13 +14137,13 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -14071,13 +14152,13 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -14086,13 +14167,13 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -14101,13 +14182,13 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -14116,13 +14197,13 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -14131,13 +14212,13 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -14146,13 +14227,13 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14161,13 +14242,13 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14176,13 +14257,13 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14191,13 +14272,13 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14206,13 +14287,13 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -14221,13 +14302,13 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
@@ -14236,13 +14317,13 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14251,13 +14332,13 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14266,13 +14347,13 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -14281,13 +14362,13 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -14296,13 +14377,13 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -14311,13 +14392,13 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14326,13 +14407,13 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14341,13 +14422,13 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14356,13 +14437,13 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14371,13 +14452,13 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14386,13 +14467,13 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14401,13 +14482,13 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14416,13 +14497,13 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
@@ -14431,13 +14512,13 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
@@ -14446,13 +14527,13 @@
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14461,13 +14542,13 @@
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
@@ -14476,13 +14557,13 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
@@ -14491,13 +14572,13 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
@@ -14506,13 +14587,13 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14521,13 +14602,13 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14536,13 +14617,13 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
@@ -14551,13 +14632,13 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14566,13 +14647,13 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14581,13 +14662,13 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14596,13 +14677,13 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14611,13 +14692,13 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
@@ -14626,13 +14707,13 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14641,13 +14722,13 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14656,13 +14737,13 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
@@ -14671,13 +14752,13 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14686,13 +14767,13 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14701,13 +14782,13 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14716,13 +14797,13 @@
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14731,13 +14812,13 @@
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
@@ -14746,13 +14827,13 @@
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14761,13 +14842,13 @@
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
@@ -14776,13 +14857,13 @@
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
@@ -14791,13 +14872,13 @@
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14806,13 +14887,13 @@
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14821,13 +14902,13 @@
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14836,13 +14917,13 @@
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
@@ -14851,13 +14932,13 @@
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
@@ -14866,13 +14947,13 @@
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -14881,13 +14962,13 @@
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
@@ -14896,13 +14977,13 @@
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
@@ -14911,13 +14992,13 @@
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
@@ -14926,13 +15007,13 @@
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -14941,13 +15022,13 @@
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -14956,13 +15037,13 @@
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -14971,13 +15052,13 @@
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -14986,13 +15067,13 @@
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -15001,13 +15082,13 @@
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
@@ -15017,48 +15098,48 @@
         <v>0</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B233" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="C233" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -15067,13 +15148,13 @@
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
@@ -15082,13 +15163,13 @@
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
@@ -15097,13 +15178,13 @@
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
@@ -15112,13 +15193,13 @@
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15127,13 +15208,13 @@
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
@@ -15143,37 +15224,37 @@
         <v>0</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P238" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15181,10 +15262,10 @@
         <v>45</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
@@ -15194,48 +15275,48 @@
         <v>0</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N239" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P239" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
@@ -15245,48 +15326,48 @@
         <v>0</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N240" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15295,13 +15376,13 @@
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
@@ -15310,13 +15391,13 @@
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15325,13 +15406,13 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15340,13 +15421,13 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
@@ -15355,13 +15436,13 @@
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15371,48 +15452,48 @@
         <v>0</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15421,13 +15502,13 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15436,13 +15517,13 @@
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15451,13 +15532,13 @@
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
@@ -15466,13 +15547,13 @@
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
@@ -15481,13 +15562,13 @@
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
@@ -15496,13 +15577,13 @@
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
@@ -15511,13 +15592,13 @@
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15526,13 +15607,13 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
@@ -15541,13 +15622,13 @@
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
@@ -15556,13 +15637,13 @@
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
@@ -15571,13 +15652,13 @@
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
@@ -15586,13 +15667,13 @@
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
@@ -15602,48 +15683,48 @@
         <v>0</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N259" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P259" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
@@ -15652,13 +15733,13 @@
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
@@ -15667,13 +15748,13 @@
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
@@ -15682,13 +15763,13 @@
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
@@ -15697,13 +15778,13 @@
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
@@ -15712,13 +15793,13 @@
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
@@ -15727,13 +15808,13 @@
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
@@ -15742,13 +15823,13 @@
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D267" s="2" t="n">
         <f aca="false">SUM(E267,G267,I267,K267,M267,O267)</f>
@@ -15757,13 +15838,13 @@
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D268" s="2" t="n">
         <f aca="false">SUM(E268,G268,I268,K268,M268,O268)</f>
@@ -15773,37 +15854,121 @@
         <v>0</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N268" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P268" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <f aca="false">SUM(E269,G269,I269,K269,M269,O269)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D270" s="2" t="n">
+        <f aca="false">SUM(E270,G270,I270,K270,M270,O270)</f>
+        <v>2</v>
+      </c>
+      <c r="E270" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="O270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P270" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <f aca="false">SUM(E271,G271,I271,K271,M271,O271)</f>
+        <v>1</v>
+      </c>
+      <c r="O271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P271" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <f aca="false">SUM(E272,G272,I272,K272,M272,O272)</f>
+        <v>1</v>
+      </c>
+      <c r="O272" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P272" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="559">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Tzaangors</t>
   </si>
   <si>
-    <t xml:space="preserve">Short Break</t>
+    <t xml:space="preserve">Long Break</t>
   </si>
   <si>
     <t xml:space="preserve">Ulthwé Army</t>
@@ -606,6 +606,12 @@
   </si>
   <si>
     <t xml:space="preserve">Chracian Noble 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krethusa the Croneseer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daughters of Khaine</t>
   </si>
   <si>
     <t xml:space="preserve">Paint</t>
@@ -3338,11 +3344,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="40720927"/>
-        <c:axId val="8761026"/>
+        <c:axId val="39370929"/>
+        <c:axId val="7559074"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="40720927"/>
+        <c:axId val="39370929"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3374,7 +3380,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8761026"/>
+        <c:crossAx val="7559074"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3382,7 +3388,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8761026"/>
+        <c:axId val="7559074"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3421,7 +3427,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40720927"/>
+        <c:crossAx val="39370929"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3462,9 +3468,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>621000</xdr:colOff>
+      <xdr:colOff>620640</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>23400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3473,7 +3479,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7723080" y="7024320"/>
-        <a:ext cx="7509240" cy="3177720"/>
+        <a:ext cx="7508880" cy="3177360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3806,7 +3812,7 @@
       </c>
       <c r="H2" s="2" t="n">
         <f aca="false">SUM(C2:C1035)</f>
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -7300,11 +7306,25 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
         <v>45870</v>
       </c>
-      <c r="B190" s="2"/>
+      <c r="B190" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
@@ -10438,63 +10458,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
@@ -10504,36 +10524,36 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10543,30 +10563,30 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
@@ -10576,30 +10596,30 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
@@ -10609,30 +10629,30 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
@@ -10642,30 +10662,30 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
@@ -10675,30 +10695,30 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10708,30 +10728,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10741,30 +10761,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10774,30 +10794,30 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
@@ -10807,30 +10827,30 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
@@ -10840,30 +10860,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
@@ -10873,30 +10893,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -10906,30 +10926,30 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
@@ -10939,7 +10959,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>1</v>
@@ -10948,18 +10968,18 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -10969,30 +10989,30 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
@@ -11002,24 +11022,24 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
@@ -11029,36 +11049,36 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
@@ -11068,24 +11088,24 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
@@ -11095,24 +11115,24 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
@@ -11122,24 +11142,24 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
@@ -11149,24 +11169,24 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -11176,24 +11196,24 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
@@ -11203,24 +11223,24 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
@@ -11230,24 +11250,24 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
@@ -11257,24 +11277,24 @@
         <v>1</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
@@ -11284,7 +11304,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>1</v>
@@ -11292,13 +11312,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
@@ -11308,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>1</v>
@@ -11316,13 +11336,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
@@ -11332,24 +11352,24 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
@@ -11359,24 +11379,24 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
@@ -11386,24 +11406,24 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
@@ -11413,24 +11433,24 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
@@ -11440,24 +11460,24 @@
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
@@ -11467,24 +11487,24 @@
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
@@ -11494,24 +11514,24 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
@@ -11521,24 +11541,24 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
@@ -11548,24 +11568,24 @@
         <v>1</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
@@ -11575,24 +11595,24 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
@@ -11602,24 +11622,24 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
@@ -11629,24 +11649,24 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
@@ -11656,24 +11676,24 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
@@ -11683,24 +11703,24 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
@@ -11710,18 +11730,18 @@
         <v>1</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
@@ -11731,18 +11751,18 @@
         <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
@@ -11752,18 +11772,18 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
@@ -11773,18 +11793,18 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
@@ -11794,18 +11814,18 @@
         <v>1</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
@@ -11815,18 +11835,18 @@
         <v>1</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
@@ -11836,18 +11856,18 @@
         <v>1</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
@@ -11857,18 +11877,18 @@
         <v>1</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
@@ -11878,18 +11898,18 @@
         <v>1</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
@@ -11899,18 +11919,18 @@
         <v>1</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
@@ -11920,19 +11940,19 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
@@ -11942,18 +11962,18 @@
         <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
@@ -11963,18 +11983,18 @@
         <v>1</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
@@ -11987,18 +12007,18 @@
         <v>1</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
@@ -12008,18 +12028,18 @@
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
@@ -12029,18 +12049,18 @@
         <v>1</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
@@ -12050,18 +12070,18 @@
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
@@ -12073,13 +12093,13 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
@@ -12089,18 +12109,18 @@
         <v>1</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
@@ -12110,18 +12130,18 @@
         <v>1</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
@@ -12131,18 +12151,18 @@
         <v>1</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
@@ -12152,18 +12172,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
@@ -12173,18 +12193,18 @@
         <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
@@ -12194,18 +12214,18 @@
         <v>1</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -12215,18 +12235,18 @@
         <v>1</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -12236,18 +12256,18 @@
         <v>1</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
@@ -12257,18 +12277,18 @@
         <v>1</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -12278,18 +12298,18 @@
         <v>1</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
@@ -12299,18 +12319,18 @@
         <v>1</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
@@ -12320,18 +12340,18 @@
         <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
@@ -12341,18 +12361,18 @@
         <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
@@ -12362,18 +12382,18 @@
         <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
@@ -12383,18 +12403,18 @@
         <v>1</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
@@ -12404,18 +12424,18 @@
         <v>1</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12425,7 +12445,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12433,10 +12453,10 @@
         <v>51</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12446,18 +12466,18 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12467,18 +12487,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12488,18 +12508,18 @@
         <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
@@ -12509,18 +12529,18 @@
         <v>1</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
@@ -12530,18 +12550,18 @@
         <v>1</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
@@ -12551,18 +12571,18 @@
         <v>1</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
@@ -12572,18 +12592,18 @@
         <v>1</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12593,18 +12613,18 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
@@ -12614,18 +12634,18 @@
         <v>1</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
@@ -12635,18 +12655,18 @@
         <v>1</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
@@ -12656,18 +12676,18 @@
         <v>1</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
@@ -12677,18 +12697,18 @@
         <v>1</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
@@ -12698,18 +12718,18 @@
         <v>1</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
@@ -12719,18 +12739,18 @@
         <v>1</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12740,18 +12760,18 @@
         <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
@@ -12761,18 +12781,18 @@
         <v>1</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
@@ -12782,18 +12802,18 @@
         <v>1</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
@@ -12803,18 +12823,18 @@
         <v>1</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
@@ -12824,18 +12844,18 @@
         <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
@@ -12845,18 +12865,18 @@
         <v>1</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12866,18 +12886,18 @@
         <v>1</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
@@ -12887,18 +12907,18 @@
         <v>1</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
@@ -12908,18 +12928,18 @@
         <v>1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
@@ -12929,18 +12949,18 @@
         <v>1</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
@@ -12950,18 +12970,18 @@
         <v>1</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
@@ -12971,18 +12991,18 @@
         <v>1</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -12992,18 +13012,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -13013,18 +13033,18 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
@@ -13034,18 +13054,18 @@
         <v>1</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
@@ -13055,18 +13075,18 @@
         <v>1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
@@ -13076,18 +13096,18 @@
         <v>1</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
@@ -13097,18 +13117,18 @@
         <v>1</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
@@ -13118,18 +13138,18 @@
         <v>1</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
@@ -13138,13 +13158,13 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -13153,13 +13173,13 @@
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
@@ -13171,10 +13191,10 @@
         <v>50</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
@@ -13184,37 +13204,37 @@
         <v>0</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13222,10 +13242,10 @@
         <v>47</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
@@ -13235,48 +13255,48 @@
         <v>0</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -13285,13 +13305,13 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
@@ -13300,13 +13320,13 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
@@ -13315,13 +13335,13 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
@@ -13333,10 +13353,10 @@
         <v>53</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
@@ -13346,48 +13366,48 @@
         <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
@@ -13396,13 +13416,13 @@
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
@@ -13411,13 +13431,13 @@
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -13426,13 +13446,13 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
@@ -13441,13 +13461,13 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13456,13 +13476,13 @@
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13471,13 +13491,13 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -13486,13 +13506,13 @@
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
@@ -13502,48 +13522,48 @@
         <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -13552,13 +13572,13 @@
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -13567,13 +13587,13 @@
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
@@ -13582,13 +13602,13 @@
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -13597,13 +13617,13 @@
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -13612,13 +13632,13 @@
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13627,13 +13647,13 @@
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13642,13 +13662,13 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13657,13 +13677,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13672,13 +13692,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13687,13 +13707,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13702,13 +13722,13 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13717,13 +13737,13 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13732,13 +13752,13 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13747,13 +13767,13 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13762,13 +13782,13 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
@@ -13777,13 +13797,13 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13792,13 +13812,13 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13807,13 +13827,13 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13822,13 +13842,13 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13837,13 +13857,13 @@
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
@@ -13852,13 +13872,13 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13867,13 +13887,13 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13882,13 +13902,13 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13897,13 +13917,13 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13912,13 +13932,13 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13927,13 +13947,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13942,13 +13962,13 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13957,13 +13977,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13972,13 +13992,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13987,13 +14007,13 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -14002,13 +14022,13 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -14017,13 +14037,13 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -14032,13 +14052,13 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -14047,13 +14067,13 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -14062,13 +14082,13 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -14077,13 +14097,13 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -14092,13 +14112,13 @@
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -14107,13 +14127,13 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -14122,13 +14142,13 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -14137,13 +14157,13 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -14152,13 +14172,13 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -14167,13 +14187,13 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -14182,13 +14202,13 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -14197,13 +14217,13 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -14212,13 +14232,13 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -14227,13 +14247,13 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14242,13 +14262,13 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14257,13 +14277,13 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14272,13 +14292,13 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14287,13 +14307,13 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -14302,13 +14322,13 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
@@ -14317,13 +14337,13 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14332,13 +14352,13 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14347,13 +14367,13 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -14362,13 +14382,13 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -14377,13 +14397,13 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -14392,13 +14412,13 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14407,13 +14427,13 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14422,13 +14442,13 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14437,13 +14457,13 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14452,13 +14472,13 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14467,13 +14487,13 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14482,13 +14502,13 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14497,13 +14517,13 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
@@ -14512,13 +14532,13 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
@@ -14527,13 +14547,13 @@
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14542,13 +14562,13 @@
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
@@ -14557,13 +14577,13 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
@@ -14572,13 +14592,13 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
@@ -14587,13 +14607,13 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14602,13 +14622,13 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14617,13 +14637,13 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
@@ -14632,13 +14652,13 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14647,13 +14667,13 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14662,13 +14682,13 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14677,13 +14697,13 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14692,13 +14712,13 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
@@ -14707,13 +14727,13 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14722,13 +14742,13 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14737,13 +14757,13 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
@@ -14752,13 +14772,13 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14767,13 +14787,13 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14782,13 +14802,13 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14797,13 +14817,13 @@
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14812,13 +14832,13 @@
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
@@ -14827,13 +14847,13 @@
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14842,13 +14862,13 @@
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
@@ -14857,13 +14877,13 @@
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
@@ -14872,13 +14892,13 @@
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14887,13 +14907,13 @@
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14902,13 +14922,13 @@
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14917,13 +14937,13 @@
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
@@ -14932,13 +14952,13 @@
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
@@ -14947,13 +14967,13 @@
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -14962,13 +14982,13 @@
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
@@ -14977,13 +14997,13 @@
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
@@ -14992,13 +15012,13 @@
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
@@ -15007,13 +15027,13 @@
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -15022,13 +15042,13 @@
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -15037,13 +15057,13 @@
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -15052,13 +15072,13 @@
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -15067,13 +15087,13 @@
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -15082,13 +15102,13 @@
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="C232" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
@@ -15098,48 +15118,48 @@
         <v>0</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -15148,13 +15168,13 @@
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
@@ -15163,13 +15183,13 @@
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
@@ -15178,13 +15198,13 @@
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
@@ -15193,13 +15213,13 @@
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15208,13 +15228,13 @@
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
@@ -15224,37 +15244,37 @@
         <v>0</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P238" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15262,10 +15282,10 @@
         <v>45</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
@@ -15275,48 +15295,48 @@
         <v>0</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N239" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P239" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
@@ -15326,48 +15346,48 @@
         <v>0</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N240" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15376,13 +15396,13 @@
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
@@ -15391,13 +15411,13 @@
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15406,13 +15426,13 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15421,13 +15441,13 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
@@ -15436,13 +15456,13 @@
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15452,48 +15472,48 @@
         <v>0</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15502,13 +15522,13 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15517,13 +15537,13 @@
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15532,13 +15552,13 @@
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
@@ -15547,13 +15567,13 @@
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
@@ -15562,13 +15582,13 @@
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
@@ -15577,13 +15597,13 @@
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
@@ -15592,13 +15612,13 @@
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15607,13 +15627,13 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
@@ -15622,13 +15642,13 @@
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
@@ -15637,13 +15657,13 @@
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
@@ -15652,13 +15672,13 @@
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
@@ -15667,13 +15687,13 @@
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
@@ -15683,48 +15703,48 @@
         <v>0</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N259" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P259" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
@@ -15733,13 +15753,13 @@
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
@@ -15748,13 +15768,13 @@
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
@@ -15763,13 +15783,13 @@
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
@@ -15778,13 +15798,13 @@
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
@@ -15793,13 +15813,13 @@
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
@@ -15808,13 +15828,13 @@
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
@@ -15823,13 +15843,13 @@
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D267" s="2" t="n">
         <f aca="false">SUM(E267,G267,I267,K267,M267,O267)</f>
@@ -15838,13 +15858,13 @@
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D268" s="2" t="n">
         <f aca="false">SUM(E268,G268,I268,K268,M268,O268)</f>
@@ -15854,48 +15874,48 @@
         <v>0</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N268" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P268" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D269" s="2" t="n">
         <f aca="false">SUM(E269,G269,I269,K269,M269,O269)</f>
@@ -15904,40 +15924,40 @@
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D270" s="2" t="n">
         <f aca="false">SUM(E270,G270,I270,K270,M270,O270)</f>
         <v>2</v>
       </c>
-      <c r="E270" s="0" t="n">
+      <c r="E270" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O270" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="7" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D271" s="2" t="n">
         <f aca="false">SUM(E271,G271,I271,K271,M271,O271)</f>
@@ -15947,18 +15967,18 @@
         <v>1</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="7" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D272" s="2" t="n">
         <f aca="false">SUM(E272,G272,I272,K272,M272,O272)</f>
@@ -15968,7 +15988,7 @@
         <v>1</v>
       </c>
       <c r="P272" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="561">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Tzaangors</t>
   </si>
   <si>
-    <t xml:space="preserve">Long Break</t>
+    <t xml:space="preserve">Chrace Spearmen / Archers</t>
   </si>
   <si>
     <t xml:space="preserve">Ulthwé Army</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">Black Guardians</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldeari</t>
+    <t xml:space="preserve">Aeldari</t>
   </si>
   <si>
     <t xml:space="preserve">Laser Yellow</t>
@@ -612,6 +612,12 @@
   </si>
   <si>
     <t xml:space="preserve">Daughters of Khaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eldrad Ulthran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warlock</t>
   </si>
   <si>
     <t xml:space="preserve">Paint</t>
@@ -2180,18 +2186,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" lang="en-US" sz="1400" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" lang="en-US" sz="1400" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Aptos Narrow"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" lang="en-US" sz="1400" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="595959"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:t>Timetable</a:t>
@@ -2239,10 +2244,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
@@ -2255,6 +2261,15 @@
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3344,11 +3359,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="39370929"/>
-        <c:axId val="7559074"/>
+        <c:axId val="72561705"/>
+        <c:axId val="31296794"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="39370929"/>
+        <c:axId val="72561705"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3371,16 +3386,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7559074"/>
+        <c:crossAx val="31296794"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3388,7 +3404,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7559074"/>
+        <c:axId val="31296794"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3418,16 +3434,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39370929"/>
+        <c:crossAx val="72561705"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3468,9 +3485,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>620640</xdr:colOff>
+      <xdr:colOff>619920</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>23400</xdr:rowOff>
+      <xdr:rowOff>22680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3479,7 +3496,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7723080" y="7024320"/>
-        <a:ext cx="7508880" cy="3177360"/>
+        <a:ext cx="7508160" cy="3176640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3753,7 +3770,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J1198"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.73"/>
@@ -3812,7 +3829,7 @@
       </c>
       <c r="H2" s="2" t="n">
         <f aca="false">SUM(C2:C1035)</f>
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -7332,17 +7349,45 @@
       </c>
       <c r="B191" s="2"/>
     </row>
-    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
         <v>45931</v>
       </c>
-      <c r="B192" s="2"/>
-    </row>
-    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="n">
         <v>45962</v>
       </c>
-      <c r="B193" s="2"/>
+      <c r="B193" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="n">
@@ -10438,7 +10483,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P1048576"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="19.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.53"/>
@@ -10458,63 +10503,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
@@ -10524,36 +10569,36 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10563,30 +10608,30 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
@@ -10596,30 +10641,30 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
@@ -10629,30 +10674,30 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
@@ -10662,30 +10707,30 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
@@ -10695,30 +10740,30 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10728,30 +10773,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10761,30 +10806,30 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10794,30 +10839,30 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
@@ -10827,30 +10872,30 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
@@ -10860,30 +10905,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
@@ -10893,30 +10938,30 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -10926,30 +10971,30 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
@@ -10959,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>1</v>
@@ -10968,18 +11013,18 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -10989,30 +11034,30 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
@@ -11022,24 +11067,24 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
@@ -11049,36 +11094,36 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
@@ -11088,24 +11133,24 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
@@ -11115,24 +11160,24 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
@@ -11142,24 +11187,24 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
@@ -11169,24 +11214,24 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -11196,24 +11241,24 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
@@ -11223,24 +11268,24 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
@@ -11250,24 +11295,24 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
@@ -11277,24 +11322,24 @@
         <v>1</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
@@ -11304,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>1</v>
@@ -11312,13 +11357,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
@@ -11328,7 +11373,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>1</v>
@@ -11336,13 +11381,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
@@ -11352,24 +11397,24 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
@@ -11379,24 +11424,24 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
@@ -11406,24 +11451,24 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
@@ -11433,24 +11478,24 @@
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
@@ -11460,24 +11505,24 @@
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
@@ -11487,24 +11532,24 @@
         <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
@@ -11514,24 +11559,24 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
@@ -11541,24 +11586,24 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
@@ -11568,24 +11613,24 @@
         <v>1</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
@@ -11595,24 +11640,24 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
@@ -11622,24 +11667,24 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
@@ -11649,24 +11694,24 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
@@ -11676,24 +11721,24 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
@@ -11703,24 +11748,24 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
@@ -11730,18 +11775,18 @@
         <v>1</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
@@ -11751,18 +11796,18 @@
         <v>1</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
@@ -11772,18 +11817,18 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
@@ -11793,18 +11838,18 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
@@ -11814,18 +11859,18 @@
         <v>1</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
@@ -11835,18 +11880,18 @@
         <v>1</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
@@ -11856,18 +11901,18 @@
         <v>1</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
@@ -11877,18 +11922,18 @@
         <v>1</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
@@ -11898,18 +11943,18 @@
         <v>1</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
@@ -11919,18 +11964,18 @@
         <v>1</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
@@ -11940,19 +11985,19 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
@@ -11962,18 +12007,18 @@
         <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
@@ -11983,18 +12028,18 @@
         <v>1</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
@@ -12007,18 +12052,18 @@
         <v>1</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
@@ -12028,18 +12073,18 @@
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
@@ -12049,18 +12094,18 @@
         <v>1</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
@@ -12070,18 +12115,18 @@
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
@@ -12093,13 +12138,13 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
@@ -12109,18 +12154,18 @@
         <v>1</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
@@ -12130,18 +12175,18 @@
         <v>1</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
@@ -12151,18 +12196,18 @@
         <v>1</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
@@ -12172,18 +12217,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
@@ -12193,18 +12238,18 @@
         <v>1</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
@@ -12214,18 +12259,18 @@
         <v>1</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -12235,18 +12280,18 @@
         <v>1</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -12256,18 +12301,18 @@
         <v>1</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
@@ -12277,18 +12322,18 @@
         <v>1</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
@@ -12298,18 +12343,18 @@
         <v>1</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
@@ -12319,18 +12364,18 @@
         <v>1</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
@@ -12340,18 +12385,18 @@
         <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
@@ -12361,18 +12406,18 @@
         <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
@@ -12382,18 +12427,18 @@
         <v>1</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
@@ -12403,18 +12448,18 @@
         <v>1</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
@@ -12424,18 +12469,18 @@
         <v>1</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12445,7 +12490,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12453,10 +12498,10 @@
         <v>51</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12466,18 +12511,18 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12487,18 +12532,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12508,18 +12553,18 @@
         <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
@@ -12529,18 +12574,18 @@
         <v>1</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
@@ -12550,18 +12595,18 @@
         <v>1</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
@@ -12571,18 +12616,18 @@
         <v>1</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
@@ -12592,18 +12637,18 @@
         <v>1</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12613,18 +12658,18 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
@@ -12634,18 +12679,18 @@
         <v>1</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
@@ -12655,18 +12700,18 @@
         <v>1</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
@@ -12676,18 +12721,18 @@
         <v>1</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
@@ -12697,18 +12742,18 @@
         <v>1</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
@@ -12718,18 +12763,18 @@
         <v>1</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
@@ -12739,18 +12784,18 @@
         <v>1</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12760,18 +12805,18 @@
         <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
@@ -12781,18 +12826,18 @@
         <v>1</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
@@ -12802,18 +12847,18 @@
         <v>1</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
@@ -12823,18 +12868,18 @@
         <v>1</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
@@ -12844,18 +12889,18 @@
         <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
@@ -12865,18 +12910,18 @@
         <v>1</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12886,18 +12931,18 @@
         <v>1</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
@@ -12907,18 +12952,18 @@
         <v>1</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
@@ -12928,18 +12973,18 @@
         <v>1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
@@ -12949,18 +12994,18 @@
         <v>1</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
@@ -12970,18 +13015,18 @@
         <v>1</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
@@ -12991,18 +13036,18 @@
         <v>1</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -13012,18 +13057,18 @@
         <v>1</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -13033,18 +13078,18 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
@@ -13054,18 +13099,18 @@
         <v>1</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
@@ -13075,18 +13120,18 @@
         <v>1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
@@ -13096,18 +13141,18 @@
         <v>1</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
@@ -13117,18 +13162,18 @@
         <v>1</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
@@ -13138,18 +13183,18 @@
         <v>1</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
@@ -13158,13 +13203,13 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -13173,13 +13218,13 @@
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
@@ -13191,10 +13236,10 @@
         <v>50</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
@@ -13204,37 +13249,37 @@
         <v>0</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O114" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13242,10 +13287,10 @@
         <v>47</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
@@ -13255,48 +13300,48 @@
         <v>0</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -13305,13 +13350,13 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
@@ -13320,13 +13365,13 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
@@ -13335,13 +13380,13 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
@@ -13353,10 +13398,10 @@
         <v>53</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
@@ -13366,48 +13411,48 @@
         <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O120" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
@@ -13416,13 +13461,13 @@
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
@@ -13431,13 +13476,13 @@
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -13446,13 +13491,13 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
@@ -13461,13 +13506,13 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13476,13 +13521,13 @@
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13491,13 +13536,13 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
@@ -13506,13 +13551,13 @@
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
@@ -13522,48 +13567,48 @@
         <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O128" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
@@ -13572,13 +13617,13 @@
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
@@ -13587,13 +13632,13 @@
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
@@ -13602,13 +13647,13 @@
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
@@ -13617,13 +13662,13 @@
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
@@ -13632,13 +13677,13 @@
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13647,13 +13692,13 @@
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13662,13 +13707,13 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13677,13 +13722,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13692,13 +13737,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13707,13 +13752,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13722,13 +13767,13 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
@@ -13737,13 +13782,13 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13752,13 +13797,13 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13767,13 +13812,13 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13782,13 +13827,13 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
@@ -13797,13 +13842,13 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
@@ -13812,13 +13857,13 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13827,13 +13872,13 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13842,13 +13887,13 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13857,13 +13902,13 @@
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
@@ -13872,13 +13917,13 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13887,13 +13932,13 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13902,13 +13947,13 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13917,13 +13962,13 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13932,13 +13977,13 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13947,13 +13992,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13962,13 +14007,13 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13977,13 +14022,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13992,13 +14037,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -14007,13 +14052,13 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -14022,13 +14067,13 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -14037,13 +14082,13 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -14052,13 +14097,13 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -14067,13 +14112,13 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
@@ -14082,13 +14127,13 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -14097,13 +14142,13 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -14112,13 +14157,13 @@
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -14127,13 +14172,13 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -14142,13 +14187,13 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -14157,13 +14202,13 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -14172,13 +14217,13 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -14187,13 +14232,13 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -14202,13 +14247,13 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -14217,13 +14262,13 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -14232,13 +14277,13 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -14247,13 +14292,13 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14262,13 +14307,13 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14277,13 +14322,13 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14292,13 +14337,13 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14307,13 +14352,13 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
@@ -14322,13 +14367,13 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
@@ -14337,13 +14382,13 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14352,13 +14397,13 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14367,13 +14412,13 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
@@ -14382,13 +14427,13 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
@@ -14397,13 +14442,13 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
@@ -14412,13 +14457,13 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14427,13 +14472,13 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14442,13 +14487,13 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14457,13 +14502,13 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14472,13 +14517,13 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14487,13 +14532,13 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14502,13 +14547,13 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14517,13 +14562,13 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
@@ -14532,13 +14577,13 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
@@ -14547,13 +14592,13 @@
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14562,13 +14607,13 @@
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
@@ -14577,13 +14622,13 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
@@ -14592,13 +14637,13 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
@@ -14607,13 +14652,13 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14622,13 +14667,13 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14637,13 +14682,13 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
@@ -14652,13 +14697,13 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14667,13 +14712,13 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
@@ -14682,13 +14727,13 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14697,13 +14742,13 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
@@ -14712,13 +14757,13 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
@@ -14727,13 +14772,13 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14742,13 +14787,13 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
@@ -14757,13 +14802,13 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
@@ -14772,13 +14817,13 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14787,13 +14832,13 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14802,13 +14847,13 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
@@ -14817,13 +14862,13 @@
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
@@ -14832,13 +14877,13 @@
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
@@ -14847,13 +14892,13 @@
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14862,13 +14907,13 @@
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
@@ -14877,13 +14922,13 @@
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
@@ -14892,13 +14937,13 @@
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
@@ -14907,13 +14952,13 @@
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
@@ -14922,13 +14967,13 @@
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
@@ -14937,13 +14982,13 @@
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
@@ -14952,13 +14997,13 @@
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
@@ -14967,13 +15012,13 @@
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -14982,13 +15027,13 @@
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
@@ -14997,13 +15042,13 @@
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
@@ -15012,13 +15057,13 @@
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
@@ -15027,13 +15072,13 @@
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
@@ -15042,13 +15087,13 @@
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
@@ -15057,13 +15102,13 @@
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
@@ -15072,13 +15117,13 @@
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -15087,13 +15132,13 @@
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
@@ -15102,13 +15147,13 @@
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="C232" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
@@ -15118,48 +15163,48 @@
         <v>0</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J232" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O232" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
@@ -15168,13 +15213,13 @@
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
@@ -15183,13 +15228,13 @@
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
@@ -15198,13 +15243,13 @@
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
@@ -15213,13 +15258,13 @@
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
@@ -15228,13 +15273,13 @@
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
@@ -15244,37 +15289,37 @@
         <v>0</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J238" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O238" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P238" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15282,10 +15327,10 @@
         <v>45</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
@@ -15295,48 +15340,48 @@
         <v>0</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N239" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O239" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P239" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
@@ -15346,48 +15391,48 @@
         <v>0</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N240" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O240" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15396,13 +15441,13 @@
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
@@ -15411,13 +15456,13 @@
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15426,13 +15471,13 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15441,13 +15486,13 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
@@ -15456,13 +15501,13 @@
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15472,48 +15517,48 @@
         <v>0</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O246" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15522,13 +15567,13 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15537,13 +15582,13 @@
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15552,13 +15597,13 @@
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
@@ -15567,13 +15612,13 @@
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
@@ -15582,13 +15627,13 @@
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
@@ -15597,13 +15642,13 @@
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
@@ -15612,13 +15657,13 @@
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15627,13 +15672,13 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
@@ -15642,13 +15687,13 @@
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
@@ -15657,13 +15702,13 @@
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
@@ -15672,13 +15717,13 @@
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
@@ -15687,13 +15732,13 @@
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
@@ -15703,48 +15748,48 @@
         <v>0</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N259" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O259" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P259" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
@@ -15753,13 +15798,13 @@
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
@@ -15768,13 +15813,13 @@
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
@@ -15783,13 +15828,13 @@
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
@@ -15798,13 +15843,13 @@
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
@@ -15813,13 +15858,13 @@
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
@@ -15828,13 +15873,13 @@
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
@@ -15843,13 +15888,13 @@
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D267" s="2" t="n">
         <f aca="false">SUM(E267,G267,I267,K267,M267,O267)</f>
@@ -15858,13 +15903,13 @@
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D268" s="2" t="n">
         <f aca="false">SUM(E268,G268,I268,K268,M268,O268)</f>
@@ -15874,48 +15919,48 @@
         <v>0</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N268" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P268" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D269" s="2" t="n">
         <f aca="false">SUM(E269,G269,I269,K269,M269,O269)</f>
@@ -15924,13 +15969,13 @@
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="7" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D270" s="2" t="n">
         <f aca="false">SUM(E270,G270,I270,K270,M270,O270)</f>
@@ -15940,24 +15985,24 @@
         <v>1</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O270" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="7" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D271" s="2" t="n">
         <f aca="false">SUM(E271,G271,I271,K271,M271,O271)</f>
@@ -15967,18 +16012,18 @@
         <v>1</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="7" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D272" s="2" t="n">
         <f aca="false">SUM(E272,G272,I272,K272,M272,O272)</f>
@@ -15988,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="P272" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="583">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -674,165 +674,165 @@
     <t xml:space="preserve">Details H2</t>
   </si>
   <si>
+    <t xml:space="preserve">Anthracite Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3rd Gen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragonfly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up NMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquatic Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green NMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">British Khaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold NMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grimy Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White lion fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hull Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japanese Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lilac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminous Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistachio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purulent Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddish Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahara Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sand Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White NMMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violed Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up Dragon Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volcanic Yellow</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wine Red</t>
   </si>
   <si>
-    <t xml:space="preserve">AK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3rd Gen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reds</t>
   </si>
   <si>
     <t xml:space="preserve">Leaves (up Yellow)</t>
   </si>
   <si>
-    <t xml:space="preserve">Volcanic Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violed Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Dragon Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White NMMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sand Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up NMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahara Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold NMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reddish Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purulent Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pistachio </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminous Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lilac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragonfly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japanese Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hull Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grimy Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White lion fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graphite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Olive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green NMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">British Khaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aquatic Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthracite Grey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drab Brown</t>
   </si>
   <si>
@@ -845,169 +845,172 @@
     <t xml:space="preserve">Leather</t>
   </si>
   <si>
+    <t xml:space="preserve">Abaddon Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citadel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Averland Sunset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barak-Nar Burgundy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bugman's Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celestra Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corax White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daemonette Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gal Vorbak Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey Seer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incubi Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jokaero Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khorne Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macragge Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mephiston Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morghast Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mournfang Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenician Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rakarth Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhinox Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screamer Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel Legion Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thousand Sons blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wraithbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XV-88</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zandri Dust</t>
   </si>
   <si>
-    <t xml:space="preserve">Citadel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XV-88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wraithbone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thousand Sons blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Fang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel Legion Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screamer Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhinox Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rakarth Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenician Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mournfang Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morghast Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mephiston Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macragge Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khorne Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jokaero Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incubi Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey Seer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gal Vorbak Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daemonette Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corax White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celestra Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bugman's Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barak-Nar Burgundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Averland Sunset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abaddon Black</t>
+    <t xml:space="preserve">Afro Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color Punch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole Wood</t>
   </si>
   <si>
     <t xml:space="preserve">Dragon Blood</t>
   </si>
   <si>
-    <t xml:space="preserve">Color Punch</t>
-  </si>
-  <si>
     <t xml:space="preserve">Armour</t>
   </si>
   <si>
-    <t xml:space="preserve">Afro Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whole Wood</t>
+    <t xml:space="preserve">Aethermatic Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aldeari Emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apothecary White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Templar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corvus Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cygor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gore-Grunta Fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryph-Charger Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryph-Hound Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iyanden Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nazdreg Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratling Grime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeleton Horde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snakebite Leather</t>
   </si>
   <si>
     <t xml:space="preserve">Volupus Pink</t>
   </si>
   <si>
-    <t xml:space="preserve">Contrast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snakebite Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skeleton Horde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratling Grime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nazdreg Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyanden Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryph-Hound Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryph-Charger Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gore-Grunta Fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cygor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leather Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corvus Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Templar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apothecary White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aldeari Emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aethermatic Blue</t>
+    <t xml:space="preserve">Cartacci Red</t>
   </si>
   <si>
     <t xml:space="preserve">Kimera</t>
@@ -1016,262 +1019,286 @@
     <t xml:space="preserve">Danilo Cartacci</t>
   </si>
   <si>
+    <t xml:space="preserve">Caucasian Skintone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiwi Brown</t>
+  </si>
+  <si>
     <t xml:space="preserve">Samurai Green</t>
   </si>
   <si>
-    <t xml:space="preserve">Kiwi Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caucasian Skintone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartacci Red</t>
+    <t xml:space="preserve">Alizarin Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp. Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobalt Bluegreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diarylide Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honey Moon Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mars Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluidine Red</t>
   </si>
   <si>
     <t xml:space="preserve">Ultramarine Blue</t>
   </si>
   <si>
-    <t xml:space="preserve">Exp. Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluidine Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mars Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honey Moon Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diarylide Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobalt Bluegreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alizarin Crimson</t>
+    <t xml:space="preserve">Bluegrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra Opaque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charcoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goldbrown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Yellow Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flameon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game (old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghost Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scorpena Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbarian Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bile Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronze Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charred Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elfic Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghost Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goblin Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorgon Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grunge Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jade Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturnal Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scrofulous Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sick Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Succubus Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toxic Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warlock Purple</t>
   </si>
   <si>
     <t xml:space="preserve">Warm Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">Vallejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game Color</t>
-  </si>
-  <si>
     <t xml:space="preserve">Up Skin</t>
   </si>
   <si>
     <t xml:space="preserve">White lion claws</t>
   </si>
   <si>
-    <t xml:space="preserve">Siena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra Opaque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goldbrown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charcoal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bluegrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Yellow Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flameon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warlock Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toxic Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Succubus Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scrofulous Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scarlet Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nocturnal Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midnight Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jade Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grunge Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorgon Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghost Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evil Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elfic Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charred Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronze Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Wash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbarian Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scorpena Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game (old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghost Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death White</t>
+    <t xml:space="preserve">Yellow Ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquitex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Violed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naphthol Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalocyanine Blue (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titanium White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparent Raw Umber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivid Lime Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fey</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow Medium Azo</t>
   </si>
   <si>
-    <t xml:space="preserve">Liquitex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vivid Lime Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transparent Raw Umber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titanium White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalocyanine Blue (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naphthol Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Violed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carbon Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ink</t>
+    <t xml:space="preserve">Asphalt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Scarlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiery Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turquoise</t>
   </si>
   <si>
     <t xml:space="preserve">Umber</t>
   </si>
   <si>
-    <t xml:space="preserve">Nocturna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midnight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiery Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Scarlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown Beast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asphalt </t>
+    <t xml:space="preserve">Black</t>
   </si>
   <si>
     <t xml:space="preserve">Scale 75</t>
@@ -1280,460 +1307,469 @@
     <t xml:space="preserve">Chesnut</t>
   </si>
   <si>
-    <t xml:space="preserve">Black</t>
+    <t xml:space="preserve">Administratum Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baharroth Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Reaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dawnstone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorn Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor's Children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Sunz Scarlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenrisian Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Dragon Bright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash Gitz Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabalite Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakophoni Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moot Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phalanx Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pink Horror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squig Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sybarite Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temple Guard Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thunderhawk Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trollslayer Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulthuan Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ushabti Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild Rider Red</t>
   </si>
   <si>
     <t xml:space="preserve">Yriel Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wild Rider Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ushabti Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ulthuan Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trollslayer Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thunderhawk Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temple Guard Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sybarite Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squig Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pink Horror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phalanx Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moot Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kakophoni Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabalite Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flash Gitz Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Dragon Bright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fenrisian Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evil Sunz Scarlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emperor's Children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorn Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dawnstone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Reaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baharroth Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administratum Grey</t>
+    <t xml:space="preserve">Metal Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor</t>
   </si>
   <si>
     <t xml:space="preserve">Silver</t>
   </si>
   <si>
-    <t xml:space="preserve">Metal Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armor</t>
-  </si>
-  <si>
     <t xml:space="preserve">White Gold</t>
   </si>
   <si>
     <t xml:space="preserve">Metallic</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Pisarski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fallen Grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron Hue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morning Sky</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sun Ray</t>
   </si>
   <si>
-    <t xml:space="preserve">Michal Pisarski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morning Sky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iron Hue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fallen Grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Sky</t>
+    <t xml:space="preserve">Basalt Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model (old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Scales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burnt Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloth / Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard / NMM Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Blue Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Sea Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deck Tan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ger. C. Beige WWII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luftwafe Unif. WWII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middlestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pale Grey Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prussian Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Skin tone</t>
   </si>
   <si>
     <t xml:space="preserve">Sunset Red</t>
   </si>
   <si>
-    <t xml:space="preserve">Model (old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunny Skin tone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prussian Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Park Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pale Grey Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Middlestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luftwafe Unif. WWII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ger. C. Beige WWII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck Tan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Sea Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Blue Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burnt Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloth / Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard / NMM Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beige Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Scales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basalt Grey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aluminium</t>
   </si>
   <si>
     <t xml:space="preserve">Model Air (old)</t>
   </si>
   <si>
+    <t xml:space="preserve">Model Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Plum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gladewyrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA Open</t>
+  </si>
+  <si>
     <t xml:space="preserve">Red Grey</t>
   </si>
   <si>
-    <t xml:space="preserve">Ninjon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hair /  Leather</t>
   </si>
   <si>
-    <t xml:space="preserve">Dark Plum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gladewyrm</t>
+    <t xml:space="preserve">Rogue Hobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Hot Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Red</t>
   </si>
   <si>
     <t xml:space="preserve">Ultramarine</t>
   </si>
   <si>
-    <t xml:space="preserve">Rogue Hobby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems Main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Hot Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Green</t>
+    <t xml:space="preserve">Agrax Earthshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carroburg Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drakenhof Nightshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Druchii Violet</t>
   </si>
   <si>
     <t xml:space="preserve">Reikland Fleshshade</t>
   </si>
   <si>
-    <t xml:space="preserve">Shade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Druchii Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drakenhof Nightshade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carroburg Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agrax Earthshade</t>
+    <t xml:space="preserve">Ancient Honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Army Painter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed Paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter Red</t>
   </si>
   <si>
     <t xml:space="preserve">Warrior Skin</t>
   </si>
   <si>
-    <t xml:space="preserve">Army Painter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Paint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slaughter Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goddess Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancient Honey</t>
+    <t xml:space="preserve">Bold Pyrrole Red</t>
   </si>
   <si>
     <t xml:space="preserve">Standard</t>
   </si>
   <si>
+    <t xml:space="preserve">Bold Titanium White</t>
+  </si>
+  <si>
     <t xml:space="preserve">NMM / W. Wood</t>
   </si>
   <si>
-    <t xml:space="preserve">Bold Titanium White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bold Pyrrole Red</t>
+    <t xml:space="preserve">Start Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalo Blue G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalo Blue R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalo Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Oxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm Yellow</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow Oxide</t>
   </si>
   <si>
-    <t xml:space="preserve">Start Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalo Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalo Blue R.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalo Blue G.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cold Yellow</t>
+    <t xml:space="preserve">Basilisk Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warpaints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Chalice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carnelian Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doomfire Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elder Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figgy Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forbidden Fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexed Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasper Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraken Lavender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leopard Stone Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White lion skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mocca Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moldy Wine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulled Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White lion Fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raging Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarab Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiger’s Eye Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Topaz Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tourmaline Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weird Elixir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilted Rose</t>
   </si>
   <si>
     <t xml:space="preserve">Wyvern Fury</t>
   </si>
   <si>
-    <t xml:space="preserve">Warpaints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilted Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weird Elixir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tourmaline Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White lion skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topaz Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiger’s Eye Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raging Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onyx Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White lion Fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulled Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moldy Wine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mocca Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leopard Stone Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kraken Lavender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasper Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexed Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forbidden Fruit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Figgy Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elder Flower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doomfire Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carnelian Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood Chalice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basilisk Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details</t>
+    <t xml:space="preserve">Xpress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin / Leaves / Gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitallier Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mummy White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twilight Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vampiric Purple</t>
   </si>
   <si>
     <t xml:space="preserve">Wicked Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xpress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vampiric Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twilight Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mummy White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospitallier Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin / Leaves / Gems</t>
   </si>
 </sst>
 </file>
@@ -3380,11 +3416,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="85033593"/>
-        <c:axId val="54932309"/>
+        <c:axId val="63062853"/>
+        <c:axId val="4075633"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="85033593"/>
+        <c:axId val="63062853"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3416,7 +3452,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54932309"/>
+        <c:crossAx val="4075633"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3424,7 +3460,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54932309"/>
+        <c:axId val="4075633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3463,7 +3499,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85033593"/>
+        <c:crossAx val="63062853"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3504,9 +3540,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>618480</xdr:colOff>
+      <xdr:colOff>617400</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>72360</xdr:rowOff>
+      <xdr:rowOff>71280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3515,7 +3551,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7968600" y="6922800"/>
-        <a:ext cx="7507080" cy="3175560"/>
+        <a:ext cx="7506000" cy="3174480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3570,8 +3606,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:P273" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:P273"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:P284" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:P284"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Paint"/>
     <tableColumn id="2" name="Brand"/>
@@ -3999,7 +4035,7 @@
       </c>
       <c r="H8" s="1" t="str">
         <f aca="false">INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 1), Paints!D:D, 0))</f>
-        <v>Grimy Grey</v>
+        <v>Black Red</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>29</v>
@@ -4026,7 +4062,7 @@
       </c>
       <c r="H9" s="2" t="str">
         <f aca="false" t="array" ref="H9:H9">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 2), ROW(Paints!D:D), ""), 2)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 3), Paints!D:D, 0)))</f>
-        <v>Black Red</v>
+        <v>Grimy Grey</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>20</v>
@@ -4107,7 +4143,7 @@
       </c>
       <c r="H12" s="2" t="str">
         <f aca="false" t="array" ref="H12:H12">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 5), ROW(Paints!D:D), ""), 5)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 6), Paints!D:D, 0)))</f>
-        <v>Afro Shadow</v>
+        <v>Dragon Blood</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10609,7 +10645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P1048576"/>
+  <dimension ref="A1:P284"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="19.87"/>
@@ -10692,28 +10728,28 @@
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="K2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="M2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>220</v>
+      <c r="O2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>218</v>
@@ -10723,18 +10759,24 @@
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>218</v>
@@ -10744,24 +10786,36 @@
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>225</v>
+      <c r="H4" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>218</v>
@@ -10771,48 +10825,24 @@
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>227</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>218</v>
@@ -10822,24 +10852,12 @@
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>218</v>
@@ -10849,18 +10867,12 @@
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>218</v>
@@ -10872,16 +10884,16 @@
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
         <v>1</v>
       </c>
-      <c r="O8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>234</v>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>218</v>
@@ -10891,19 +10903,13 @@
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
-        <v>2</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>236</v>
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10918,12 +10924,18 @@
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>218</v>
@@ -10933,12 +10945,18 @@
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>218</v>
@@ -10948,12 +10966,36 @@
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>218</v>
@@ -10963,18 +11005,12 @@
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>218</v>
@@ -10984,12 +11020,30 @@
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>242</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>218</v>
@@ -10999,24 +11053,48 @@
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>218</v>
@@ -11026,24 +11104,48 @@
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>218</v>
@@ -11053,48 +11155,24 @@
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>227</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>50</v>
+        <v>249</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>218</v>
@@ -11104,48 +11182,24 @@
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>227</v>
+        <v>2</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>218</v>
@@ -11155,30 +11209,12 @@
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
-        <v>3</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>218</v>
@@ -11188,12 +11224,18 @@
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>218</v>
@@ -11203,36 +11245,12 @@
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
-        <v>4</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>218</v>
@@ -11242,18 +11260,12 @@
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>218</v>
@@ -11263,18 +11275,12 @@
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
-        <v>1</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>218</v>
@@ -11284,18 +11290,24 @@
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
-        <v>1</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>257</v>
+        <v>2</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>218</v>
@@ -11307,11 +11319,11 @@
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
         <v>1</v>
       </c>
-      <c r="G25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>259</v>
+      <c r="O25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11326,7 +11338,13 @@
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11341,12 +11359,24 @@
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>262</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>218</v>
@@ -11356,24 +11386,48 @@
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>246</v>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>247</v>
       </c>
+      <c r="I28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>218</v>
@@ -11383,31 +11437,19 @@
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
-        <v>4</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>264</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>264</v>
+      <c r="H29" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11422,24 +11464,18 @@
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
-        <v>2</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>267</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>218</v>
@@ -11451,23 +11487,23 @@
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
         <v>3</v>
       </c>
+      <c r="E31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11494,7 +11530,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11509,13 +11545,7 @@
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
-        <v>1</v>
-      </c>
-      <c r="O33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11547,16 +11577,19 @@
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
         <v>1</v>
       </c>
+      <c r="H35" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>275</v>
@@ -11566,12 +11599,18 @@
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>275</v>
@@ -11586,7 +11625,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>275</v>
@@ -11596,13 +11635,7 @@
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
-        <v>1</v>
-      </c>
-      <c r="K38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11617,12 +11650,24 @@
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>275</v>
@@ -11637,7 +11682,7 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>275</v>
@@ -11647,12 +11692,18 @@
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>275</v>
@@ -11667,7 +11718,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>275</v>
@@ -11677,12 +11728,18 @@
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>275</v>
@@ -11697,7 +11754,7 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>275</v>
@@ -11712,7 +11769,7 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>275</v>
@@ -11727,7 +11784,7 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>275</v>
@@ -11742,7 +11799,7 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>275</v>
@@ -11752,18 +11809,12 @@
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
-        <v>1</v>
-      </c>
-      <c r="M48" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>275</v>
@@ -11778,7 +11829,7 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>275</v>
@@ -11788,18 +11839,12 @@
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
-        <v>1</v>
-      </c>
-      <c r="M50" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>275</v>
@@ -11814,7 +11859,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>275</v>
@@ -11824,19 +11869,7 @@
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
-        <v>2</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11851,12 +11884,18 @@
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>275</v>
@@ -11871,7 +11910,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>275</v>
@@ -11881,18 +11920,12 @@
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
-        <v>1</v>
-      </c>
-      <c r="M55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>275</v>
@@ -11904,14 +11937,11 @@
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
         <v>1</v>
       </c>
-      <c r="H56" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>302</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11941,7 +11971,13 @@
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11962,24 +11998,24 @@
         <v>1</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>218</v>
@@ -11995,19 +12031,19 @@
         <v>1</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>310</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12022,7 +12058,19 @@
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12037,7 +12085,13 @@
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12073,18 +12127,15 @@
         <v>1</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K64" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>282</v>
+        <v>316</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>275</v>
@@ -12094,18 +12145,21 @@
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
-        <v>1</v>
-      </c>
-      <c r="O65" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>246</v>
+        <v>2</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>275</v>
@@ -12115,12 +12169,24 @@
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>275</v>
@@ -12130,12 +12196,15 @@
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>275</v>
@@ -12150,7 +12219,7 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>275</v>
@@ -12160,15 +12229,12 @@
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
-        <v>1</v>
-      </c>
-      <c r="M69" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>275</v>
@@ -12178,24 +12244,12 @@
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
-        <v>2</v>
-      </c>
-      <c r="K70" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="O70" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="2" t="s">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>275</v>
@@ -12205,21 +12259,18 @@
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
-        <v>2</v>
-      </c>
-      <c r="K71" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="M71" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="O71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>275</v>
@@ -12235,10 +12286,13 @@
         <v>1</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="M72" s="1" t="n">
-        <v>1</v>
+        <v>242</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12268,13 +12322,7 @@
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
-        <v>1</v>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12289,45 +12337,39 @@
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
-        <v>2</v>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O75" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" s="2" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>228</v>
+        <v>329</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12336,13 +12378,13 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12351,13 +12393,13 @@
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12366,13 +12408,13 @@
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12381,23 +12423,17 @@
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>335</v>
+        <v>261</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
-        <v>1</v>
-      </c>
-      <c r="O81" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" s="2" t="s">
-        <v>220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12405,7 +12441,7 @@
         <v>336</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>337</v>
@@ -12420,22 +12456,28 @@
         <v>338</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>337</v>
@@ -12447,10 +12489,10 @@
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>238</v>
+        <v>341</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>337</v>
@@ -12462,10 +12504,10 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>337</v>
@@ -12477,31 +12519,25 @@
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
-        <v>1</v>
-      </c>
-      <c r="K87" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>337</v>
@@ -12519,10 +12555,10 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>337</v>
@@ -12540,25 +12576,31 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>337</v>
@@ -12570,10 +12612,10 @@
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>337</v>
@@ -12585,10 +12627,10 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>337</v>
@@ -12600,23 +12642,17 @@
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
-        <v>1</v>
-      </c>
-      <c r="I94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12624,7 +12660,7 @@
         <v>350</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>337</v>
@@ -12646,72 +12682,57 @@
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E96" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G96" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="K96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="O96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P96" s="1" t="s">
-        <v>355</v>
+        <v>235</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
-        <v>3</v>
-      </c>
-      <c r="G97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="M97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P97" s="2" t="s">
-        <v>358</v>
+        <v>1</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12720,13 +12741,13 @@
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
@@ -12741,13 +12762,13 @@
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
@@ -12756,226 +12777,211 @@
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
-        <v>1</v>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>236</v>
+        <v>3</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="M101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
-        <v>3</v>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="G102" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
-        <v>1</v>
-      </c>
-      <c r="G103" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
-        <v>1</v>
-      </c>
-      <c r="K104" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
-        <v>1</v>
-      </c>
-      <c r="K105" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
         <v>1</v>
       </c>
-      <c r="M106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" s="2" t="s">
-        <v>273</v>
+      <c r="K106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="B107" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>353</v>
+      <c r="C107" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D107" s="2" t="n">
         <f aca="false">SUM(E107,G107,I107,K107,M107,O107)</f>
-        <v>1</v>
-      </c>
-      <c r="M107" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N107" s="2" t="s">
-        <v>234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D108" s="2" t="n">
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>220</v>
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="M108" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>220</v>
+        <v>247</v>
+      </c>
+      <c r="O108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D109" s="2" t="n">
         <f aca="false">SUM(E109,G109,I109,K109,M109,O109)</f>
-        <v>2</v>
-      </c>
-      <c r="E109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="M109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N109" s="2" t="s">
-        <v>220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D110" s="2" t="n">
         <f aca="false">SUM(E110,G110,I110,K110,M110,O110)</f>
@@ -12985,39 +12991,33 @@
         <v>1</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>373</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B111" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>353</v>
+      <c r="C111" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D111" s="2" t="n">
         <f aca="false">SUM(E111,G111,I111,K111,M111,O111)</f>
-        <v>1</v>
-      </c>
-      <c r="K111" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
@@ -13027,84 +13027,72 @@
         <v>1</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>373</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
-        <v>3</v>
-      </c>
-      <c r="E113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="M113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N113" s="2" t="s">
-        <v>273</v>
+        <v>2</v>
+      </c>
+      <c r="K113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="O113" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P113" s="2" t="s">
-        <v>273</v>
+      <c r="P113" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="M114" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N114" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O114" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P114" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
+      </c>
+      <c r="K114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B115" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>353</v>
+      <c r="C115" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D115" s="2" t="n">
         <f aca="false">SUM(E115,G115,I115,K115,M115,O115)</f>
@@ -13113,13 +13101,13 @@
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D116" s="2" t="n">
         <f aca="false">SUM(E116,G116,I116,K116,M116,O116)</f>
@@ -13128,175 +13116,151 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B117" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>353</v>
+      <c r="C117" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D117" s="2" t="n">
         <f aca="false">SUM(E117,G117,I117,K117,M117,O117)</f>
-        <v>2</v>
-      </c>
-      <c r="E117" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K117" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D118" s="2" t="n">
         <f aca="false">SUM(E118,G118,I118,K118,M118,O118)</f>
-        <v>2</v>
-      </c>
-      <c r="K118" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O118" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P118" s="1" t="s">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
-        <v>1</v>
-      </c>
-      <c r="K119" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" s="2" t="s">
-        <v>226</v>
+        <v>3</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="M119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="O119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
-        <v>1</v>
-      </c>
-      <c r="K120" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="2" t="s">
-        <v>251</v>
+        <v>3</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="M120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="O120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
-        <v>0</v>
-      </c>
-      <c r="E122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" s="2" t="s">
-        <v>227</v>
+        <v>299</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
@@ -13306,33 +13270,45 @@
         <v>1</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>251</v>
+        <v>383</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="M124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="B125" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>388</v>
+      <c r="C125" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D125" s="2" t="n">
         <f aca="false">SUM(E125,G125,I125,K125,M125,O125)</f>
@@ -13341,13 +13317,13 @@
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="B126" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>388</v>
+      <c r="C126" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
@@ -13356,136 +13332,178 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="M127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
         <v>1</v>
       </c>
-      <c r="K128" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>395</v>
+      <c r="M128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D129" s="2" t="n">
         <f aca="false">SUM(E129,G129,I129,K129,M129,O129)</f>
-        <v>1</v>
-      </c>
-      <c r="G129" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="G133" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>401</v>
+        <v>265</v>
+      </c>
+      <c r="K133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
@@ -13494,13 +13512,13 @@
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
@@ -13509,13 +13527,13 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13524,13 +13542,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13539,13 +13557,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13554,13 +13572,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13569,28 +13587,34 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13599,13 +13623,13 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
@@ -13614,13 +13638,13 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13629,79 +13653,55 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
-        <v>0</v>
-      </c>
-      <c r="E144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="G144" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" s="2" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K145" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13710,13 +13710,13 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>251</v>
+        <v>416</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>417</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
@@ -13731,7 +13731,7 @@
         <v>417</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
@@ -13746,11 +13746,47 @@
         <v>417</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
         <v>0</v>
+      </c>
+      <c r="E149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13758,10 +13794,10 @@
         <v>420</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13770,13 +13806,13 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13785,55 +13821,43 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
-        <v>1</v>
-      </c>
-      <c r="O152" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P152" s="2" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
-        <v>1</v>
-      </c>
-      <c r="M153" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N153" s="2" t="s">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13842,13 +13866,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="C155" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13860,10 +13884,10 @@
         <v>427</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13872,13 +13896,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>428</v>
+        <v>243</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13887,13 +13911,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>275</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13908,7 +13932,7 @@
         <v>275</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13923,7 +13947,7 @@
         <v>275</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13938,7 +13962,7 @@
         <v>275</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13953,7 +13977,7 @@
         <v>275</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13968,11 +13992,17 @@
         <v>275</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13983,7 +14013,7 @@
         <v>275</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -13998,7 +14028,7 @@
         <v>275</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -14013,7 +14043,7 @@
         <v>275</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -14028,7 +14058,7 @@
         <v>275</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -14043,7 +14073,7 @@
         <v>275</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -14058,17 +14088,11 @@
         <v>275</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
-        <v>1</v>
-      </c>
-      <c r="K169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" s="2" t="s">
-        <v>223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14079,7 +14103,7 @@
         <v>275</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -14094,7 +14118,7 @@
         <v>275</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
@@ -14109,7 +14133,7 @@
         <v>275</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -14124,7 +14148,7 @@
         <v>275</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -14139,7 +14163,7 @@
         <v>275</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -14151,73 +14175,55 @@
         <v>446</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
-        <v>1</v>
-      </c>
-      <c r="O175" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P175" s="2" t="s">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>246</v>
+        <v>447</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
-        <v>1</v>
-      </c>
-      <c r="O176" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P176" s="2" t="s">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
-        <v>1</v>
-      </c>
-      <c r="O177" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P177" s="2" t="s">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14226,43 +14232,55 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O180" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14271,13 +14289,13 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14286,100 +14304,106 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>457</v>
+        <v>230</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O183" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P183" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O184" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P184" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O185" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P185" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
-        <v>1</v>
-      </c>
-      <c r="K186" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L186" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
-        <v>1</v>
-      </c>
-      <c r="K187" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L187" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
@@ -14388,13 +14412,13 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14403,13 +14427,13 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14418,34 +14442,28 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
-        <v>1</v>
-      </c>
-      <c r="K191" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L191" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14460,62 +14478,32 @@
         <v>352</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O193" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P193" s="2" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
         <v>0</v>
-      </c>
-      <c r="E194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P194" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14526,7 +14514,7 @@
         <v>352</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
@@ -14541,11 +14529,23 @@
         <v>352</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="M196" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O196" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P196" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14556,49 +14556,61 @@
         <v>352</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K197" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>373</v>
+        <v>473</v>
+      </c>
+      <c r="O197" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P197" s="2" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
-        <v>1</v>
-      </c>
-      <c r="K198" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L198" s="2" t="s">
-        <v>276</v>
+        <v>2</v>
+      </c>
+      <c r="E198" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G198" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
@@ -14607,13 +14619,13 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
@@ -14622,56 +14634,44 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
-        <v>2</v>
-      </c>
-      <c r="E201" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G201" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" s="2" t="s">
-        <v>247</v>
+        <v>1</v>
+      </c>
+      <c r="K201" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K202" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="O202" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P202" s="2" t="s">
-        <v>479</v>
+        <v>383</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14682,23 +14682,11 @@
         <v>352</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
-        <v>2</v>
-      </c>
-      <c r="M203" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N203" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="O203" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P203" s="2" t="s">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14709,7 +14697,7 @@
         <v>352</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
@@ -14718,38 +14706,68 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
         <v>0</v>
       </c>
+      <c r="E205" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G205" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I205" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K205" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M205" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O205" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
-        <v>1</v>
-      </c>
-      <c r="O206" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P206" s="2" t="s">
-        <v>483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14760,7 +14778,7 @@
         <v>352</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
@@ -14775,220 +14793,142 @@
         <v>352</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
         <v>1</v>
       </c>
-      <c r="O208" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P208" s="2" t="s">
-        <v>448</v>
+      <c r="K208" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
-        <v>3</v>
-      </c>
-      <c r="E209" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G209" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="K209" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L209" s="2" t="s">
-        <v>489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
-        <v>2</v>
-      </c>
-      <c r="G210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
-        <v>1</v>
-      </c>
-      <c r="K211" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L211" s="2" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K212" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L212" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O212" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P212" s="2" t="s">
-        <v>220</v>
+        <v>276</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
-        <v>4</v>
-      </c>
-      <c r="E213" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G213" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>498</v>
+        <v>1</v>
       </c>
       <c r="K213" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O213" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P213" s="2" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
-        <v>1</v>
-      </c>
-      <c r="K214" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L214" s="2" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
-        <v>2</v>
-      </c>
-      <c r="G215" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K215" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L215" s="2" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>51</v>
+        <v>493</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>494</v>
@@ -14997,367 +14937,322 @@
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
         <v>1</v>
       </c>
-      <c r="K216" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L216" s="2" t="s">
-        <v>395</v>
+      <c r="O216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P216" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>501</v>
+        <v>261</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>275</v>
+        <v>352</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
-        <v>1</v>
-      </c>
-      <c r="O217" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P217" s="2" t="s">
-        <v>226</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E217" s="1"/>
+      <c r="L217" s="2"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="K218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
         <v>0</v>
       </c>
+      <c r="H219" s="2"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
-        <v>1</v>
-      </c>
-      <c r="O220" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P220" s="2" t="s">
-        <v>220</v>
+        <v>3</v>
+      </c>
+      <c r="E220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>506</v>
+        <v>51</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
-        <v>1</v>
-      </c>
-      <c r="O222" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P222" s="1" t="s">
-        <v>226</v>
+        <v>2</v>
+      </c>
+      <c r="G222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
         <v>1</v>
       </c>
-      <c r="O223" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P223" s="1" t="s">
-        <v>220</v>
+      <c r="K223" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E224" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
+      </c>
+      <c r="G224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="K224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>414</v>
       </c>
       <c r="O224" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P224" s="1" t="s">
-        <v>226</v>
+      <c r="P224" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="O225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P225" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>271</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
-        <v>0</v>
-      </c>
-      <c r="E226" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G226" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I226" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="2" t="s">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M226" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N226" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O226" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P226" s="2" t="s">
-        <v>227</v>
+        <v>414</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>45</v>
+        <v>512</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
         <v>0</v>
       </c>
-      <c r="E227" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G227" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I227" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K227" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L227" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M227" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N227" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O227" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P227" s="2" t="s">
-        <v>227</v>
-      </c>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
-        <v>0</v>
-      </c>
-      <c r="E228" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G228" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H228" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I228" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K228" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L228" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M228" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N228" s="2" t="s">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="O228" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P228" s="2" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
-        <v>1</v>
-      </c>
-      <c r="O229" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P229" s="2" t="s">
-        <v>220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
@@ -15366,95 +15261,107 @@
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O231" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P231" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C232" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>519</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
-        <v>3</v>
-      </c>
-      <c r="E232" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G232" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="I232" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J232" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C233" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>519</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E233" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="O233" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P233" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C234" s="2" t="s">
+      <c r="B234" s="1" t="s">
         <v>519</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P234" s="1" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C235" s="2" t="s">
+      <c r="B235" s="1" t="s">
         <v>519</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P235" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15462,86 +15369,188 @@
         <v>525</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P236" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
         <v>0</v>
       </c>
+      <c r="E237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="M237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>527</v>
+        <v>45</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
         <v>0</v>
       </c>
+      <c r="E238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="M238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="7" t="s">
-        <v>528</v>
+        <v>483</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
         <v>0</v>
       </c>
+      <c r="E239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
-        <v>2</v>
-      </c>
-      <c r="E240" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G240" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15549,10 +15558,10 @@
         <v>530</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
@@ -15561,28 +15570,40 @@
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>406</v>
+        <v>531</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E242" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G242" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15591,13 +15612,13 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
@@ -15606,55 +15627,43 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>508</v>
+        <v>330</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
-        <v>1</v>
-      </c>
-      <c r="K245" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L245" s="2" t="s">
-        <v>535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>532</v>
+      <c r="B246" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
-        <v>1</v>
-      </c>
-      <c r="O246" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P246" s="1" t="s">
-        <v>537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
@@ -15663,13 +15672,13 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
@@ -15678,13 +15687,13 @@
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>532</v>
+        <v>411</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
@@ -15693,28 +15702,46 @@
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>532</v>
+        <v>539</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H250" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="I250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
@@ -15723,56 +15750,61 @@
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>508</v>
+        <v>330</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
-        <v>2</v>
-      </c>
-      <c r="E252" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="L252" s="2"/>
-      <c r="O252" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P252" s="1" t="s">
-        <v>544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>532</v>
+        <v>542</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15781,101 +15813,53 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>532</v>
+        <v>546</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
-        <v>2</v>
-      </c>
-      <c r="E255" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F255" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="K255" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L255" s="2" t="s">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
-        <v>1</v>
-      </c>
-      <c r="O256" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P256" s="1" t="s">
-        <v>537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
-        <v>0</v>
-      </c>
-      <c r="E257" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G257" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I257" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J257" s="2" t="s">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M257" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N257" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O257" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P257" s="2" t="s">
-        <v>227</v>
+        <v>549</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15883,10 +15867,10 @@
         <v>550</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
@@ -15897,32 +15881,26 @@
       <c r="A259" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>532</v>
+      <c r="B259" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
-        <v>1</v>
-      </c>
-      <c r="K259" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L259" s="2" t="s">
-        <v>552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
@@ -15931,13 +15909,13 @@
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
@@ -15946,17 +15924,23 @@
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>532</v>
+        <v>554</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" s="2" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15964,10 +15948,10 @@
         <v>556</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
@@ -15979,20 +15963,50 @@
         <v>557</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>535</v>
+        <v>247</v>
+      </c>
+      <c r="M264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16000,221 +16014,410 @@
         <v>558</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P265" s="1" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C266" s="1" t="s">
-        <v>532</v>
+        <v>560</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L266" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>532</v>
+        <v>561</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D267" s="2" t="n">
         <f aca="false">SUM(E267,G267,I267,K267,M267,O267)</f>
-        <v>3</v>
-      </c>
-      <c r="E267" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G267" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H267" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K267" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L267" s="2" t="s">
-        <v>561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>563</v>
+      <c r="B268" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D268" s="2" t="n">
         <f aca="false">SUM(E268,G268,I268,K268,M268,O268)</f>
         <v>0</v>
       </c>
-      <c r="E268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H268" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J268" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L268" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="M268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N268" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P268" s="2" t="s">
-        <v>227</v>
-      </c>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>352</v>
+        <v>519</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="D269" s="2" t="n">
         <f aca="false">SUM(E269,G269,I269,K269,M269,O269)</f>
-        <v>1</v>
-      </c>
-      <c r="K269" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L269" s="2" t="s">
-        <v>226</v>
+        <v>2</v>
+      </c>
+      <c r="E269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="L269" s="2"/>
+      <c r="O269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P269" s="1" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>563</v>
+      <c r="B270" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D270" s="2" t="n">
         <f aca="false">SUM(E270,G270,I270,K270,M270,O270)</f>
-        <v>1</v>
-      </c>
-      <c r="G270" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>563</v>
+      <c r="B271" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D271" s="2" t="n">
         <f aca="false">SUM(E271,G271,I271,K271,M271,O271)</f>
-        <v>1</v>
-      </c>
-      <c r="E271" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D272" s="2" t="n">
         <f aca="false">SUM(E272,G272,I272,K272,M272,O272)</f>
-        <v>1</v>
-      </c>
-      <c r="E272" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>563</v>
+        <v>568</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D273" s="2" t="n">
         <f aca="false">SUM(E273,G273,I273,K273,M273,O273)</f>
-        <v>1</v>
-      </c>
-      <c r="K273" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L273" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <f aca="false">SUM(E274,G274,I274,K274,M274,O274)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="7" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B275" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D275" s="2" t="n">
+        <f aca="false">SUM(E275,G275,I275,K275,M275,O275)</f>
+        <v>1</v>
+      </c>
+      <c r="O275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P275" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D276" s="2" t="n">
+        <f aca="false">SUM(E276,G276,I276,K276,M276,O276)</f>
+        <v>1</v>
+      </c>
+      <c r="K276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D277" s="2" t="n">
+        <f aca="false">SUM(E277,G277,I277,K277,M277,O277)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D278" s="2" t="n">
+        <f aca="false">SUM(E278,G278,I278,K278,M278,O278)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <f aca="false">SUM(E279,G279,I279,K279,M279,O279)</f>
+        <v>1</v>
+      </c>
+      <c r="K279" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L279" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D280" s="2" t="n">
+        <f aca="false">SUM(E280,G280,I280,K280,M280,O280)</f>
+        <v>1</v>
+      </c>
+      <c r="E280" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D281" s="2" t="n">
+        <f aca="false">SUM(E281,G281,I281,K281,M281,O281)</f>
+        <v>1</v>
+      </c>
+      <c r="E281" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D282" s="2" t="n">
+        <f aca="false">SUM(E282,G282,I282,K282,M282,O282)</f>
+        <v>1</v>
+      </c>
+      <c r="G282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D283" s="2" t="n">
+        <f aca="false">SUM(E283,G283,I283,K283,M283,O283)</f>
+        <v>1</v>
+      </c>
+      <c r="K283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L283" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D284" s="2" t="n">
+        <f aca="false">SUM(E284,G284,I284,K284,M284,O284)</f>
+        <v>0</v>
+      </c>
+      <c r="E284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Painting Record.xlsx
+++ b/Painting Record.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="596">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -635,6 +635,9 @@
     <t xml:space="preserve">Korhil Lionmane</t>
   </si>
   <si>
+    <t xml:space="preserve">The Visarch</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paint</t>
   </si>
   <si>
@@ -833,6 +836,591 @@
     <t xml:space="preserve">Leaves (up Yellow)</t>
   </si>
   <si>
+    <t xml:space="preserve">Afro Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color Punch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancient Honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Army Painter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed Paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basilisk Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warpaints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Chalice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carnelian Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doomfire Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elder Flower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figgy Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forbidden Fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexed Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasper Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraken Lavender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leopard Stone Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White lion skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mocca Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moldy Wine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulled Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White lion Fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raging Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarab Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiger’s Eye Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Topaz Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tourmaline Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weird Elixir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilted Rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyvern Fury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abaddon Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citadel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Averland Sunset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barak-Nar Burgundy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bugman's Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celestra Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corax White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daemonette Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gal Vorbak Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey Seer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incubi Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jokaero Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khorne Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macragge Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mephiston Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morghast Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mournfang Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenician Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rakarth Flesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhinox Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screamer Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel Legion Drab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thousand Sons blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wraithbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XV-88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zandri Dust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aethermatic Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aldeari Emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apothecary White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Templar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadow Tenebrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corvus Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cygor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather Shadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gore-Grunta Fur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryph-Charger Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryph-Hound Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iyanden Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nazdreg Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratling Grime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeleton Horde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snakebite Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volupus Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administratum Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baharroth Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balor Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Reaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dawnstone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorn Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperor's Children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Sunz Scarlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fenrisian Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Dragon Bright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash Gitz Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabalite Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakophoni Purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moot Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phalanx Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pink Horror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squig Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sybarite Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temple Guard Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thunderhawk Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trollslayer Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulthuan Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ushabti Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild Rider Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yriel Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrax Earthshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carroburg Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drakenhof Nightshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Druchii Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reikland Fleshshade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartacci Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danilo Cartacci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caucasian Skintone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiwi Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samurai Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alizarin Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp. Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobalt Bluegreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diarylide Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honey Moon Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mars Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Dark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Brown Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxide Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluidine Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultramarine Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Pisarski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fallen Grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron Hue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morning Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun Ray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalo Blue G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalo Blue R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalo Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Oxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titanium White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow Oxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquitex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muted Violed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hue Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naphthol Crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phthalocyanine Blue (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparent Raw Umber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivid Lime Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow Medium Azo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asphalt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nocturna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Scarlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiery Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umber</t>
+  </si>
+  <si>
     <t xml:space="preserve">Drab Brown</t>
   </si>
   <si>
@@ -842,238 +1430,91 @@
     <t xml:space="preserve">Adepticon</t>
   </si>
   <si>
-    <t xml:space="preserve">Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abaddon Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citadel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Averland Sunset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barak-Nar Burgundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bugman's Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celestra Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corax White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daemonette Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gal Vorbak Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey Seer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incubi Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jokaero Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khorne Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macragge Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mephiston Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morghast Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mournfang Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenician Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rakarth Flesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhinox Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screamer Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel Legion Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Fang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thousand Sons blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wraithbone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XV-88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zandri Dust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afro Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color Punch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whole Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aethermatic Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aldeari Emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apothecary White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black Templar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shadow Tenebrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corvus Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cygor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leather Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gore-Grunta Fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryph-Charger Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryph-Hound Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyanden Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nazdreg Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratling Grime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skeleton Horde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snakebite Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volupus Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartacci Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kimera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danilo Cartacci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caucasian Skintone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiwi Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samurai Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alizarin Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp. Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobalt Bluegreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diarylide Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honey Moon Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mars Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Brown Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxide Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toluidine Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultramarine Blue</t>
+    <t xml:space="preserve">Bright Yellow Ochre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flameon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metallic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Plum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gladewyrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair /  Leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogue Hobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Hot Pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gems Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultramarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bold Pyrrole Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bold Titanium White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMM / W. Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale 75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chesnut</t>
   </si>
   <si>
     <t xml:space="preserve">Bluegrey</t>
@@ -1103,12 +1544,6 @@
     <t xml:space="preserve">Under gold</t>
   </si>
   <si>
-    <t xml:space="preserve">Bright Yellow Ochre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flameon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Death White</t>
   </si>
   <si>
@@ -1121,12 +1556,15 @@
     <t xml:space="preserve">Scorpena Green</t>
   </si>
   <si>
+    <t xml:space="preserve">Angel Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Color</t>
+  </si>
+  <si>
     <t xml:space="preserve">Barbarian Skin</t>
   </si>
   <si>
-    <t xml:space="preserve">Game Color</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bile Green</t>
   </si>
   <si>
@@ -1220,207 +1658,12 @@
     <t xml:space="preserve">Yellow Ink</t>
   </si>
   <si>
-    <t xml:space="preserve">Carbon Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquitex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muted Violed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hue Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naphthol Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalocyanine Blue (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titanium White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transparent Raw Umber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vivid Lime Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow Medium Azo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asphalt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nocturna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown Beast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep Scarlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiery Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midnight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale 75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chesnut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administratum Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baharroth Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balor Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Reaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dawnstone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorn Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emperor's Children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evil Sunz Scarlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fenrisian Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Dragon Bright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flash Gitz Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabalite Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kakophoni Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moot Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phalanx Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pink Horror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squig Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sybarite Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temple Guard Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thunderhawk Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trollslayer Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ulthuan Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ushabti Bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wild Rider Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yriel Yellow</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metal Color</t>
   </si>
   <si>
-    <t xml:space="preserve">Armor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Silver</t>
   </si>
   <si>
-    <t xml:space="preserve">White Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metallic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Sky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Pisarski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fallen Grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iron Hue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morning Sky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun Ray</t>
-  </si>
-  <si>
     <t xml:space="preserve">Basalt Grey</t>
   </si>
   <si>
@@ -1472,9 +1715,6 @@
     <t xml:space="preserve">Ice Yellow</t>
   </si>
   <si>
-    <t xml:space="preserve">Ivory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Luftwafe Unif. WWII</t>
   </si>
   <si>
@@ -1511,256 +1751,55 @@
     <t xml:space="preserve">Model Color</t>
   </si>
   <si>
-    <t xml:space="preserve">Dark Plum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninjon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gladewyrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOVA Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOVA Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair /  Leather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rogue Hobby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Hot Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dark Turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gems Main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultramarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agrax Earthshade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carroburg Crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drakenhof Nightshade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Druchii Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reikland Fleshshade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancient Honey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Army Painter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Paint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goddess Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Shadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slaughter Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warrior Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bold Pyrrole Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bold Titanium White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMM / W. Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cold Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalo Blue G.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalo Blue R.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phthalo Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm Yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow Oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basilisk Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warpaints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood Chalice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carnelian Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doomfire Drab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elder Flower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Figgy Pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forbidden Fruit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexed Violet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasper Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kraken Lavender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leopard Stone Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White lion skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mocca Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moldy Wine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulled Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onyx Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White lion Fur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raging Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scarab Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiger’s Eye Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topaz Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tourmaline Skin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weird Elixir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilted Rose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wyvern Fury</t>
+    <t xml:space="preserve">Armor Green</t>
   </si>
   <si>
     <t xml:space="preserve">Xpress</t>
   </si>
   <si>
+    <t xml:space="preserve">Black Lotus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardinal Purple</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skin / Leaves / Gems</t>
   </si>
   <si>
+    <t xml:space="preserve">Dreadnought Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forest Green</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitallier Black</t>
   </si>
   <si>
     <t xml:space="preserve">Tenebrous</t>
   </si>
   <si>
+    <t xml:space="preserve">Legacy Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monastic Green</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mummy White</t>
   </si>
   <si>
     <t xml:space="preserve">Hue Bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mystic Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orc Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seraph Red</t>
   </si>
   <si>
     <t xml:space="preserve">Twilight Rose</t>
@@ -3416,11 +3455,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="63062853"/>
-        <c:axId val="4075633"/>
+        <c:axId val="79038778"/>
+        <c:axId val="55995403"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="63062853"/>
+        <c:axId val="79038778"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3452,7 +3491,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4075633"/>
+        <c:crossAx val="55995403"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3460,7 +3499,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4075633"/>
+        <c:axId val="55995403"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3499,7 +3538,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63062853"/>
+        <c:crossAx val="79038778"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3540,9 +3579,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>617400</xdr:colOff>
+      <xdr:colOff>617040</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>71280</xdr:rowOff>
+      <xdr:rowOff>70920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3551,7 +3590,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7968600" y="6922800"/>
-        <a:ext cx="7506000" cy="3174480"/>
+        <a:ext cx="7505640" cy="3174120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3606,8 +3645,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:P284" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:P284"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:P296" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:P296"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Paint"/>
     <tableColumn id="2" name="Brand"/>
@@ -3884,7 +3923,7 @@
       </c>
       <c r="H2" s="2" t="n">
         <f aca="false">SUM(C2:C1039)</f>
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -4089,7 +4128,7 @@
       </c>
       <c r="H10" s="2" t="str">
         <f aca="false" t="array" ref="H10:H10">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 3), ROW(Paints!D:D), ""), 3)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 4), Paints!D:D, 0)))</f>
-        <v>Warm Grey</v>
+        <v>Dark Turquoise</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>33</v>
@@ -4116,7 +4155,7 @@
       </c>
       <c r="H11" s="2" t="str">
         <f aca="false" t="array" ref="H11:H11">IFERROR(INDEX(Paints!A:A, SMALL(IF(Paints!D:D=LARGE(Paints!D:D, 4), ROW(Paints!D:D), ""), 4)), INDEX(Paints!A:A, MATCH(LARGE(Paints!D:D, 5), Paints!D:D, 0)))</f>
-        <v>Dark Turquoise</v>
+        <v>Warm Grey</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>35</v>
@@ -7570,11 +7609,25 @@
       </c>
       <c r="B200" s="2"/>
     </row>
-    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="B201" s="2"/>
+      <c r="B201" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="n">
@@ -7583,30 +7636,57 @@
       <c r="B202" s="2"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="3" t="n">
+        <v>46143</v>
+      </c>
       <c r="B203" s="2"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="3" t="n">
+        <v>46174</v>
+      </c>
       <c r="B204" s="2"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="3" t="n">
+        <v>46204</v>
+      </c>
       <c r="B205" s="2"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="3" t="n">
+        <v>46235</v>
+      </c>
       <c r="B206" s="2"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="3" t="n">
+        <v>46266</v>
+      </c>
       <c r="B207" s="2"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="3" t="n">
+        <v>46296</v>
+      </c>
       <c r="B208" s="2"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="B209" s="2"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="3" t="n">
+        <v>46357</v>
+      </c>
       <c r="B210" s="2"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="3" t="n">
+        <v>46388</v>
+      </c>
       <c r="B211" s="2"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10645,7 +10725,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P284"/>
+  <dimension ref="A1:P296"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="19.87"/>
@@ -10666,63 +10746,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>179</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D2" s="2" t="n">
         <f aca="false">SUM(E2,G2,I2,K2,M2,O2)</f>
@@ -10732,30 +10812,30 @@
         <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(E3,G3,I3,K3,M3,O3)</f>
@@ -10765,24 +10845,24 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D4" s="2" t="n">
         <f aca="false">SUM(E4,G4,I4,K4,M4,O4)</f>
@@ -10792,36 +10872,36 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">SUM(E5,G5,I5,K5,M5,O5)</f>
@@ -10831,24 +10911,24 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">SUM(E6,G6,I6,K6,M6,O6)</f>
@@ -10857,13 +10937,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">SUM(E7,G7,I7,K7,M7,O7)</f>
@@ -10872,13 +10952,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="n">
         <f aca="false">SUM(E8,G8,I8,K8,M8,O8)</f>
@@ -10888,18 +10968,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">SUM(E9,G9,I9,K9,M9,O9)</f>
@@ -10909,18 +10989,18 @@
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(E10,G10,I10,K10,M10,O10)</f>
@@ -10930,18 +11010,18 @@
         <v>1</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">SUM(E11,G11,I11,K11,M11,O11)</f>
@@ -10951,18 +11031,18 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D12" s="2" t="n">
         <f aca="false">SUM(E12,G12,I12,K12,M12,O12)</f>
@@ -10972,36 +11052,36 @@
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUM(E13,G13,I13,K13,M13,O13)</f>
@@ -11010,13 +11090,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D14" s="2" t="n">
         <f aca="false">SUM(E14,G14,I14,K14,M14,O14)</f>
@@ -11026,19 +11106,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11046,10 +11126,10 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D15" s="2" t="n">
         <f aca="false">SUM(E15,G15,I15,K15,M15,O15)</f>
@@ -11059,37 +11139,37 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11097,10 +11177,10 @@
         <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D16" s="2" t="n">
         <f aca="false">SUM(E16,G16,I16,K16,M16,O16)</f>
@@ -11110,48 +11190,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D17" s="2" t="n">
         <f aca="false">SUM(E17,G17,I17,K17,M17,O17)</f>
@@ -11161,24 +11241,24 @@
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D18" s="2" t="n">
         <f aca="false">SUM(E18,G18,I18,K18,M18,O18)</f>
@@ -11188,24 +11268,24 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D19" s="2" t="n">
         <f aca="false">SUM(E19,G19,I19,K19,M19,O19)</f>
@@ -11214,13 +11294,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D20" s="2" t="n">
         <f aca="false">SUM(E20,G20,I20,K20,M20,O20)</f>
@@ -11230,18 +11310,18 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D21" s="2" t="n">
         <f aca="false">SUM(E21,G21,I21,K21,M21,O21)</f>
@@ -11250,13 +11330,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D22" s="2" t="n">
         <f aca="false">SUM(E22,G22,I22,K22,M22,O22)</f>
@@ -11265,13 +11345,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23" s="2" t="n">
         <f aca="false">SUM(E23,G23,I23,K23,M23,O23)</f>
@@ -11280,13 +11360,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D24" s="2" t="n">
         <f aca="false">SUM(E24,G24,I24,K24,M24,O24)</f>
@@ -11296,24 +11376,24 @@
         <v>1</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D25" s="2" t="n">
         <f aca="false">SUM(E25,G25,I25,K25,M25,O25)</f>
@@ -11323,18 +11403,18 @@
         <v>1</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D26" s="2" t="n">
         <f aca="false">SUM(E26,G26,I26,K26,M26,O26)</f>
@@ -11344,18 +11424,18 @@
         <v>1</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D27" s="2" t="n">
         <f aca="false">SUM(E27,G27,I27,K27,M27,O27)</f>
@@ -11365,13 +11445,13 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11379,10 +11459,10 @@
         <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D28" s="2" t="n">
         <f aca="false">SUM(E28,G28,I28,K28,M28,O28)</f>
@@ -11392,48 +11472,48 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D29" s="2" t="n">
         <f aca="false">SUM(E29,G29,I29,K29,M29,O29)</f>
@@ -11443,24 +11523,24 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D30" s="2" t="n">
         <f aca="false">SUM(E30,G30,I30,K30,M30,O30)</f>
@@ -11470,18 +11550,18 @@
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D31" s="2" t="n">
         <f aca="false">SUM(E31,G31,I31,K31,M31,O31)</f>
@@ -11491,72 +11571,96 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>271</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>272</v>
       </c>
       <c r="D32" s="2" t="n">
         <f aca="false">SUM(E32,G32,I32,K32,M32,O32)</f>
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>275</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D33" s="2" t="n">
         <f aca="false">SUM(E33,G33,I33,K33,M33,O33)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>276</v>
+      <c r="B34" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="D34" s="2" t="n">
         <f aca="false">SUM(E34,G34,I34,K34,M34,O34)</f>
@@ -11565,115 +11669,130 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>276</v>
+      <c r="C35" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="D35" s="2" t="n">
         <f aca="false">SUM(E35,G35,I35,K35,M35,O35)</f>
-        <v>1</v>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>279</v>
+      <c r="P35" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="D36" s="2" t="n">
         <f aca="false">SUM(E36,G36,I36,K36,M36,O36)</f>
         <v>1</v>
       </c>
-      <c r="M36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>250</v>
+      <c r="O36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="D37" s="2" t="n">
         <f aca="false">SUM(E37,G37,I37,K37,M37,O37)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D38" s="2" t="n">
         <f aca="false">SUM(E38,G38,I38,K38,M38,O38)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D39" s="2" t="n">
         <f aca="false">SUM(E39,G39,I39,K39,M39,O39)</f>
-        <v>2</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="D40" s="2" t="n">
         <f aca="false">SUM(E40,G40,I40,K40,M40,O40)</f>
@@ -11682,70 +11801,64 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>276</v>
+        <v>289</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D41" s="2" t="n">
         <f aca="false">SUM(E41,G41,I41,K41,M41,O41)</f>
-        <v>1</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D42" s="2" t="n">
         <f aca="false">SUM(E42,G42,I42,K42,M42,O42)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>276</v>
+        <v>292</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D43" s="2" t="n">
         <f aca="false">SUM(E43,G43,I43,K43,M43,O43)</f>
-        <v>1</v>
-      </c>
-      <c r="M43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D44" s="2" t="n">
         <f aca="false">SUM(E44,G44,I44,K44,M44,O44)</f>
@@ -11754,13 +11867,13 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D45" s="2" t="n">
         <f aca="false">SUM(E45,G45,I45,K45,M45,O45)</f>
@@ -11769,13 +11882,13 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>276</v>
+        <v>295</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D46" s="2" t="n">
         <f aca="false">SUM(E46,G46,I46,K46,M46,O46)</f>
@@ -11784,28 +11897,34 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D47" s="2" t="n">
         <f aca="false">SUM(E47,G47,I47,K47,M47,O47)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>276</v>
+        <v>298</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D48" s="2" t="n">
         <f aca="false">SUM(E48,G48,I48,K48,M48,O48)</f>
@@ -11814,58 +11933,112 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D49" s="2" t="n">
         <f aca="false">SUM(E49,G49,I49,K49,M49,O49)</f>
         <v>0</v>
       </c>
+      <c r="E49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>276</v>
+        <v>300</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D50" s="2" t="n">
         <f aca="false">SUM(E50,G50,I50,K50,M50,O50)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D51" s="2" t="n">
         <f aca="false">SUM(E51,G51,I51,K51,M51,O51)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>276</v>
+        <v>304</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D52" s="2" t="n">
         <f aca="false">SUM(E52,G52,I52,K52,M52,O52)</f>
@@ -11874,49 +12047,56 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>276</v>
+        <v>305</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D53" s="2" t="n">
         <f aca="false">SUM(E53,G53,I53,K53,M53,O53)</f>
-        <v>1</v>
-      </c>
-      <c r="K53" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D54" s="2" t="n">
         <f aca="false">SUM(E54,G54,I54,K54,M54,O54)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="L54" s="2"/>
+      <c r="O54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>276</v>
+        <v>308</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D55" s="2" t="n">
         <f aca="false">SUM(E55,G55,I55,K55,M55,O55)</f>
@@ -11925,34 +12105,28 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>276</v>
+        <v>309</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D56" s="2" t="n">
         <f aca="false">SUM(E56,G56,I56,K56,M56,O56)</f>
-        <v>1</v>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>276</v>
+        <v>310</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D57" s="2" t="n">
         <f aca="false">SUM(E57,G57,I57,K57,M57,O57)</f>
@@ -11961,148 +12135,100 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>276</v>
+        <v>311</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D58" s="2" t="n">
         <f aca="false">SUM(E58,G58,I58,K58,M58,O58)</f>
-        <v>1</v>
-      </c>
-      <c r="O58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D59" s="2" t="n">
         <f aca="false">SUM(E59,G59,I59,K59,M59,O59)</f>
-        <v>3</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D60" s="2" t="n">
         <f aca="false">SUM(E60,G60,I60,K60,M60,O60)</f>
-        <v>3</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="K60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>224</v>
+        <v>1</v>
+      </c>
+      <c r="O60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="D61" s="2" t="n">
         <f aca="false">SUM(E61,G61,I61,K61,M61,O61)</f>
-        <v>2</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>222</v>
+        <v>1</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D62" s="2" t="n">
         <f aca="false">SUM(E62,G62,I62,K62,M62,O62)</f>
-        <v>1</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D63" s="2" t="n">
         <f aca="false">SUM(E63,G63,I63,K63,M63,O63)</f>
@@ -12111,88 +12237,67 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D64" s="2" t="n">
         <f aca="false">SUM(E64,G64,I64,K64,M64,O64)</f>
-        <v>2</v>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="M64" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D65" s="2" t="n">
         <f aca="false">SUM(E65,G65,I65,K65,M65,O65)</f>
-        <v>2</v>
-      </c>
-      <c r="K65" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="M65" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="C66" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D66" s="2" t="n">
         <f aca="false">SUM(E66,G66,I66,K66,M66,O66)</f>
-        <v>2</v>
-      </c>
-      <c r="K66" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>319</v>
+        <v>1</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D67" s="2" t="n">
         <f aca="false">SUM(E67,G67,I67,K67,M67,O67)</f>
@@ -12201,16 +12306,19 @@
       <c r="M67" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="N67" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D68" s="2" t="n">
         <f aca="false">SUM(E68,G68,I68,K68,M68,O68)</f>
@@ -12219,13 +12327,13 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D69" s="2" t="n">
         <f aca="false">SUM(E69,G69,I69,K69,M69,O69)</f>
@@ -12234,76 +12342,76 @@
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D70" s="2" t="n">
         <f aca="false">SUM(E70,G70,I70,K70,M70,O70)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D71" s="2" t="n">
         <f aca="false">SUM(E71,G71,I71,K71,M71,O71)</f>
-        <v>1</v>
-      </c>
-      <c r="O71" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" s="2" t="s">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D72" s="2" t="n">
         <f aca="false">SUM(E72,G72,I72,K72,M72,O72)</f>
-        <v>2</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K72" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>299</v>
+        <v>1</v>
+      </c>
+      <c r="M72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D73" s="2" t="n">
         <f aca="false">SUM(E73,G73,I73,K73,M73,O73)</f>
@@ -12312,28 +12420,34 @@
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D74" s="2" t="n">
         <f aca="false">SUM(E74,G74,I74,K74,M74,O74)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D75" s="2" t="n">
         <f aca="false">SUM(E75,G75,I75,K75,M75,O75)</f>
@@ -12342,34 +12456,28 @@
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D76" s="2" t="n">
         <f aca="false">SUM(E76,G76,I76,K76,M76,O76)</f>
-        <v>1</v>
-      </c>
-      <c r="O76" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" s="2" t="s">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D77" s="2" t="n">
         <f aca="false">SUM(E77,G77,I77,K77,M77,O77)</f>
@@ -12378,13 +12486,13 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D78" s="2" t="n">
         <f aca="false">SUM(E78,G78,I78,K78,M78,O78)</f>
@@ -12393,13 +12501,13 @@
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D79" s="2" t="n">
         <f aca="false">SUM(E79,G79,I79,K79,M79,O79)</f>
@@ -12408,13 +12516,13 @@
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D80" s="2" t="n">
         <f aca="false">SUM(E80,G80,I80,K80,M80,O80)</f>
@@ -12423,13 +12531,13 @@
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>261</v>
+        <v>338</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D81" s="2" t="n">
         <f aca="false">SUM(E81,G81,I81,K81,M81,O81)</f>
@@ -12438,13 +12546,13 @@
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D82" s="2" t="n">
         <f aca="false">SUM(E82,G82,I82,K82,M82,O82)</f>
@@ -12453,49 +12561,49 @@
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D83" s="2" t="n">
         <f aca="false">SUM(E83,G83,I83,K83,M83,O83)</f>
-        <v>1</v>
-      </c>
-      <c r="I83" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D84" s="2" t="n">
         <f aca="false">SUM(E84,G84,I84,K84,M84,O84)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D85" s="2" t="n">
         <f aca="false">SUM(E85,G85,I85,K85,M85,O85)</f>
@@ -12504,13 +12612,13 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D86" s="2" t="n">
         <f aca="false">SUM(E86,G86,I86,K86,M86,O86)</f>
@@ -12519,106 +12627,118 @@
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D87" s="2" t="n">
         <f aca="false">SUM(E87,G87,I87,K87,M87,O87)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D88" s="2" t="n">
         <f aca="false">SUM(E88,G88,I88,K88,M88,O88)</f>
-        <v>1</v>
-      </c>
-      <c r="K88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D89" s="2" t="n">
         <f aca="false">SUM(E89,G89,I89,K89,M89,O89)</f>
         <v>1</v>
       </c>
-      <c r="K89" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>276</v>
+      <c r="O89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D90" s="2" t="n">
         <f aca="false">SUM(E90,G90,I90,K90,M90,O90)</f>
-        <v>1</v>
-      </c>
-      <c r="K90" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>276</v>
+        <v>2</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="O90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D91" s="2" t="n">
         <f aca="false">SUM(E91,G91,I91,K91,M91,O91)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D92" s="2" t="n">
         <f aca="false">SUM(E92,G92,I92,K92,M92,O92)</f>
@@ -12627,112 +12747,121 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="D93" s="2" t="n">
         <f aca="false">SUM(E93,G93,I93,K93,M93,O93)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="M93" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D94" s="2" t="n">
         <f aca="false">SUM(E94,G94,I94,K94,M94,O94)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D95" s="2" t="n">
         <f aca="false">SUM(E95,G95,I95,K95,M95,O95)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D96" s="2" t="n">
         <f aca="false">SUM(E96,G96,I96,K96,M96,O96)</f>
-        <v>3</v>
-      </c>
-      <c r="E96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I96" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>235</v>
+        <v>1</v>
+      </c>
+      <c r="M96" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D97" s="2" t="n">
         <f aca="false">SUM(E97,G97,I97,K97,M97,O97)</f>
-        <v>1</v>
-      </c>
-      <c r="E97" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D98" s="2" t="n">
         <f aca="false">SUM(E98,G98,I98,K98,M98,O98)</f>
@@ -12741,100 +12870,91 @@
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D99" s="2" t="n">
         <f aca="false">SUM(E99,G99,I99,K99,M99,O99)</f>
-        <v>1</v>
-      </c>
-      <c r="K99" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D100" s="2" t="n">
         <f aca="false">SUM(E100,G100,I100,K100,M100,O100)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D101" s="2" t="n">
         <f aca="false">SUM(E101,G101,I101,K101,M101,O101)</f>
-        <v>3</v>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="M101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P101" s="2" t="s">
-        <v>359</v>
+        <v>2</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="D102" s="2" t="n">
         <f aca="false">SUM(E102,G102,I102,K102,M102,O102)</f>
-        <v>1</v>
-      </c>
-      <c r="G102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D103" s="2" t="n">
         <f aca="false">SUM(E103,G103,I103,K103,M103,O103)</f>
@@ -12843,13 +12963,13 @@
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D104" s="2" t="n">
         <f aca="false">SUM(E104,G104,I104,K104,M104,O104)</f>
@@ -12858,13 +12978,13 @@
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D105" s="2" t="n">
         <f aca="false">SUM(E105,G105,I105,K105,M105,O105)</f>
@@ -12873,33 +12993,27 @@
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D106" s="2" t="n">
         <f aca="false">SUM(E106,G106,I106,K106,M106,O106)</f>
-        <v>1</v>
-      </c>
-      <c r="K106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C107" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D107" s="2" t="n">
@@ -12909,10 +13023,10 @@
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>367</v>
@@ -12921,49 +13035,13 @@
         <f aca="false">SUM(E108,G108,I108,K108,M108,O108)</f>
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="2" t="s">
-        <v>247</v>
-      </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>367</v>
@@ -12975,10 +13053,10 @@
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>367</v>
@@ -12991,17 +13069,17 @@
         <v>1</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C111" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D111" s="2" t="n">
@@ -13011,87 +13089,57 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D112" s="2" t="n">
         <f aca="false">SUM(E112,G112,I112,K112,M112,O112)</f>
-        <v>1</v>
-      </c>
-      <c r="K112" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="2" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D113" s="2" t="n">
         <f aca="false">SUM(E113,G113,I113,K113,M113,O113)</f>
-        <v>2</v>
-      </c>
-      <c r="K113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P113" s="1" t="s">
-        <v>244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D114" s="2" t="n">
         <f aca="false">SUM(E114,G114,I114,K114,M114,O114)</f>
-        <v>2</v>
-      </c>
-      <c r="E114" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K114" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" s="2" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C115" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D115" s="2" t="n">
@@ -13101,10 +13149,10 @@
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>367</v>
@@ -13116,12 +13164,12 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C117" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D117" s="2" t="n">
@@ -13131,10 +13179,10 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>367</v>
@@ -13146,89 +13194,47 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D119" s="2" t="n">
         <f aca="false">SUM(E119,G119,I119,K119,M119,O119)</f>
-        <v>3</v>
-      </c>
-      <c r="E119" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="M119" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N119" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O119" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P119" s="2" t="s">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D120" s="2" t="n">
         <f aca="false">SUM(E120,G120,I120,K120,M120,O120)</f>
-        <v>3</v>
-      </c>
-      <c r="E120" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="M120" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N120" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O120" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" s="2" t="s">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D121" s="2" t="n">
         <f aca="false">SUM(E121,G121,I121,K121,M121,O121)</f>
-        <v>1</v>
-      </c>
-      <c r="K121" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="2" t="s">
-        <v>383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13236,20 +13242,14 @@
         <v>384</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D122" s="2" t="n">
         <f aca="false">SUM(E122,G122,I122,K122,M122,O122)</f>
-        <v>1</v>
-      </c>
-      <c r="K122" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13257,20 +13257,14 @@
         <v>385</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D123" s="2" t="n">
         <f aca="false">SUM(E123,G123,I123,K123,M123,O123)</f>
-        <v>1</v>
-      </c>
-      <c r="K123" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13278,36 +13272,24 @@
         <v>386</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D124" s="2" t="n">
         <f aca="false">SUM(E124,G124,I124,K124,M124,O124)</f>
-        <v>2</v>
-      </c>
-      <c r="E124" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="M124" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N124" s="2" t="s">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C125" s="1" t="s">
+      <c r="B125" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D125" s="2" t="n">
@@ -13319,15 +13301,21 @@
       <c r="A126" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C126" s="1" t="s">
+      <c r="B126" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D126" s="2" t="n">
         <f aca="false">SUM(E126,G126,I126,K126,M126,O126)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M126" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13335,26 +13323,20 @@
         <v>389</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D127" s="2" t="n">
         <f aca="false">SUM(E127,G127,I127,K127,M127,O127)</f>
-        <v>2</v>
-      </c>
-      <c r="E127" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="M127" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N127" s="2" t="s">
-        <v>268</v>
+        <v>1</v>
+      </c>
+      <c r="O127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13362,30 +13344,24 @@
         <v>390</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D128" s="2" t="n">
         <f aca="false">SUM(E128,G128,I128,K128,M128,O128)</f>
-        <v>1</v>
-      </c>
-      <c r="M128" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N128" s="2" t="s">
-        <v>238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C129" s="1" t="s">
+      <c r="B129" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D129" s="2" t="n">
@@ -13398,142 +13374,118 @@
         <v>392</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D130" s="2" t="n">
         <f aca="false">SUM(E130,G130,I130,K130,M130,O130)</f>
-        <v>1</v>
-      </c>
-      <c r="M130" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N130" s="2" t="s">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="D131" s="2" t="n">
         <f aca="false">SUM(E131,G131,I131,K131,M131,O131)</f>
         <v>1</v>
       </c>
-      <c r="K131" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="2" t="s">
-        <v>227</v>
+      <c r="O131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D132" s="2" t="n">
         <f aca="false">SUM(E132,G132,I132,K132,M132,O132)</f>
-        <v>1</v>
-      </c>
-      <c r="K132" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D133" s="2" t="n">
         <f aca="false">SUM(E133,G133,I133,K133,M133,O133)</f>
-        <v>4</v>
-      </c>
-      <c r="E133" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G133" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K133" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="O133" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P133" s="1" t="s">
-        <v>397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>367</v>
+        <v>397</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="D134" s="2" t="n">
         <f aca="false">SUM(E134,G134,I134,K134,M134,O134)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="D135" s="2" t="n">
         <f aca="false">SUM(E135,G135,I135,K135,M135,O135)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D136" s="2" t="n">
         <f aca="false">SUM(E136,G136,I136,K136,M136,O136)</f>
@@ -13542,13 +13494,13 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D137" s="2" t="n">
         <f aca="false">SUM(E137,G137,I137,K137,M137,O137)</f>
@@ -13557,13 +13509,13 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B138" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D138" s="2" t="n">
         <f aca="false">SUM(E138,G138,I138,K138,M138,O138)</f>
@@ -13572,13 +13524,13 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D139" s="2" t="n">
         <f aca="false">SUM(E139,G139,I139,K139,M139,O139)</f>
@@ -13587,34 +13539,28 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>407</v>
+        <v>262</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D140" s="2" t="n">
         <f aca="false">SUM(E140,G140,I140,K140,M140,O140)</f>
-        <v>1</v>
-      </c>
-      <c r="G140" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D141" s="2" t="n">
         <f aca="false">SUM(E141,G141,I141,K141,M141,O141)</f>
@@ -13623,28 +13569,34 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D142" s="2" t="n">
         <f aca="false">SUM(E142,G142,I142,K142,M142,O142)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I142" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D143" s="2" t="n">
         <f aca="false">SUM(E143,G143,I143,K143,M143,O143)</f>
@@ -13653,55 +13605,43 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D144" s="2" t="n">
         <f aca="false">SUM(E144,G144,I144,K144,M144,O144)</f>
-        <v>1</v>
-      </c>
-      <c r="G144" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D145" s="2" t="n">
         <f aca="false">SUM(E145,G145,I145,K145,M145,O145)</f>
-        <v>1</v>
-      </c>
-      <c r="K145" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="2" t="s">
-        <v>414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D146" s="2" t="n">
         <f aca="false">SUM(E146,G146,I146,K146,M146,O146)</f>
@@ -13710,94 +13650,76 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D147" s="2" t="n">
         <f aca="false">SUM(E147,G147,I147,K147,M147,O147)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K147" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D148" s="2" t="n">
         <f aca="false">SUM(E148,G148,I148,K148,M148,O148)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K148" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D149" s="2" t="n">
         <f aca="false">SUM(E149,G149,I149,K149,M149,O149)</f>
-        <v>0</v>
-      </c>
-      <c r="E149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="2" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" s="2" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D150" s="2" t="n">
         <f aca="false">SUM(E150,G150,I150,K150,M150,O150)</f>
@@ -13806,13 +13728,13 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>421</v>
+        <v>256</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D151" s="2" t="n">
         <f aca="false">SUM(E151,G151,I151,K151,M151,O151)</f>
@@ -13821,13 +13743,13 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="7" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D152" s="2" t="n">
         <f aca="false">SUM(E152,G152,I152,K152,M152,O152)</f>
@@ -13836,13 +13758,13 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D153" s="2" t="n">
         <f aca="false">SUM(E153,G153,I153,K153,M153,O153)</f>
@@ -13851,13 +13773,13 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D154" s="2" t="n">
         <f aca="false">SUM(E154,G154,I154,K154,M154,O154)</f>
@@ -13866,13 +13788,13 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="D155" s="2" t="n">
         <f aca="false">SUM(E155,G155,I155,K155,M155,O155)</f>
@@ -13881,13 +13803,13 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="D156" s="2" t="n">
         <f aca="false">SUM(E156,G156,I156,K156,M156,O156)</f>
@@ -13896,13 +13818,13 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>243</v>
+        <v>423</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="D157" s="2" t="n">
         <f aca="false">SUM(E157,G157,I157,K157,M157,O157)</f>
@@ -13911,13 +13833,13 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="D158" s="2" t="n">
         <f aca="false">SUM(E158,G158,I158,K158,M158,O158)</f>
@@ -13926,13 +13848,13 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="D159" s="2" t="n">
         <f aca="false">SUM(E159,G159,I159,K159,M159,O159)</f>
@@ -13941,13 +13863,13 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="7" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="D160" s="2" t="n">
         <f aca="false">SUM(E160,G160,I160,K160,M160,O160)</f>
@@ -13956,13 +13878,13 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D161" s="2" t="n">
         <f aca="false">SUM(E161,G161,I161,K161,M161,O161)</f>
@@ -13971,13 +13893,13 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D162" s="2" t="n">
         <f aca="false">SUM(E162,G162,I162,K162,M162,O162)</f>
@@ -13986,34 +13908,40 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D163" s="2" t="n">
         <f aca="false">SUM(E163,G163,I163,K163,M163,O163)</f>
-        <v>1</v>
-      </c>
-      <c r="K163" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" s="2" t="s">
-        <v>253</v>
+        <v>2</v>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D164" s="2" t="n">
         <f aca="false">SUM(E164,G164,I164,K164,M164,O164)</f>
@@ -14022,13 +13950,13 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D165" s="2" t="n">
         <f aca="false">SUM(E165,G165,I165,K165,M165,O165)</f>
@@ -14037,13 +13965,13 @@
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D166" s="2" t="n">
         <f aca="false">SUM(E166,G166,I166,K166,M166,O166)</f>
@@ -14052,13 +13980,13 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D167" s="2" t="n">
         <f aca="false">SUM(E167,G167,I167,K167,M167,O167)</f>
@@ -14067,13 +13995,13 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D168" s="2" t="n">
         <f aca="false">SUM(E168,G168,I168,K168,M168,O168)</f>
@@ -14082,13 +14010,13 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D169" s="2" t="n">
         <f aca="false">SUM(E169,G169,I169,K169,M169,O169)</f>
@@ -14097,13 +14025,13 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D170" s="2" t="n">
         <f aca="false">SUM(E170,G170,I170,K170,M170,O170)</f>
@@ -14112,28 +14040,46 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D171" s="2" t="n">
         <f aca="false">SUM(E171,G171,I171,K171,M171,O171)</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="I171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D172" s="2" t="n">
         <f aca="false">SUM(E172,G172,I172,K172,M172,O172)</f>
@@ -14142,13 +14088,13 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>275</v>
+        <v>399</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D173" s="2" t="n">
         <f aca="false">SUM(E173,G173,I173,K173,M173,O173)</f>
@@ -14157,13 +14103,13 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D174" s="2" t="n">
         <f aca="false">SUM(E174,G174,I174,K174,M174,O174)</f>
@@ -14172,13 +14118,13 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D175" s="2" t="n">
         <f aca="false">SUM(E175,G175,I175,K175,M175,O175)</f>
@@ -14187,13 +14133,13 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D176" s="2" t="n">
         <f aca="false">SUM(E176,G176,I176,K176,M176,O176)</f>
@@ -14202,13 +14148,13 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D177" s="2" t="n">
         <f aca="false">SUM(E177,G177,I177,K177,M177,O177)</f>
@@ -14217,13 +14163,13 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D178" s="2" t="n">
         <f aca="false">SUM(E178,G178,I178,K178,M178,O178)</f>
@@ -14232,23 +14178,23 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D179" s="2" t="n">
         <f aca="false">SUM(E179,G179,I179,K179,M179,O179)</f>
         <v>1</v>
       </c>
-      <c r="M179" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N179" s="2" t="s">
-        <v>258</v>
+      <c r="G179" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14256,20 +14202,14 @@
         <v>451</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D180" s="2" t="n">
         <f aca="false">SUM(E180,G180,I180,K180,M180,O180)</f>
-        <v>1</v>
-      </c>
-      <c r="O180" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P180" s="2" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14277,10 +14217,10 @@
         <v>452</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D181" s="2" t="n">
         <f aca="false">SUM(E181,G181,I181,K181,M181,O181)</f>
@@ -14289,13 +14229,13 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D182" s="2" t="n">
         <f aca="false">SUM(E182,G182,I182,K182,M182,O182)</f>
@@ -14304,76 +14244,70 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>230</v>
+        <v>453</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>352</v>
+        <v>442</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D183" s="2" t="n">
         <f aca="false">SUM(E183,G183,I183,K183,M183,O183)</f>
         <v>1</v>
       </c>
-      <c r="O183" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P183" s="2" t="s">
-        <v>455</v>
+      <c r="G183" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>352</v>
+        <v>442</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D184" s="2" t="n">
         <f aca="false">SUM(E184,G184,I184,K184,M184,O184)</f>
         <v>1</v>
       </c>
-      <c r="O184" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P184" s="2" t="s">
+      <c r="K184" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L184" s="2" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="D185" s="2" t="n">
         <f aca="false">SUM(E185,G185,I185,K185,M185,O185)</f>
-        <v>1</v>
-      </c>
-      <c r="O185" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P185" s="2" t="s">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D186" s="2" t="n">
         <f aca="false">SUM(E186,G186,I186,K186,M186,O186)</f>
@@ -14382,13 +14316,13 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D187" s="2" t="n">
         <f aca="false">SUM(E187,G187,I187,K187,M187,O187)</f>
@@ -14397,28 +14331,64 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D188" s="2" t="n">
         <f aca="false">SUM(E188,G188,I188,K188,M188,O188)</f>
         <v>0</v>
       </c>
+      <c r="E188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="M188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D189" s="2" t="n">
         <f aca="false">SUM(E189,G189,I189,K189,M189,O189)</f>
@@ -14427,13 +14397,13 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D190" s="2" t="n">
         <f aca="false">SUM(E190,G190,I190,K190,M190,O190)</f>
@@ -14442,13 +14412,13 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D191" s="2" t="n">
         <f aca="false">SUM(E191,G191,I191,K191,M191,O191)</f>
@@ -14457,13 +14427,13 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="D192" s="2" t="n">
         <f aca="false">SUM(E192,G192,I192,K192,M192,O192)</f>
@@ -14472,53 +14442,65 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="D193" s="2" t="n">
         <f aca="false">SUM(E193,G193,I193,K193,M193,O193)</f>
-        <v>1</v>
-      </c>
-      <c r="O193" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P193" s="2" t="s">
-        <v>469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D194" s="2" t="n">
         <f aca="false">SUM(E194,G194,I194,K194,M194,O194)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G194" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O194" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P194" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="D195" s="2" t="n">
         <f aca="false">SUM(E195,G195,I195,K195,M195,O195)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G195" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14526,142 +14508,155 @@
         <v>471</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D196" s="2" t="n">
         <f aca="false">SUM(E196,G196,I196,K196,M196,O196)</f>
-        <v>2</v>
-      </c>
-      <c r="M196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N196" s="2" t="s">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="O196" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P196" s="2" t="s">
-        <v>279</v>
+        <v>473</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="D197" s="2" t="n">
         <f aca="false">SUM(E197,G197,I197,K197,M197,O197)</f>
         <v>2</v>
       </c>
+      <c r="G197" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>476</v>
+      </c>
       <c r="K197" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L197" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="O197" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P197" s="2" t="s">
-        <v>474</v>
+      <c r="L197" s="1" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="D198" s="2" t="n">
         <f aca="false">SUM(E198,G198,I198,K198,M198,O198)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E198" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="G198" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>231</v>
+        <v>266</v>
+      </c>
+      <c r="K198" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="D199" s="2" t="n">
         <f aca="false">SUM(E199,G199,I199,K199,M199,O199)</f>
         <v>0</v>
       </c>
+      <c r="H199" s="2"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>477</v>
+        <v>51</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="D200" s="2" t="n">
         <f aca="false">SUM(E200,G200,I200,K200,M200,O200)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K200" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="D201" s="2" t="n">
         <f aca="false">SUM(E201,G201,I201,K201,M201,O201)</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G201" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="K201" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>276</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="D202" s="2" t="n">
         <f aca="false">SUM(E202,G202,I202,K202,M202,O202)</f>
@@ -14671,165 +14666,279 @@
         <v>1</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>383</v>
+        <v>455</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="D203" s="2" t="n">
         <f aca="false">SUM(E203,G203,I203,K203,M203,O203)</f>
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E203" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G203" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="K203" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="O203" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P203" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="D204" s="2" t="n">
         <f aca="false">SUM(E204,G204,I204,K204,M204,O204)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K204" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="O204" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P204" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="D205" s="2" t="n">
         <f aca="false">SUM(E205,G205,I205,K205,M205,O205)</f>
-        <v>0</v>
-      </c>
-      <c r="E205" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G205" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I205" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="2" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M205" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N205" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O205" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P205" s="2" t="s">
-        <v>247</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="D206" s="2" t="n">
         <f aca="false">SUM(E206,G206,I206,K206,M206,O206)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O206" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P206" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="D207" s="2" t="n">
         <f aca="false">SUM(E207,G207,I207,K207,M207,O207)</f>
         <v>0</v>
       </c>
+      <c r="E207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="M207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>485</v>
+        <v>45</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="D208" s="2" t="n">
         <f aca="false">SUM(E208,G208,I208,K208,M208,O208)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L208" s="2" t="s">
-        <v>276</v>
+        <v>493</v>
+      </c>
+      <c r="M208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="D209" s="2" t="n">
         <f aca="false">SUM(E209,G209,I209,K209,M209,O209)</f>
         <v>0</v>
       </c>
+      <c r="E209" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G209" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I209" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K209" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="M209" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O209" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>352</v>
+        <v>496</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="D210" s="2" t="n">
         <f aca="false">SUM(E210,G210,I210,K210,M210,O210)</f>
@@ -14838,13 +14947,13 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>352</v>
+        <v>496</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="D211" s="2" t="n">
         <f aca="false">SUM(E211,G211,I211,K211,M211,O211)</f>
@@ -14853,70 +14962,82 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>489</v>
+        <v>244</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>352</v>
+        <v>496</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="D212" s="2" t="n">
         <f aca="false">SUM(E212,G212,I212,K212,M212,O212)</f>
-        <v>1</v>
-      </c>
-      <c r="K212" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L212" s="2" t="s">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>352</v>
+        <v>499</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="D213" s="2" t="n">
         <f aca="false">SUM(E213,G213,I213,K213,M213,O213)</f>
-        <v>1</v>
-      </c>
-      <c r="K213" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L213" s="2" t="s">
-        <v>276</v>
+        <v>3</v>
+      </c>
+      <c r="E213" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G213" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I213" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>352</v>
+        <v>499</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="D214" s="2" t="n">
         <f aca="false">SUM(E214,G214,I214,K214,M214,O214)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>352</v>
+        <v>499</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="D215" s="2" t="n">
         <f aca="false">SUM(E215,G215,I215,K215,M215,O215)</f>
@@ -14925,175 +15046,140 @@
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>352</v>
+        <v>499</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D216" s="2" t="n">
         <f aca="false">SUM(E216,G216,I216,K216,M216,O216)</f>
         <v>1</v>
       </c>
-      <c r="O216" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P216" s="2" t="s">
-        <v>455</v>
+      <c r="K216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>261</v>
+        <v>504</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>352</v>
+        <v>499</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D217" s="2" t="n">
         <f aca="false">SUM(E217,G217,I217,K217,M217,O217)</f>
         <v>0</v>
       </c>
-      <c r="E217" s="1"/>
-      <c r="L217" s="2"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D218" s="2" t="n">
         <f aca="false">SUM(E218,G218,I218,K218,M218,O218)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G218" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="K218" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L218" s="1" t="s">
-        <v>499</v>
+        <v>239</v>
+      </c>
+      <c r="M218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P218" s="2" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="D219" s="2" t="n">
         <f aca="false">SUM(E219,G219,I219,K219,M219,O219)</f>
         <v>0</v>
       </c>
-      <c r="H219" s="2"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="D220" s="2" t="n">
         <f aca="false">SUM(E220,G220,I220,K220,M220,O220)</f>
-        <v>3</v>
-      </c>
-      <c r="E220" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G220" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H220" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K220" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L220" s="2" t="s">
-        <v>503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>51</v>
+        <v>510</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D221" s="2" t="n">
         <f aca="false">SUM(E221,G221,I221,K221,M221,O221)</f>
-        <v>1</v>
-      </c>
-      <c r="K221" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L221" s="2" t="s">
-        <v>414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D222" s="2" t="n">
         <f aca="false">SUM(E222,G222,I222,K222,M222,O222)</f>
-        <v>2</v>
-      </c>
-      <c r="G222" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K222" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L222" s="2" t="s">
-        <v>414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L222" s="2"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D223" s="2" t="n">
         <f aca="false">SUM(E223,G223,I223,K223,M223,O223)</f>
@@ -15103,192 +15189,210 @@
         <v>1</v>
       </c>
       <c r="L223" s="2" t="s">
-        <v>414</v>
+        <v>244</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>504</v>
+        <v>514</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D224" s="2" t="n">
         <f aca="false">SUM(E224,G224,I224,K224,M224,O224)</f>
-        <v>4</v>
-      </c>
-      <c r="E224" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="G224" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="K224" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L224" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="O224" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P224" s="2" t="s">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D225" s="2" t="n">
         <f aca="false">SUM(E225,G225,I225,K225,M225,O225)</f>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L225" s="2" t="s">
-        <v>414</v>
+        <v>248</v>
+      </c>
+      <c r="M225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="O225" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P225" s="2" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D226" s="2" t="n">
         <f aca="false">SUM(E226,G226,I226,K226,M226,O226)</f>
-        <v>1</v>
-      </c>
-      <c r="K226" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L226" s="2" t="s">
-        <v>414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="D227" s="2" t="n">
         <f aca="false">SUM(E227,G227,I227,K227,M227,O227)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>513</v>
+        <v>518</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D228" s="2" t="n">
         <f aca="false">SUM(E228,G228,I228,K228,M228,O228)</f>
-        <v>1</v>
-      </c>
-      <c r="O228" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P228" s="2" t="s">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>275</v>
+        <v>499</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D229" s="2" t="n">
         <f aca="false">SUM(E229,G229,I229,K229,M229,O229)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>275</v>
+        <v>499</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D230" s="2" t="n">
         <f aca="false">SUM(E230,G230,I230,K230,M230,O230)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K230" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="O230" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P230" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>275</v>
+        <v>499</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D231" s="2" t="n">
         <f aca="false">SUM(E231,G231,I231,K231,M231,O231)</f>
-        <v>1</v>
-      </c>
-      <c r="O231" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P231" s="2" t="s">
-        <v>250</v>
+        <v>2</v>
+      </c>
+      <c r="E231" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K231" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D232" s="2" t="n">
         <f aca="false">SUM(E232,G232,I232,K232,M232,O232)</f>
@@ -15297,92 +15401,80 @@
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="D233" s="2" t="n">
         <f aca="false">SUM(E233,G233,I233,K233,M233,O233)</f>
-        <v>2</v>
-      </c>
-      <c r="E233" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F233" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O233" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P233" s="1" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D234" s="2" t="n">
         <f aca="false">SUM(E234,G234,I234,K234,M234,O234)</f>
-        <v>1</v>
-      </c>
-      <c r="O234" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P234" s="1" t="s">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="D235" s="2" t="n">
         <f aca="false">SUM(E235,G235,I235,K235,M235,O235)</f>
-        <v>1</v>
-      </c>
-      <c r="O235" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P235" s="1" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="D236" s="2" t="n">
         <f aca="false">SUM(E236,G236,I236,K236,M236,O236)</f>
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="M236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N236" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="O236" s="1" t="n">
         <v>1</v>
       </c>
       <c r="P236" s="2" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15390,220 +15482,148 @@
         <v>527</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="D237" s="2" t="n">
         <f aca="false">SUM(E237,G237,I237,K237,M237,O237)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G237" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I237" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J237" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K237" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L237" s="2" t="s">
-        <v>528</v>
+        <v>1</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="M237" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N237" s="2" t="s">
-        <v>247</v>
+        <v>356</v>
       </c>
       <c r="O237" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P237" s="2" t="s">
-        <v>247</v>
+        <v>356</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="D238" s="2" t="n">
         <f aca="false">SUM(E238,G238,I238,K238,M238,O238)</f>
-        <v>0</v>
-      </c>
-      <c r="E238" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G238" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I238" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J238" s="2" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="M238" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N238" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O238" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P238" s="2" t="s">
-        <v>247</v>
+        <v>529</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="7" t="s">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="D239" s="2" t="n">
         <f aca="false">SUM(E239,G239,I239,K239,M239,O239)</f>
-        <v>0</v>
-      </c>
-      <c r="E239" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G239" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I239" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J239" s="2" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M239" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N239" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O239" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P239" s="2" t="s">
-        <v>247</v>
+        <v>303</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>399</v>
+        <v>531</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D240" s="2" t="n">
         <f aca="false">SUM(E240,G240,I240,K240,M240,O240)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D241" s="2" t="n">
         <f aca="false">SUM(E241,G241,I241,K241,M241,O241)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="M241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N241" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D242" s="2" t="n">
         <f aca="false">SUM(E242,G242,I242,K242,M242,O242)</f>
-        <v>2</v>
-      </c>
-      <c r="E242" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G242" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>529</v>
+        <v>534</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D243" s="2" t="n">
         <f aca="false">SUM(E243,G243,I243,K243,M243,O243)</f>
@@ -15612,43 +15632,61 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D244" s="2" t="n">
         <f aca="false">SUM(E244,G244,I244,K244,M244,O244)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="M244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N244" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D245" s="2" t="n">
         <f aca="false">SUM(E245,G245,I245,K245,M245,O245)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M245" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N245" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>529</v>
+        <v>537</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D246" s="2" t="n">
         <f aca="false">SUM(E246,G246,I246,K246,M246,O246)</f>
@@ -15657,91 +15695,115 @@
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D247" s="2" t="n">
         <f aca="false">SUM(E247,G247,I247,K247,M247,O247)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M247" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N247" s="2" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D248" s="2" t="n">
         <f aca="false">SUM(E248,G248,I248,K248,M248,O248)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>411</v>
+        <v>540</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D249" s="2" t="n">
         <f aca="false">SUM(E249,G249,I249,K249,M249,O249)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D250" s="2" t="n">
         <f aca="false">SUM(E250,G250,I250,K250,M250,O250)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E250" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>532</v>
+        <v>263</v>
       </c>
       <c r="G250" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="I250" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J250" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
+      </c>
+      <c r="K250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P250" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>529</v>
+        <v>544</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D251" s="2" t="n">
         <f aca="false">SUM(E251,G251,I251,K251,M251,O251)</f>
@@ -15750,61 +15812,55 @@
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>541</v>
+        <v>231</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>330</v>
+        <v>499</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="D252" s="2" t="n">
         <f aca="false">SUM(E252,G252,I252,K252,M252,O252)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O252" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P252" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D253" s="2" t="n">
         <f aca="false">SUM(E253,G253,I253,K253,M253,O253)</f>
-        <v>3</v>
-      </c>
-      <c r="E253" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G253" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H253" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K253" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L253" s="2" t="s">
-        <v>544</v>
+        <v>1</v>
+      </c>
+      <c r="O253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P253" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D254" s="2" t="n">
         <f aca="false">SUM(E254,G254,I254,K254,M254,O254)</f>
@@ -15813,28 +15869,34 @@
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>543</v>
+        <v>549</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D255" s="2" t="n">
         <f aca="false">SUM(E255,G255,I255,K255,M255,O255)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O255" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P255" s="2" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>543</v>
+        <v>495</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D256" s="2" t="n">
         <f aca="false">SUM(E256,G256,I256,K256,M256,O256)</f>
@@ -15843,79 +15905,109 @@
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="D257" s="2" t="n">
         <f aca="false">SUM(E257,G257,I257,K257,M257,O257)</f>
-        <v>1</v>
-      </c>
-      <c r="K257" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L257" s="2" t="s">
-        <v>549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>543</v>
+        <v>552</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D258" s="2" t="n">
         <f aca="false">SUM(E258,G258,I258,K258,M258,O258)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="M258" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N258" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="O258" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P258" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>543</v>
+        <v>553</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D259" s="2" t="n">
         <f aca="false">SUM(E259,G259,I259,K259,M259,O259)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="O259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P259" s="2" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>543</v>
+        <v>556</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D260" s="2" t="n">
         <f aca="false">SUM(E260,G260,I260,K260,M260,O260)</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>543</v>
+        <v>557</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D261" s="2" t="n">
         <f aca="false">SUM(E261,G261,I261,K261,M261,O261)</f>
@@ -15924,163 +16016,151 @@
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D262" s="2" t="n">
         <f aca="false">SUM(E262,G262,I262,K262,M262,O262)</f>
-        <v>1</v>
-      </c>
-      <c r="K262" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L262" s="2" t="s">
-        <v>555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>543</v>
+        <v>559</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D263" s="2" t="n">
         <f aca="false">SUM(E263,G263,I263,K263,M263,O263)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D264" s="2" t="n">
         <f aca="false">SUM(E264,G264,I264,K264,M264,O264)</f>
-        <v>0</v>
-      </c>
-      <c r="E264" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G264" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I264" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" s="2" t="s">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M264" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O264" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" s="2" t="s">
-        <v>247</v>
+        <v>529</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>543</v>
+        <v>561</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="D265" s="2" t="n">
         <f aca="false">SUM(E265,G265,I265,K265,M265,O265)</f>
-        <v>1</v>
-      </c>
-      <c r="O265" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P265" s="1" t="s">
-        <v>559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D266" s="2" t="n">
         <f aca="false">SUM(E266,G266,I266,K266,M266,O266)</f>
-        <v>2</v>
-      </c>
-      <c r="E266" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F266" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="K266" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L266" s="2" t="s">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>543</v>
+        <v>563</v>
+      </c>
+      